--- a/Unity/Assets/Config/Excel/JingLingConfig.xlsx
+++ b/Unity/Assets/Config/Excel/JingLingConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitMengJing\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A16568A3-EEF8-4AE3-B454-BDD636F58970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FB02C76-2E11-476A-AAB4-56B6A5F21E31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JingLingProto" sheetId="1" r:id="rId1"/>
@@ -367,9 +367,6 @@
     <t>生命上限+1%</t>
   </si>
   <si>
-    <t>山贼</t>
-  </si>
-  <si>
     <t>119303;50</t>
   </si>
   <si>
@@ -404,9 +401,6 @@
   </si>
   <si>
     <t>法术强度提升100点</t>
-  </si>
-  <si>
-    <t>巨锤酋长</t>
   </si>
   <si>
     <t>100403;100</t>
@@ -741,6 +735,14 @@
   </si>
   <si>
     <t>0,170,400,75,0</t>
+  </si>
+  <si>
+    <t>绿石怪</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>森灵守卫者</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -885,7 +887,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -910,6 +912,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="10" fillId="4" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1366,7 +1371,7 @@
         <v>36</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="R4" s="2" t="s">
         <v>37</v>
@@ -1535,7 +1540,7 @@
         <v>0</v>
       </c>
       <c r="Z6" s="7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7" spans="3:26" x14ac:dyDescent="0.3">
@@ -1603,7 +1608,7 @@
         <v>0</v>
       </c>
       <c r="Z7" s="7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="3:26" x14ac:dyDescent="0.3">
@@ -1671,7 +1676,7 @@
         <v>0</v>
       </c>
       <c r="Z8" s="7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9" spans="3:26" x14ac:dyDescent="0.3">
@@ -1739,15 +1744,15 @@
         <v>0</v>
       </c>
       <c r="Z9" s="7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C10" s="3">
         <v>10005</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>65</v>
+      <c r="D10" s="10" t="s">
+        <v>188</v>
       </c>
       <c r="E10" s="4">
         <v>2</v>
@@ -1771,7 +1776,7 @@
         <v>310105</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M10" s="3">
         <v>0</v>
@@ -1786,7 +1791,7 @@
         <v>52</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="S10" s="5">
         <v>2</v>
@@ -1807,7 +1812,7 @@
         <v>0</v>
       </c>
       <c r="Z10" s="7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="3:26" x14ac:dyDescent="0.3">
@@ -1815,7 +1820,7 @@
         <v>10006</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E11" s="4">
         <v>2</v>
@@ -1839,7 +1844,7 @@
         <v>310106</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M11" s="3">
         <v>0</v>
@@ -1854,7 +1859,7 @@
         <v>52</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="S11" s="5">
         <v>2</v>
@@ -1875,7 +1880,7 @@
         <v>0</v>
       </c>
       <c r="Z11" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="3:26" x14ac:dyDescent="0.3">
@@ -1883,7 +1888,7 @@
         <v>10007</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E12" s="4">
         <v>2</v>
@@ -1907,7 +1912,7 @@
         <v>310107</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M12" s="3">
         <v>0</v>
@@ -1922,7 +1927,7 @@
         <v>52</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S12" s="5">
         <v>2</v>
@@ -1943,7 +1948,7 @@
         <v>0</v>
       </c>
       <c r="Z12" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="3:26" x14ac:dyDescent="0.3">
@@ -1951,7 +1956,7 @@
         <v>10008</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E13" s="4">
         <v>2</v>
@@ -1975,7 +1980,7 @@
         <v>310160</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M13" s="3">
         <v>0</v>
@@ -1987,10 +1992,10 @@
         <v>-1</v>
       </c>
       <c r="P13" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q13" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="Q13" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="S13" s="5">
         <v>2</v>
@@ -2018,8 +2023,8 @@
       <c r="C14" s="3">
         <v>10009</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>78</v>
+      <c r="D14" s="10" t="s">
+        <v>189</v>
       </c>
       <c r="E14" s="4">
         <v>2</v>
@@ -2043,7 +2048,7 @@
         <v>310161</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -2055,10 +2060,10 @@
         <v>-1</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="S14" s="5">
         <v>2</v>
@@ -2087,7 +2092,7 @@
         <v>10010</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E15" s="4">
         <v>2</v>
@@ -2111,7 +2116,7 @@
         <v>310162</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -2123,10 +2128,10 @@
         <v>-1</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="S15" s="5">
         <v>2</v>
@@ -2155,7 +2160,7 @@
         <v>10011</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E16" s="4">
         <v>2</v>
@@ -2179,7 +2184,7 @@
         <v>310163</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="M16" s="3">
         <v>0</v>
@@ -2191,10 +2196,10 @@
         <v>-1</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="S16" s="5">
         <v>2</v>
@@ -2215,7 +2220,7 @@
         <v>0</v>
       </c>
       <c r="Z16" s="9" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="17" spans="3:26" x14ac:dyDescent="0.3">
@@ -2223,7 +2228,7 @@
         <v>10012</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E17" s="4">
         <v>2</v>
@@ -2247,7 +2252,7 @@
         <v>310164</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="M17" s="3">
         <v>0</v>
@@ -2259,10 +2264,10 @@
         <v>-1</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="S17" s="5">
         <v>2</v>
@@ -2283,7 +2288,7 @@
         <v>0</v>
       </c>
       <c r="Z17" s="9" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" spans="3:26" x14ac:dyDescent="0.3">
@@ -2291,7 +2296,7 @@
         <v>10013</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E18" s="4">
         <v>2</v>
@@ -2315,7 +2320,7 @@
         <v>310165</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="M18" s="3">
         <v>0</v>
@@ -2327,10 +2332,10 @@
         <v>-1</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="S18" s="5">
         <v>2</v>
@@ -2351,7 +2356,7 @@
         <v>0</v>
       </c>
       <c r="Z18" s="9" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19" spans="3:26" x14ac:dyDescent="0.3">
@@ -2359,7 +2364,7 @@
         <v>10014</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E19" s="4">
         <v>2</v>
@@ -2419,7 +2424,7 @@
         <v>0</v>
       </c>
       <c r="Z19" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="3:26" x14ac:dyDescent="0.3">
@@ -2427,7 +2432,7 @@
         <v>10015</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E20" s="4">
         <v>2</v>
@@ -2487,7 +2492,7 @@
         <v>0</v>
       </c>
       <c r="Z20" s="7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="21" spans="3:26" x14ac:dyDescent="0.3">
@@ -2495,7 +2500,7 @@
         <v>10016</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E21" s="4">
         <v>2</v>
@@ -2555,7 +2560,7 @@
         <v>0</v>
       </c>
       <c r="Z21" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="22" spans="3:26" x14ac:dyDescent="0.3">
@@ -2563,7 +2568,7 @@
         <v>10017</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E22" s="4">
         <v>2</v>
@@ -2623,7 +2628,7 @@
         <v>0</v>
       </c>
       <c r="Z22" s="7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23" spans="3:26" x14ac:dyDescent="0.3">
@@ -2631,7 +2636,7 @@
         <v>10018</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E23" s="4">
         <v>2</v>
@@ -2655,7 +2660,7 @@
         <v>320105</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M23" s="3">
         <v>0</v>
@@ -2670,7 +2675,7 @@
         <v>52</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="S23" s="5">
         <v>2</v>
@@ -2691,7 +2696,7 @@
         <v>0</v>
       </c>
       <c r="Z23" s="7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="24" spans="3:26" x14ac:dyDescent="0.3">
@@ -2699,7 +2704,7 @@
         <v>10019</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E24" s="4">
         <v>2</v>
@@ -2759,7 +2764,7 @@
         <v>0</v>
       </c>
       <c r="Z24" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" spans="3:26" x14ac:dyDescent="0.3">
@@ -2767,7 +2772,7 @@
         <v>10020</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E25" s="4">
         <v>2</v>
@@ -2827,7 +2832,7 @@
         <v>0</v>
       </c>
       <c r="Z25" s="7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="3:26" x14ac:dyDescent="0.3">
@@ -2835,7 +2840,7 @@
         <v>10021</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E26" s="4">
         <v>2</v>
@@ -2871,7 +2876,7 @@
         <v>-1</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>61</v>
@@ -2895,7 +2900,7 @@
         <v>0</v>
       </c>
       <c r="Z26" s="9" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="3:26" x14ac:dyDescent="0.3">
@@ -2903,7 +2908,7 @@
         <v>10022</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E27" s="4">
         <v>2</v>
@@ -2939,7 +2944,7 @@
         <v>-1</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>64</v>
@@ -2963,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="Z27" s="9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="3:26" x14ac:dyDescent="0.3">
@@ -2971,7 +2976,7 @@
         <v>10023</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E28" s="4">
         <v>2</v>
@@ -2995,7 +3000,7 @@
         <v>320163</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M28" s="3">
         <v>0</v>
@@ -3007,10 +3012,10 @@
         <v>-1</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q28" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="S28" s="5">
         <v>2</v>
@@ -3031,7 +3036,7 @@
         <v>0</v>
       </c>
       <c r="Z28" s="9" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="3:26" x14ac:dyDescent="0.3">
@@ -3039,7 +3044,7 @@
         <v>10024</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E29" s="4">
         <v>2</v>
@@ -3063,7 +3068,7 @@
         <v>320164</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -3075,10 +3080,10 @@
         <v>-1</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q29" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="S29" s="5">
         <v>2</v>
@@ -3099,7 +3104,7 @@
         <v>0</v>
       </c>
       <c r="Z29" s="9" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="3:26" x14ac:dyDescent="0.3">
@@ -3107,7 +3112,7 @@
         <v>10025</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E30" s="4">
         <v>2</v>
@@ -3131,7 +3136,7 @@
         <v>320165</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M30" s="3">
         <v>0</v>
@@ -3143,10 +3148,10 @@
         <v>-1</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q30" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S30" s="5">
         <v>2</v>
@@ -3167,7 +3172,7 @@
         <v>0</v>
       </c>
       <c r="Z30" s="9" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="3:26" x14ac:dyDescent="0.3">
@@ -3175,7 +3180,7 @@
         <v>10026</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E31" s="4">
         <v>2</v>
@@ -3199,7 +3204,7 @@
         <v>330101</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M31" s="3">
         <v>0</v>
@@ -3214,7 +3219,7 @@
         <v>52</v>
       </c>
       <c r="Q31" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="S31" s="5">
         <v>2</v>
@@ -3235,7 +3240,7 @@
         <v>0</v>
       </c>
       <c r="Z31" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="32" spans="3:26" x14ac:dyDescent="0.3">
@@ -3243,7 +3248,7 @@
         <v>10027</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E32" s="4">
         <v>2</v>
@@ -3267,7 +3272,7 @@
         <v>330102</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -3282,7 +3287,7 @@
         <v>52</v>
       </c>
       <c r="Q32" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="S32" s="5">
         <v>2</v>
@@ -3303,7 +3308,7 @@
         <v>0</v>
       </c>
       <c r="Z32" s="7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="33" spans="3:26" x14ac:dyDescent="0.3">
@@ -3311,7 +3316,7 @@
         <v>10028</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E33" s="4">
         <v>2</v>
@@ -3335,7 +3340,7 @@
         <v>330103</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="M33" s="3">
         <v>0</v>
@@ -3350,7 +3355,7 @@
         <v>52</v>
       </c>
       <c r="Q33" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="S33" s="5">
         <v>2</v>
@@ -3371,7 +3376,7 @@
         <v>0</v>
       </c>
       <c r="Z33" s="7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="34" spans="3:26" x14ac:dyDescent="0.3">
@@ -3379,7 +3384,7 @@
         <v>10029</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E34" s="4">
         <v>2</v>
@@ -3403,7 +3408,7 @@
         <v>330104</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="M34" s="3">
         <v>0</v>
@@ -3418,7 +3423,7 @@
         <v>52</v>
       </c>
       <c r="Q34" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="S34" s="5">
         <v>2</v>
@@ -3439,7 +3444,7 @@
         <v>0</v>
       </c>
       <c r="Z34" s="7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="35" spans="3:26" x14ac:dyDescent="0.3">
@@ -3447,7 +3452,7 @@
         <v>10030</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E35" s="4">
         <v>2</v>
@@ -3471,7 +3476,7 @@
         <v>330105</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="M35" s="3">
         <v>0</v>
@@ -3486,7 +3491,7 @@
         <v>52</v>
       </c>
       <c r="Q35" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="S35" s="5">
         <v>2</v>
@@ -3507,7 +3512,7 @@
         <v>0</v>
       </c>
       <c r="Z35" s="7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="36" spans="3:26" x14ac:dyDescent="0.3">
@@ -3515,7 +3520,7 @@
         <v>10031</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E36" s="4">
         <v>2</v>
@@ -3539,7 +3544,7 @@
         <v>330106</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="M36" s="3">
         <v>0</v>
@@ -3554,7 +3559,7 @@
         <v>52</v>
       </c>
       <c r="Q36" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="S36" s="5">
         <v>2</v>
@@ -3575,7 +3580,7 @@
         <v>0</v>
       </c>
       <c r="Z36" s="7" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="37" spans="3:26" x14ac:dyDescent="0.3">
@@ -3583,7 +3588,7 @@
         <v>10032</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E37" s="4">
         <v>2</v>
@@ -3607,7 +3612,7 @@
         <v>330107</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M37" s="3">
         <v>0</v>
@@ -3622,7 +3627,7 @@
         <v>52</v>
       </c>
       <c r="Q37" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S37" s="5">
         <v>2</v>
@@ -3643,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="Z37" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="38" spans="3:26" x14ac:dyDescent="0.3">
@@ -3651,7 +3656,7 @@
         <v>10033</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E38" s="4">
         <v>2</v>
@@ -3675,7 +3680,7 @@
         <v>330161</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M38" s="3">
         <v>0</v>
@@ -3690,7 +3695,7 @@
         <v>52</v>
       </c>
       <c r="Q38" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="S38" s="5">
         <v>2</v>
@@ -3711,7 +3716,7 @@
         <v>0</v>
       </c>
       <c r="Z38" s="9" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="39" spans="3:26" x14ac:dyDescent="0.3">
@@ -3719,7 +3724,7 @@
         <v>10034</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E39" s="4">
         <v>2</v>
@@ -3755,7 +3760,7 @@
         <v>-1</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q39" s="3" t="s">
         <v>53</v>
@@ -3779,7 +3784,7 @@
         <v>0</v>
       </c>
       <c r="Z39" s="9" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="40" spans="3:26" x14ac:dyDescent="0.3">
@@ -3787,7 +3792,7 @@
         <v>10035</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E40" s="4">
         <v>2</v>
@@ -3823,7 +3828,7 @@
         <v>-1</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q40" s="3" t="s">
         <v>58</v>
@@ -3847,7 +3852,7 @@
         <v>0</v>
       </c>
       <c r="Z40" s="9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="41" spans="3:26" x14ac:dyDescent="0.3">
@@ -3855,7 +3860,7 @@
         <v>10036</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E41" s="4">
         <v>2</v>
@@ -3891,7 +3896,7 @@
         <v>-1</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>61</v>
@@ -3915,7 +3920,7 @@
         <v>0</v>
       </c>
       <c r="Z41" s="9" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="42" spans="3:26" x14ac:dyDescent="0.3">
@@ -3923,7 +3928,7 @@
         <v>10037</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E42" s="4">
         <v>2</v>
@@ -3959,7 +3964,7 @@
         <v>-1</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>64</v>
@@ -3983,7 +3988,7 @@
         <v>0</v>
       </c>
       <c r="Z42" s="9" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="43" spans="3:26" x14ac:dyDescent="0.3">
@@ -3991,7 +3996,7 @@
         <v>10038</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E43" s="4">
         <v>2</v>
@@ -4015,7 +4020,7 @@
         <v>340101</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -4030,7 +4035,7 @@
         <v>52</v>
       </c>
       <c r="Q43" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="S43" s="5">
         <v>2</v>
@@ -4051,7 +4056,7 @@
         <v>0</v>
       </c>
       <c r="Z43" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="44" spans="3:26" x14ac:dyDescent="0.3">
@@ -4059,7 +4064,7 @@
         <v>10039</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E44" s="4">
         <v>2</v>
@@ -4119,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="Z44" s="7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="45" spans="3:26" x14ac:dyDescent="0.3">
@@ -4127,7 +4132,7 @@
         <v>10040</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E45" s="4">
         <v>2</v>
@@ -4187,7 +4192,7 @@
         <v>0</v>
       </c>
       <c r="Z45" s="7" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="46" spans="3:26" x14ac:dyDescent="0.3">
@@ -4195,7 +4200,7 @@
         <v>10041</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E46" s="4">
         <v>2</v>
@@ -4255,7 +4260,7 @@
         <v>0</v>
       </c>
       <c r="Z46" s="7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="47" spans="3:26" x14ac:dyDescent="0.3">
@@ -4263,7 +4268,7 @@
         <v>10042</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E47" s="4">
         <v>2</v>
@@ -4323,7 +4328,7 @@
         <v>0</v>
       </c>
       <c r="Z47" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="48" spans="3:26" x14ac:dyDescent="0.3">
@@ -4331,7 +4336,7 @@
         <v>10043</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E48" s="4">
         <v>2</v>
@@ -4355,7 +4360,7 @@
         <v>340106</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
@@ -4370,7 +4375,7 @@
         <v>52</v>
       </c>
       <c r="Q48" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="S48" s="5">
         <v>2</v>
@@ -4391,7 +4396,7 @@
         <v>0</v>
       </c>
       <c r="Z48" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="49" spans="3:26" x14ac:dyDescent="0.3">
@@ -4399,7 +4404,7 @@
         <v>10044</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E49" s="4">
         <v>2</v>
@@ -4423,7 +4428,7 @@
         <v>340107</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -4438,7 +4443,7 @@
         <v>52</v>
       </c>
       <c r="Q49" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="S49" s="5">
         <v>2</v>
@@ -4459,7 +4464,7 @@
         <v>0</v>
       </c>
       <c r="Z49" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="50" spans="3:26" x14ac:dyDescent="0.3">
@@ -4467,7 +4472,7 @@
         <v>10045</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E50" s="4">
         <v>2</v>
@@ -4491,7 +4496,7 @@
         <v>340161</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M50" s="3">
         <v>0</v>
@@ -4503,10 +4508,10 @@
         <v>-1</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q50" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S50" s="5">
         <v>2</v>
@@ -4527,7 +4532,7 @@
         <v>0</v>
       </c>
       <c r="Z50" s="9" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="51" spans="3:26" x14ac:dyDescent="0.3">
@@ -4535,7 +4540,7 @@
         <v>10046</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E51" s="4">
         <v>2</v>
@@ -4559,7 +4564,7 @@
         <v>340162</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M51" s="3">
         <v>0</v>
@@ -4571,10 +4576,10 @@
         <v>-1</v>
       </c>
       <c r="P51" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q51" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="Q51" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="S51" s="5">
         <v>2</v>
@@ -4595,7 +4600,7 @@
         <v>0</v>
       </c>
       <c r="Z51" s="9" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="52" spans="3:26" x14ac:dyDescent="0.3">
@@ -4603,7 +4608,7 @@
         <v>10047</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E52" s="4">
         <v>2</v>
@@ -4627,7 +4632,7 @@
         <v>340163</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -4639,10 +4644,10 @@
         <v>-1</v>
       </c>
       <c r="P52" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q52" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="S52" s="5">
         <v>2</v>
@@ -4663,7 +4668,7 @@
         <v>0</v>
       </c>
       <c r="Z52" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="53" spans="3:26" x14ac:dyDescent="0.3">
@@ -4671,7 +4676,7 @@
         <v>10048</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E53" s="4">
         <v>2</v>
@@ -4695,7 +4700,7 @@
         <v>340164</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="M53" s="3">
         <v>0</v>
@@ -4707,10 +4712,10 @@
         <v>-1</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="S53" s="5">
         <v>2</v>
@@ -4731,7 +4736,7 @@
         <v>0</v>
       </c>
       <c r="Z53" s="9" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="54" spans="3:26" x14ac:dyDescent="0.3">
@@ -4739,7 +4744,7 @@
         <v>10049</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E54" s="4">
         <v>2</v>
@@ -4763,7 +4768,7 @@
         <v>340165</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="M54" s="3">
         <v>0</v>
@@ -4775,10 +4780,10 @@
         <v>-1</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q54" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="S54" s="5">
         <v>2</v>
@@ -4799,7 +4804,7 @@
         <v>0</v>
       </c>
       <c r="Z54" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="55" spans="3:26" x14ac:dyDescent="0.3">
@@ -4807,7 +4812,7 @@
         <v>10050</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E55" s="4">
         <v>2</v>
@@ -4831,7 +4836,7 @@
         <v>350101</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="M55" s="3">
         <v>0</v>
@@ -4846,7 +4851,7 @@
         <v>52</v>
       </c>
       <c r="Q55" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="S55" s="5">
         <v>2</v>
@@ -4867,7 +4872,7 @@
         <v>0</v>
       </c>
       <c r="Z55" s="7" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="56" spans="3:26" x14ac:dyDescent="0.3">
@@ -4875,7 +4880,7 @@
         <v>10051</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E56" s="4">
         <v>2</v>
@@ -4899,7 +4904,7 @@
         <v>350102</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="M56" s="3">
         <v>0</v>
@@ -4914,7 +4919,7 @@
         <v>52</v>
       </c>
       <c r="Q56" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="S56" s="5">
         <v>2</v>
@@ -4935,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="Z56" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="57" spans="3:26" x14ac:dyDescent="0.3">
@@ -4943,7 +4948,7 @@
         <v>10052</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E57" s="4">
         <v>2</v>
@@ -4967,7 +4972,7 @@
         <v>350103</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M57" s="3">
         <v>0</v>
@@ -4982,7 +4987,7 @@
         <v>52</v>
       </c>
       <c r="Q57" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="S57" s="5">
         <v>2</v>
@@ -5003,7 +5008,7 @@
         <v>0</v>
       </c>
       <c r="Z57" s="7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="58" spans="3:26" x14ac:dyDescent="0.3">
@@ -5011,7 +5016,7 @@
         <v>10053</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E58" s="4">
         <v>2</v>
@@ -5035,7 +5040,7 @@
         <v>350104</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -5050,7 +5055,7 @@
         <v>52</v>
       </c>
       <c r="Q58" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="S58" s="5">
         <v>2</v>
@@ -5071,7 +5076,7 @@
         <v>0</v>
       </c>
       <c r="Z58" s="7" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="59" spans="3:26" x14ac:dyDescent="0.3">
@@ -5079,7 +5084,7 @@
         <v>10054</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E59" s="4">
         <v>2</v>
@@ -5139,7 +5144,7 @@
         <v>0</v>
       </c>
       <c r="Z59" s="7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="60" spans="3:26" x14ac:dyDescent="0.3">
@@ -5147,7 +5152,7 @@
         <v>10055</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E60" s="4">
         <v>2</v>
@@ -5207,7 +5212,7 @@
         <v>0</v>
       </c>
       <c r="Z60" s="7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="61" spans="3:26" x14ac:dyDescent="0.3">
@@ -5215,7 +5220,7 @@
         <v>10056</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E61" s="4">
         <v>2</v>
@@ -5251,7 +5256,7 @@
         <v>-1</v>
       </c>
       <c r="P61" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q61" s="3" t="s">
         <v>61</v>
@@ -5275,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="Z61" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="62" spans="3:26" x14ac:dyDescent="0.3">
@@ -5283,7 +5288,7 @@
         <v>10057</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E62" s="4">
         <v>2</v>
@@ -5319,7 +5324,7 @@
         <v>-1</v>
       </c>
       <c r="P62" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q62" s="3" t="s">
         <v>64</v>
@@ -5343,7 +5348,7 @@
         <v>0</v>
       </c>
       <c r="Z62" s="9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="63" spans="3:26" x14ac:dyDescent="0.3">
@@ -5351,7 +5356,7 @@
         <v>10058</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E63" s="4">
         <v>2</v>
@@ -5375,7 +5380,7 @@
         <v>350163</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M63" s="3">
         <v>0</v>
@@ -5387,10 +5392,10 @@
         <v>-1</v>
       </c>
       <c r="P63" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q63" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="S63" s="5">
         <v>2</v>
@@ -5411,7 +5416,7 @@
         <v>0</v>
       </c>
       <c r="Z63" s="9" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="64" spans="3:26" x14ac:dyDescent="0.3">
@@ -5419,7 +5424,7 @@
         <v>10059</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E64" s="4">
         <v>2</v>
@@ -5443,7 +5448,7 @@
         <v>350164</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="M64" s="3">
         <v>0</v>
@@ -5455,10 +5460,10 @@
         <v>-1</v>
       </c>
       <c r="P64" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q64" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="S64" s="5">
         <v>2</v>
@@ -5487,7 +5492,7 @@
         <v>10060</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E65" s="4">
         <v>2</v>
@@ -5511,7 +5516,7 @@
         <v>350165</v>
       </c>
       <c r="L65" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="M65" s="3">
         <v>0</v>
@@ -5523,10 +5528,10 @@
         <v>-1</v>
       </c>
       <c r="P65" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q65" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="S65" s="5">
         <v>2</v>
@@ -5547,7 +5552,7 @@
         <v>0</v>
       </c>
       <c r="Z65" s="9" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="66" spans="3:26" x14ac:dyDescent="0.3">
@@ -5555,7 +5560,7 @@
         <v>20001</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E66" s="3">
         <v>1</v>
@@ -5579,32 +5584,32 @@
         <v>400001</v>
       </c>
       <c r="L66" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="M66" s="5">
+        <v>0</v>
+      </c>
+      <c r="N66" s="1">
+        <v>0</v>
+      </c>
+      <c r="P66" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q66" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="M66" s="5">
-        <v>0</v>
-      </c>
-      <c r="N66" s="1">
-        <v>0</v>
-      </c>
-      <c r="P66" s="1" t="s">
+      <c r="S66" s="5">
+        <v>2</v>
+      </c>
+      <c r="T66" s="5">
+        <v>0</v>
+      </c>
+      <c r="U66" s="5">
+        <v>0</v>
+      </c>
+      <c r="V66" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="S66" s="5">
-        <v>2</v>
-      </c>
-      <c r="T66" s="5">
-        <v>0</v>
-      </c>
-      <c r="U66" s="5">
-        <v>0</v>
-      </c>
-      <c r="V66" s="1" t="s">
-        <v>146</v>
-      </c>
       <c r="W66" s="1">
         <v>0</v>
       </c>
@@ -5612,7 +5617,7 @@
         <v>0</v>
       </c>
       <c r="Z66" s="7" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="67" spans="3:26" x14ac:dyDescent="0.3">
@@ -5620,7 +5625,7 @@
         <v>20002</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E67" s="3">
         <v>1</v>
@@ -5644,32 +5649,32 @@
         <v>400002</v>
       </c>
       <c r="L67" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="M67" s="5">
+        <v>0</v>
+      </c>
+      <c r="N67" s="1">
+        <v>0</v>
+      </c>
+      <c r="P67" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q67" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="M67" s="5">
-        <v>0</v>
-      </c>
-      <c r="N67" s="1">
-        <v>0</v>
-      </c>
-      <c r="P67" s="1" t="s">
+      <c r="S67" s="5">
+        <v>2</v>
+      </c>
+      <c r="T67" s="5">
+        <v>0</v>
+      </c>
+      <c r="U67" s="5">
+        <v>0</v>
+      </c>
+      <c r="V67" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="Q67" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="S67" s="5">
-        <v>2</v>
-      </c>
-      <c r="T67" s="5">
-        <v>0</v>
-      </c>
-      <c r="U67" s="5">
-        <v>0</v>
-      </c>
-      <c r="V67" s="1" t="s">
-        <v>146</v>
-      </c>
       <c r="W67" s="1">
         <v>0</v>
       </c>
@@ -5677,7 +5682,7 @@
         <v>0</v>
       </c>
       <c r="Z67" s="7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="68" spans="3:26" x14ac:dyDescent="0.3">
@@ -5685,7 +5690,7 @@
         <v>20003</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E68" s="3">
         <v>1</v>
@@ -5709,7 +5714,7 @@
         <v>400003</v>
       </c>
       <c r="L68" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M68" s="5">
         <v>0</v>
@@ -5718,23 +5723,23 @@
         <v>0</v>
       </c>
       <c r="P68" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q68" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="S68" s="5">
+        <v>2</v>
+      </c>
+      <c r="T68" s="5">
+        <v>0</v>
+      </c>
+      <c r="U68" s="5">
+        <v>0</v>
+      </c>
+      <c r="V68" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="Q68" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="S68" s="5">
-        <v>2</v>
-      </c>
-      <c r="T68" s="5">
-        <v>0</v>
-      </c>
-      <c r="U68" s="5">
-        <v>0</v>
-      </c>
-      <c r="V68" s="1" t="s">
-        <v>146</v>
-      </c>
       <c r="W68" s="1">
         <v>0</v>
       </c>
@@ -5742,7 +5747,7 @@
         <v>0</v>
       </c>
       <c r="Z68" s="7" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="69" spans="3:26" x14ac:dyDescent="0.3">
@@ -5750,7 +5755,7 @@
         <v>20004</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E69" s="3">
         <v>1</v>
@@ -5783,7 +5788,7 @@
         <v>0</v>
       </c>
       <c r="P69" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q69" s="3" t="s">
         <v>61</v>
@@ -5798,7 +5803,7 @@
         <v>0</v>
       </c>
       <c r="V69" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="W69" s="1">
         <v>0</v>
@@ -5807,7 +5812,7 @@
         <v>0</v>
       </c>
       <c r="Z69" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="70" spans="3:26" x14ac:dyDescent="0.3">
@@ -5815,7 +5820,7 @@
         <v>20005</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E70" s="3">
         <v>1</v>
@@ -5848,7 +5853,7 @@
         <v>0</v>
       </c>
       <c r="P70" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q70" s="3" t="s">
         <v>64</v>
@@ -5863,7 +5868,7 @@
         <v>0</v>
       </c>
       <c r="V70" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="W70" s="1">
         <v>0</v>
@@ -5872,7 +5877,7 @@
         <v>0</v>
       </c>
       <c r="Z70" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="71" spans="3:26" x14ac:dyDescent="0.3">
@@ -5880,7 +5885,7 @@
         <v>20006</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E71" s="3">
         <v>1</v>
@@ -5904,7 +5909,7 @@
         <v>400006</v>
       </c>
       <c r="L71" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="M71" s="5">
         <v>0</v>
@@ -5913,23 +5918,23 @@
         <v>0</v>
       </c>
       <c r="P71" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q71" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="S71" s="5">
+        <v>2</v>
+      </c>
+      <c r="T71" s="5">
+        <v>0</v>
+      </c>
+      <c r="U71" s="5">
+        <v>0</v>
+      </c>
+      <c r="V71" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="Q71" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="S71" s="5">
-        <v>2</v>
-      </c>
-      <c r="T71" s="5">
-        <v>0</v>
-      </c>
-      <c r="U71" s="5">
-        <v>0</v>
-      </c>
-      <c r="V71" s="1" t="s">
-        <v>146</v>
-      </c>
       <c r="W71" s="1">
         <v>0</v>
       </c>
@@ -5937,7 +5942,7 @@
         <v>0</v>
       </c>
       <c r="Z71" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="72" spans="3:26" x14ac:dyDescent="0.3">
@@ -5945,7 +5950,7 @@
         <v>20007</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E72" s="3">
         <v>1</v>
@@ -5969,7 +5974,7 @@
         <v>400007</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="M72" s="5">
         <v>0</v>
@@ -5978,23 +5983,23 @@
         <v>0</v>
       </c>
       <c r="P72" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q72" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="S72" s="5">
+        <v>2</v>
+      </c>
+      <c r="T72" s="5">
+        <v>0</v>
+      </c>
+      <c r="U72" s="5">
+        <v>0</v>
+      </c>
+      <c r="V72" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="S72" s="5">
-        <v>2</v>
-      </c>
-      <c r="T72" s="5">
-        <v>0</v>
-      </c>
-      <c r="U72" s="5">
-        <v>0</v>
-      </c>
-      <c r="V72" s="1" t="s">
-        <v>146</v>
-      </c>
       <c r="W72" s="1">
         <v>0</v>
       </c>
@@ -6002,7 +6007,7 @@
         <v>0</v>
       </c>
       <c r="Z72" s="7" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="73" spans="3:26" x14ac:dyDescent="0.3">
@@ -6010,7 +6015,7 @@
         <v>20008</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E73" s="3">
         <v>1</v>
@@ -6043,7 +6048,7 @@
         <v>0</v>
       </c>
       <c r="P73" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q73" s="3" t="s">
         <v>58</v>
@@ -6058,7 +6063,7 @@
         <v>0</v>
       </c>
       <c r="V73" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="W73" s="1">
         <v>0</v>
@@ -6067,7 +6072,7 @@
         <v>0</v>
       </c>
       <c r="Z73" s="7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="74" spans="3:26" x14ac:dyDescent="0.3">

--- a/Unity/Assets/Config/Excel/JingLingConfig.xlsx
+++ b/Unity/Assets/Config/Excel/JingLingConfig.xlsx
@@ -1,32 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitMengJing\Unity\Assets\Config\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FB02C76-2E11-476A-AAB4-56B6A5F21E31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12795"/>
   </bookViews>
   <sheets>
     <sheet name="JingLingProto" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Admin</author>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="G3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -50,7 +57,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="I3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -75,7 +82,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="O3" authorId="1">
       <text>
         <r>
           <rPr>
@@ -98,7 +105,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="W3" authorId="1">
       <text>
         <r>
           <rPr>
@@ -117,7 +124,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="E4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -140,7 +147,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="F4" authorId="0">
       <text>
         <r>
           <rPr>
@@ -283,6 +290,9 @@
     <t>Lv</t>
   </si>
   <si>
+    <t>ProDes</t>
+  </si>
+  <si>
     <t>Des</t>
   </si>
   <si>
@@ -322,7 +332,7 @@
     <t>double</t>
   </si>
   <si>
-    <t>史莱姆</t>
+    <t>软泥怪</t>
   </si>
   <si>
     <t>100403;50</t>
@@ -337,70 +347,82 @@
     <t>击败怪物有一定怪物激活</t>
   </si>
   <si>
+    <t>0,60,250,35,0</t>
+  </si>
+  <si>
+    <t>森灵小妖</t>
+  </si>
+  <si>
+    <t>100203;500</t>
+  </si>
+  <si>
+    <t>生命上限+500点</t>
+  </si>
+  <si>
+    <t>森灵小猪</t>
+  </si>
+  <si>
+    <t>202103;0.01</t>
+  </si>
+  <si>
+    <t>重击概率+1%</t>
+  </si>
+  <si>
+    <t>绿林熊妖</t>
+  </si>
+  <si>
+    <t>100202;0.01</t>
+  </si>
+  <si>
+    <t>生命上限+1%</t>
+  </si>
+  <si>
+    <t>绿石怪</t>
+  </si>
+  <si>
+    <t>119303;50</t>
+  </si>
+  <si>
+    <t>命中等级提升50点</t>
+  </si>
+  <si>
+    <t>森林蜘蛛</t>
+  </si>
+  <si>
+    <t>200903;0.05</t>
+  </si>
+  <si>
+    <t>伤害加成+5%</t>
+  </si>
+  <si>
+    <t>0,60,250,40,0</t>
+  </si>
+  <si>
+    <t>森林熊</t>
+  </si>
+  <si>
+    <t>200303;0.01</t>
+  </si>
+  <si>
+    <t>闪避概率+1%</t>
+  </si>
+  <si>
+    <t>獠牙猪妖</t>
+  </si>
+  <si>
+    <t>120703;100</t>
+  </si>
+  <si>
+    <t>领主级</t>
+  </si>
+  <si>
+    <t>法术强度提升100点</t>
+  </si>
+  <si>
     <t>0,110,400,60,0</t>
   </si>
   <si>
-    <t>森灵小妖</t>
-  </si>
-  <si>
-    <t>100203;500</t>
-  </si>
-  <si>
-    <t>生命上限+500点</t>
-  </si>
-  <si>
-    <t>森灵小猪</t>
-  </si>
-  <si>
-    <t>202103;0.01</t>
-  </si>
-  <si>
-    <t>重击概率+1%</t>
-  </si>
-  <si>
-    <t>绿林熊妖</t>
-  </si>
-  <si>
-    <t>100202;0.01</t>
-  </si>
-  <si>
-    <t>生命上限+1%</t>
-  </si>
-  <si>
-    <t>119303;50</t>
-  </si>
-  <si>
-    <t>命中等级提升50点</t>
-  </si>
-  <si>
-    <t>森林蜘蛛</t>
-  </si>
-  <si>
-    <t>200903;0.05</t>
-  </si>
-  <si>
-    <t>伤害加成+5%</t>
-  </si>
-  <si>
-    <t>森林熊</t>
-  </si>
-  <si>
-    <t>200303;0.01</t>
-  </si>
-  <si>
-    <t>闪避概率+1%</t>
-  </si>
-  <si>
-    <t>獠牙猪妖</t>
-  </si>
-  <si>
-    <t>120703;100</t>
-  </si>
-  <si>
-    <t>领主级</t>
-  </si>
-  <si>
-    <t>法术强度提升100点</t>
+    <t>森灵守卫者</t>
   </si>
   <si>
     <t>100403;100</t>
@@ -427,6 +449,9 @@
     <t>攻击强度提升100点</t>
   </si>
   <si>
+    <t>0,220,400,80,0</t>
+  </si>
+  <si>
     <t>森灵之树</t>
   </si>
   <si>
@@ -436,6 +461,9 @@
     <t>抗暴率+1%</t>
   </si>
   <si>
+    <t>0,125,400,65,0</t>
+  </si>
+  <si>
     <t>漠灵风暴之王</t>
   </si>
   <si>
@@ -445,45 +473,75 @@
     <t>物防提升100点</t>
   </si>
   <si>
+    <t>0,170,400,60,0</t>
+  </si>
+  <si>
     <t>绿洲龟</t>
   </si>
   <si>
     <t>绿洲恐龙</t>
   </si>
   <si>
+    <t>0,110,250,60,0</t>
+  </si>
+  <si>
     <t>绿洲蜗牛</t>
   </si>
   <si>
     <t>荒漠鹰</t>
   </si>
   <si>
+    <t>0,80,250,50,0</t>
+  </si>
+  <si>
     <t>迅捷恐龙</t>
   </si>
   <si>
     <t>遗迹火焰</t>
   </si>
   <si>
+    <t>0,60,250,30,0</t>
+  </si>
+  <si>
     <t>遗迹弓手</t>
   </si>
   <si>
     <t>荒漠巨蟹</t>
   </si>
   <si>
+    <t>0,135,400,70,0</t>
+  </si>
+  <si>
     <t>沙漠之鳄</t>
   </si>
   <si>
+    <t>0,190,500,70,-60</t>
+  </si>
+  <si>
     <t>绿洲龟王</t>
   </si>
   <si>
+    <t>0,150,400,80,0</t>
+  </si>
+  <si>
     <t>遗迹守护者</t>
   </si>
   <si>
+    <t>0,200,400,80,0</t>
+  </si>
+  <si>
     <t>遗迹之王</t>
   </si>
   <si>
+    <t>0,120,400,70,0</t>
+  </si>
+  <si>
     <t>螃蟹护卫</t>
   </si>
   <si>
+    <t>0,90,250,50,0</t>
+  </si>
+  <si>
     <t>猛虎</t>
   </si>
   <si>
@@ -499,6 +557,9 @@
     <t>兽人骑兵</t>
   </si>
   <si>
+    <t>0,90,250,60,0</t>
+  </si>
+  <si>
     <t>岩石护卫</t>
   </si>
   <si>
@@ -511,27 +572,48 @@
     <t>暴击概率+1%</t>
   </si>
   <si>
+    <t>0,125,400,70,0</t>
+  </si>
+  <si>
     <t>森林之王</t>
   </si>
   <si>
+    <t>0,280,400,70,0</t>
+  </si>
+  <si>
     <t>地下巨鳄</t>
   </si>
   <si>
+    <t>0,130,400,80,-60</t>
+  </si>
+  <si>
     <t>地下兽人祭祀</t>
   </si>
   <si>
+    <t>0,140,400,65,0</t>
+  </si>
+  <si>
     <t>地灵牛头之王</t>
   </si>
   <si>
     <t>冰灵蜘蛛</t>
   </si>
   <si>
-    <t>雪狼</t>
+    <t>0,70,250,40,0</t>
+  </si>
+  <si>
+    <t>冰狼</t>
+  </si>
+  <si>
+    <t>0,80,250,45,0</t>
   </si>
   <si>
     <t>冰灵山羊</t>
   </si>
   <si>
+    <t>0,90,250,55,0</t>
+  </si>
+  <si>
     <t>冰封蜗牛</t>
   </si>
   <si>
@@ -550,18 +632,33 @@
     <t>冰灵之王</t>
   </si>
   <si>
+    <t>0,150,400,60,0</t>
+  </si>
+  <si>
     <t>冰岩巨人</t>
   </si>
   <si>
+    <t>0,140,400,70,0</t>
+  </si>
+  <si>
     <t>冰雪之主</t>
   </si>
   <si>
+    <t>0,160,400,65,0</t>
+  </si>
+  <si>
     <t>冰封巨龙</t>
   </si>
   <si>
+    <t>0,550,400,100,-60</t>
+  </si>
+  <si>
     <t>精灵蝴蝶</t>
   </si>
   <si>
+    <t>0,90,250,40,0</t>
+  </si>
+  <si>
     <t>影月护卫</t>
   </si>
   <si>
@@ -580,18 +677,30 @@
     <t>影月碟王</t>
   </si>
   <si>
+    <t>0,250,400,80,0</t>
+  </si>
+  <si>
     <t>影月女王</t>
   </si>
   <si>
+    <t>0,150,400,70,0</t>
+  </si>
+  <si>
     <t>暗灵守卫者</t>
   </si>
   <si>
+    <t>0,90,400,50,0</t>
+  </si>
+  <si>
     <t>暗灵狮鹫</t>
   </si>
   <si>
     <t>暗灵之主</t>
   </si>
   <si>
+    <t>0,170,400,75,0</t>
+  </si>
+  <si>
     <t>邪恶鳄鱼</t>
   </si>
   <si>
@@ -607,6 +716,9 @@
     <t>野外有一定几率遇到,可以抓捕它哟！</t>
   </si>
   <si>
+    <t>0,90,250,45,35</t>
+  </si>
+  <si>
     <t>火焰松鼠</t>
   </si>
   <si>
@@ -622,6 +734,9 @@
     <t>天空守卫</t>
   </si>
   <si>
+    <t>0,80,250,40,0</t>
+  </si>
+  <si>
     <t>熔岩之魔</t>
   </si>
   <si>
@@ -632,124 +747,19 @@
   </si>
   <si>
     <t>天狼蜘蛛</t>
-  </si>
-  <si>
-    <t>ProDes</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,110,250,60,0</t>
-  </si>
-  <si>
-    <t>0,60,250,35,0</t>
-  </si>
-  <si>
-    <t>0,60,250,40,0</t>
-  </si>
-  <si>
-    <t>0,80,250,50,0</t>
-  </si>
-  <si>
-    <t>0,60,250,30,0</t>
-  </si>
-  <si>
-    <t>0,90,250,50,0</t>
-  </si>
-  <si>
-    <t>0,90,250,60,0</t>
-  </si>
-  <si>
-    <t>0,70,250,40,0</t>
-  </si>
-  <si>
-    <t>0,80,250,45,0</t>
-  </si>
-  <si>
-    <t>0,90,250,55,0</t>
-  </si>
-  <si>
-    <t>0,90,250,40,0</t>
-  </si>
-  <si>
-    <t>0,90,250,45,35</t>
-  </si>
-  <si>
-    <t>0,80,250,40,0</t>
-  </si>
-  <si>
-    <t>0,220,400,80,0</t>
-  </si>
-  <si>
-    <t>0,125,400,65,0</t>
-  </si>
-  <si>
-    <t>0,170,400,60,0</t>
-  </si>
-  <si>
-    <t>0,135,400,70,0</t>
-  </si>
-  <si>
-    <t>0,190,500,70,-60</t>
-  </si>
-  <si>
-    <t>0,150,400,80,0</t>
-  </si>
-  <si>
-    <t>0,200,400,80,0</t>
-  </si>
-  <si>
-    <t>0,120,400,70,0</t>
-  </si>
-  <si>
-    <t>0,125,400,70,0</t>
-  </si>
-  <si>
-    <t>0,280,400,70,0</t>
-  </si>
-  <si>
-    <t>0,130,400,80,-60</t>
-  </si>
-  <si>
-    <t>0,140,400,65,0</t>
-  </si>
-  <si>
-    <t>0,150,400,60,0</t>
-  </si>
-  <si>
-    <t>0,140,400,70,0</t>
-  </si>
-  <si>
-    <t>0,160,400,65,0</t>
-  </si>
-  <si>
-    <t>0,550,400,100,-60</t>
-  </si>
-  <si>
-    <t>0,250,400,80,0</t>
-  </si>
-  <si>
-    <t>0,150,400,70,0</t>
-  </si>
-  <si>
-    <t>0,90,400,50,0</t>
-  </si>
-  <si>
-    <t>0,170,400,75,0</t>
-  </si>
-  <si>
-    <t>绿石怪</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>森灵守卫者</t>
-    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -784,10 +794,148 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color indexed="8"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -800,30 +948,8 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -838,7 +964,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14990691854609822"/>
+        <fgColor theme="0" tint="-0.149906918546098"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -848,8 +974,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -883,11 +1195,253 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -902,33 +1456,71 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="4" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="4" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1215,14 +1807,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="C1:Z108"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="1" customWidth="1"/>
@@ -1247,13 +1839,13 @@
     <col min="27" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" ht="20.1" customHeight="1"/>
+    <row r="2" ht="20.1" customHeight="1" spans="25:25">
       <c r="Y2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" ht="20.1" customHeight="1" spans="3:26">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1327,7 +1919,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" ht="20.1" customHeight="1" spans="3:26">
       <c r="C4" s="2" t="s">
         <v>1</v>
       </c>
@@ -1370,117 +1962,117 @@
       <c r="P4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="Q4" s="8" t="s">
-        <v>154</v>
+      <c r="Q4" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="X4" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Y4" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Z4" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="5" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" ht="20.1" customHeight="1" spans="3:26">
       <c r="C5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="F5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="K5" s="2" t="s">
+      <c r="L5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="N5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="O5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="P5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="W5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="N5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P5" s="2" t="s">
+      <c r="X5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="Q5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="U5" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="V5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="W5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="X5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y5" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="Z5" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" ht="20.1" customHeight="1" spans="3:26">
       <c r="C6" s="3">
         <v>10001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E6" s="4">
         <v>2</v>
@@ -1503,8 +2095,8 @@
       <c r="K6" s="4">
         <v>310101</v>
       </c>
-      <c r="L6" s="6" t="s">
-        <v>51</v>
+      <c r="L6" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="M6" s="3">
         <v>0</v>
@@ -1516,10 +2108,10 @@
         <v>-1</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="S6" s="5">
         <v>2</v>
@@ -1531,7 +2123,7 @@
         <v>0</v>
       </c>
       <c r="V6" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W6" s="5">
         <v>0</v>
@@ -1539,16 +2131,16 @@
       <c r="Y6" s="5">
         <v>0</v>
       </c>
-      <c r="Z6" s="7" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="7" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z6" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="3:26">
       <c r="C7" s="3">
         <v>10002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E7" s="4">
         <v>2</v>
@@ -1571,8 +2163,8 @@
       <c r="K7" s="4">
         <v>310102</v>
       </c>
-      <c r="L7" s="6" t="s">
-        <v>57</v>
+      <c r="L7" s="7" t="s">
+        <v>58</v>
       </c>
       <c r="M7" s="3">
         <v>0</v>
@@ -1584,10 +2176,10 @@
         <v>-1</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S7" s="5">
         <v>2</v>
@@ -1599,7 +2191,7 @@
         <v>0</v>
       </c>
       <c r="V7" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W7" s="5">
         <v>0</v>
@@ -1607,16 +2199,16 @@
       <c r="Y7" s="5">
         <v>0</v>
       </c>
-      <c r="Z7" s="7" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="8" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z7" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="3:26">
       <c r="C8" s="3">
         <v>10003</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E8" s="4">
         <v>2</v>
@@ -1639,8 +2231,8 @@
       <c r="K8" s="4">
         <v>310103</v>
       </c>
-      <c r="L8" s="6" t="s">
-        <v>60</v>
+      <c r="L8" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -1652,10 +2244,10 @@
         <v>-1</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S8" s="5">
         <v>2</v>
@@ -1667,7 +2259,7 @@
         <v>0</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W8" s="5">
         <v>0</v>
@@ -1675,16 +2267,16 @@
       <c r="Y8" s="5">
         <v>0</v>
       </c>
-      <c r="Z8" s="7" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="9" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z8" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="3:26">
       <c r="C9" s="3">
         <v>10004</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E9" s="4">
         <v>2</v>
@@ -1707,8 +2299,8 @@
       <c r="K9" s="4">
         <v>310104</v>
       </c>
-      <c r="L9" s="6" t="s">
-        <v>63</v>
+      <c r="L9" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="M9" s="3">
         <v>0</v>
@@ -1720,10 +2312,10 @@
         <v>-1</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S9" s="5">
         <v>2</v>
@@ -1735,7 +2327,7 @@
         <v>0</v>
       </c>
       <c r="V9" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W9" s="5">
         <v>0</v>
@@ -1743,16 +2335,16 @@
       <c r="Y9" s="5">
         <v>0</v>
       </c>
-      <c r="Z9" s="7" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="10" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z9" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="3:26">
       <c r="C10" s="3">
         <v>10005</v>
       </c>
-      <c r="D10" s="10" t="s">
-        <v>188</v>
+      <c r="D10" s="4" t="s">
+        <v>66</v>
       </c>
       <c r="E10" s="4">
         <v>2</v>
@@ -1775,8 +2367,8 @@
       <c r="K10" s="4">
         <v>310105</v>
       </c>
-      <c r="L10" s="6" t="s">
-        <v>65</v>
+      <c r="L10" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="M10" s="3">
         <v>0</v>
@@ -1788,10 +2380,10 @@
         <v>-1</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="S10" s="5">
         <v>2</v>
@@ -1803,7 +2395,7 @@
         <v>0</v>
       </c>
       <c r="V10" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W10" s="5">
         <v>0</v>
@@ -1811,16 +2403,16 @@
       <c r="Y10" s="5">
         <v>0</v>
       </c>
-      <c r="Z10" s="7" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="11" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z10" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="11" spans="3:26">
       <c r="C11" s="3">
         <v>10006</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E11" s="4">
         <v>2</v>
@@ -1843,8 +2435,8 @@
       <c r="K11" s="4">
         <v>310106</v>
       </c>
-      <c r="L11" s="6" t="s">
-        <v>68</v>
+      <c r="L11" s="7" t="s">
+        <v>70</v>
       </c>
       <c r="M11" s="3">
         <v>0</v>
@@ -1856,10 +2448,10 @@
         <v>-1</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="S11" s="5">
         <v>2</v>
@@ -1871,7 +2463,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W11" s="5">
         <v>0</v>
@@ -1879,16 +2471,16 @@
       <c r="Y11" s="5">
         <v>0</v>
       </c>
-      <c r="Z11" s="7" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="12" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z11" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="3:26">
       <c r="C12" s="3">
         <v>10007</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E12" s="4">
         <v>2</v>
@@ -1911,8 +2503,8 @@
       <c r="K12" s="4">
         <v>310107</v>
       </c>
-      <c r="L12" s="6" t="s">
-        <v>71</v>
+      <c r="L12" s="7" t="s">
+        <v>74</v>
       </c>
       <c r="M12" s="3">
         <v>0</v>
@@ -1924,39 +2516,39 @@
         <v>-1</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q12" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="S12" s="5">
+        <v>2</v>
+      </c>
+      <c r="T12" s="5">
+        <v>0</v>
+      </c>
+      <c r="U12" s="5">
+        <v>0</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="W12" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="S12" s="5">
-        <v>2</v>
-      </c>
-      <c r="T12" s="5">
-        <v>0</v>
-      </c>
-      <c r="U12" s="5">
-        <v>0</v>
-      </c>
-      <c r="V12" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="W12" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="7" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="13" spans="3:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="3:26">
       <c r="C13" s="3">
         <v>10008</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E13" s="4">
         <v>2</v>
@@ -1979,8 +2571,8 @@
       <c r="K13" s="4">
         <v>310160</v>
       </c>
-      <c r="L13" s="6" t="s">
-        <v>74</v>
+      <c r="L13" s="7" t="s">
+        <v>77</v>
       </c>
       <c r="M13" s="3">
         <v>0</v>
@@ -1992,10 +2584,10 @@
         <v>-1</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="S13" s="5">
         <v>2</v>
@@ -2007,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="V13" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W13" s="5">
         <v>0</v>
@@ -2015,16 +2607,16 @@
       <c r="Y13" s="5">
         <v>0</v>
       </c>
-      <c r="Z13" s="9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z13" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="3:26">
       <c r="C14" s="3">
         <v>10009</v>
       </c>
-      <c r="D14" s="10" t="s">
-        <v>189</v>
+      <c r="D14" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="E14" s="4">
         <v>2</v>
@@ -2047,8 +2639,8 @@
       <c r="K14" s="4">
         <v>310161</v>
       </c>
-      <c r="L14" s="6" t="s">
-        <v>77</v>
+      <c r="L14" s="7" t="s">
+        <v>82</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -2060,10 +2652,10 @@
         <v>-1</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="S14" s="5">
         <v>2</v>
@@ -2075,7 +2667,7 @@
         <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W14" s="5">
         <v>0</v>
@@ -2083,16 +2675,16 @@
       <c r="Y14" s="5">
         <v>0</v>
       </c>
-      <c r="Z14" s="9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z14" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="3:26">
       <c r="C15" s="3">
         <v>10010</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E15" s="4">
         <v>2</v>
@@ -2115,8 +2707,8 @@
       <c r="K15" s="4">
         <v>310162</v>
       </c>
-      <c r="L15" s="6" t="s">
-        <v>80</v>
+      <c r="L15" s="7" t="s">
+        <v>85</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -2128,10 +2720,10 @@
         <v>-1</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="S15" s="5">
         <v>2</v>
@@ -2143,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="V15" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W15" s="5">
         <v>0</v>
@@ -2151,16 +2743,16 @@
       <c r="Y15" s="5">
         <v>0</v>
       </c>
-      <c r="Z15" s="9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z15" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="3:26">
       <c r="C16" s="3">
         <v>10011</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E16" s="4">
         <v>2</v>
@@ -2183,8 +2775,8 @@
       <c r="K16" s="4">
         <v>310163</v>
       </c>
-      <c r="L16" s="6" t="s">
-        <v>83</v>
+      <c r="L16" s="7" t="s">
+        <v>88</v>
       </c>
       <c r="M16" s="3">
         <v>0</v>
@@ -2196,10 +2788,10 @@
         <v>-1</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="S16" s="5">
         <v>2</v>
@@ -2211,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="V16" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W16" s="5">
         <v>0</v>
@@ -2219,16 +2811,16 @@
       <c r="Y16" s="5">
         <v>0</v>
       </c>
-      <c r="Z16" s="9" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z16" s="8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17" spans="3:26">
       <c r="C17" s="3">
         <v>10012</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="E17" s="4">
         <v>2</v>
@@ -2251,8 +2843,8 @@
       <c r="K17" s="4">
         <v>310164</v>
       </c>
-      <c r="L17" s="6" t="s">
-        <v>86</v>
+      <c r="L17" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="M17" s="3">
         <v>0</v>
@@ -2264,10 +2856,10 @@
         <v>-1</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="S17" s="5">
         <v>2</v>
@@ -2279,7 +2871,7 @@
         <v>0</v>
       </c>
       <c r="V17" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W17" s="5">
         <v>0</v>
@@ -2287,16 +2879,16 @@
       <c r="Y17" s="5">
         <v>0</v>
       </c>
-      <c r="Z17" s="9" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z17" s="8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26">
       <c r="C18" s="3">
         <v>10013</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="E18" s="4">
         <v>2</v>
@@ -2319,8 +2911,8 @@
       <c r="K18" s="4">
         <v>310165</v>
       </c>
-      <c r="L18" s="6" t="s">
-        <v>89</v>
+      <c r="L18" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="M18" s="3">
         <v>0</v>
@@ -2332,10 +2924,10 @@
         <v>-1</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="S18" s="5">
         <v>2</v>
@@ -2347,7 +2939,7 @@
         <v>0</v>
       </c>
       <c r="V18" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W18" s="5">
         <v>0</v>
@@ -2355,16 +2947,16 @@
       <c r="Y18" s="5">
         <v>0</v>
       </c>
-      <c r="Z18" s="9" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z18" s="8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26">
       <c r="C19" s="3">
         <v>10014</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="E19" s="4">
         <v>2</v>
@@ -2387,8 +2979,8 @@
       <c r="K19" s="4">
         <v>320101</v>
       </c>
-      <c r="L19" s="6" t="s">
-        <v>51</v>
+      <c r="L19" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="M19" s="3">
         <v>0</v>
@@ -2400,10 +2992,10 @@
         <v>-1</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="S19" s="5">
         <v>2</v>
@@ -2415,7 +3007,7 @@
         <v>0</v>
       </c>
       <c r="V19" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W19" s="5">
         <v>0</v>
@@ -2423,16 +3015,16 @@
       <c r="Y19" s="5">
         <v>0</v>
       </c>
-      <c r="Z19" s="7" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z19" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="3:26">
       <c r="C20" s="3">
         <v>10015</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="E20" s="4">
         <v>2</v>
@@ -2455,8 +3047,8 @@
       <c r="K20" s="4">
         <v>320102</v>
       </c>
-      <c r="L20" s="6" t="s">
-        <v>57</v>
+      <c r="L20" s="7" t="s">
+        <v>58</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -2468,10 +3060,10 @@
         <v>-1</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S20" s="5">
         <v>2</v>
@@ -2483,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="V20" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W20" s="5">
         <v>0</v>
@@ -2491,16 +3083,16 @@
       <c r="Y20" s="5">
         <v>0</v>
       </c>
-      <c r="Z20" s="7" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z20" s="8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26">
       <c r="C21" s="3">
         <v>10016</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="E21" s="4">
         <v>2</v>
@@ -2523,8 +3115,8 @@
       <c r="K21" s="4">
         <v>320103</v>
       </c>
-      <c r="L21" s="6" t="s">
-        <v>60</v>
+      <c r="L21" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="M21" s="3">
         <v>0</v>
@@ -2536,10 +3128,10 @@
         <v>-1</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S21" s="5">
         <v>2</v>
@@ -2551,7 +3143,7 @@
         <v>0</v>
       </c>
       <c r="V21" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W21" s="5">
         <v>0</v>
@@ -2559,16 +3151,16 @@
       <c r="Y21" s="5">
         <v>0</v>
       </c>
-      <c r="Z21" s="7" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z21" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26">
       <c r="C22" s="3">
         <v>10017</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="E22" s="4">
         <v>2</v>
@@ -2591,8 +3183,8 @@
       <c r="K22" s="4">
         <v>320104</v>
       </c>
-      <c r="L22" s="6" t="s">
-        <v>63</v>
+      <c r="L22" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -2604,10 +3196,10 @@
         <v>-1</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S22" s="5">
         <v>2</v>
@@ -2619,7 +3211,7 @@
         <v>0</v>
       </c>
       <c r="V22" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W22" s="5">
         <v>0</v>
@@ -2627,16 +3219,16 @@
       <c r="Y22" s="5">
         <v>0</v>
       </c>
-      <c r="Z22" s="7" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z22" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26">
       <c r="C23" s="3">
         <v>10018</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="E23" s="4">
         <v>2</v>
@@ -2659,8 +3251,8 @@
       <c r="K23" s="4">
         <v>320105</v>
       </c>
-      <c r="L23" s="6" t="s">
-        <v>65</v>
+      <c r="L23" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="M23" s="3">
         <v>0</v>
@@ -2672,10 +3264,10 @@
         <v>-1</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="S23" s="5">
         <v>2</v>
@@ -2687,7 +3279,7 @@
         <v>0</v>
       </c>
       <c r="V23" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W23" s="5">
         <v>0</v>
@@ -2695,16 +3287,16 @@
       <c r="Y23" s="5">
         <v>0</v>
       </c>
-      <c r="Z23" s="7" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z23" s="8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26">
       <c r="C24" s="3">
         <v>10019</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="E24" s="4">
         <v>2</v>
@@ -2727,8 +3319,8 @@
       <c r="K24" s="4">
         <v>320106</v>
       </c>
-      <c r="L24" s="6" t="s">
-        <v>51</v>
+      <c r="L24" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -2740,10 +3332,10 @@
         <v>-1</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="S24" s="5">
         <v>2</v>
@@ -2755,7 +3347,7 @@
         <v>0</v>
       </c>
       <c r="V24" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W24" s="5">
         <v>0</v>
@@ -2763,16 +3355,16 @@
       <c r="Y24" s="5">
         <v>0</v>
       </c>
-      <c r="Z24" s="7" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z24" s="8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26">
       <c r="C25" s="3">
         <v>10020</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="E25" s="4">
         <v>2</v>
@@ -2795,8 +3387,8 @@
       <c r="K25" s="4">
         <v>320107</v>
       </c>
-      <c r="L25" s="6" t="s">
-        <v>57</v>
+      <c r="L25" s="7" t="s">
+        <v>58</v>
       </c>
       <c r="M25" s="3">
         <v>0</v>
@@ -2808,10 +3400,10 @@
         <v>-1</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q25" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S25" s="5">
         <v>2</v>
@@ -2823,7 +3415,7 @@
         <v>0</v>
       </c>
       <c r="V25" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W25" s="5">
         <v>0</v>
@@ -2831,16 +3423,16 @@
       <c r="Y25" s="5">
         <v>0</v>
       </c>
-      <c r="Z25" s="7" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z25" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26">
       <c r="C26" s="3">
         <v>10021</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="E26" s="4">
         <v>2</v>
@@ -2863,8 +3455,8 @@
       <c r="K26" s="4">
         <v>320161</v>
       </c>
-      <c r="L26" s="6" t="s">
-        <v>60</v>
+      <c r="L26" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="M26" s="3">
         <v>0</v>
@@ -2876,10 +3468,10 @@
         <v>-1</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q26" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S26" s="5">
         <v>2</v>
@@ -2891,7 +3483,7 @@
         <v>0</v>
       </c>
       <c r="V26" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W26" s="5">
         <v>0</v>
@@ -2899,16 +3491,16 @@
       <c r="Y26" s="5">
         <v>0</v>
       </c>
-      <c r="Z26" s="9" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z26" s="8" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26">
       <c r="C27" s="3">
         <v>10022</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="E27" s="4">
         <v>2</v>
@@ -2931,8 +3523,8 @@
       <c r="K27" s="4">
         <v>320162</v>
       </c>
-      <c r="L27" s="6" t="s">
-        <v>63</v>
+      <c r="L27" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="M27" s="3">
         <v>0</v>
@@ -2944,10 +3536,10 @@
         <v>-1</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S27" s="5">
         <v>2</v>
@@ -2959,7 +3551,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W27" s="5">
         <v>0</v>
@@ -2967,16 +3559,16 @@
       <c r="Y27" s="5">
         <v>0</v>
       </c>
-      <c r="Z27" s="9" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z27" s="8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26">
       <c r="C28" s="3">
         <v>10023</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="E28" s="4">
         <v>2</v>
@@ -2999,8 +3591,8 @@
       <c r="K28" s="4">
         <v>320163</v>
       </c>
-      <c r="L28" s="6" t="s">
-        <v>65</v>
+      <c r="L28" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="M28" s="3">
         <v>0</v>
@@ -3012,10 +3604,10 @@
         <v>-1</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q28" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="S28" s="5">
         <v>2</v>
@@ -3027,7 +3619,7 @@
         <v>0</v>
       </c>
       <c r="V28" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W28" s="5">
         <v>0</v>
@@ -3035,16 +3627,16 @@
       <c r="Y28" s="5">
         <v>0</v>
       </c>
-      <c r="Z28" s="9" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z28" s="8" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26">
       <c r="C29" s="3">
         <v>10024</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="E29" s="4">
         <v>2</v>
@@ -3067,8 +3659,8 @@
       <c r="K29" s="4">
         <v>320164</v>
       </c>
-      <c r="L29" s="6" t="s">
-        <v>68</v>
+      <c r="L29" s="7" t="s">
+        <v>70</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -3080,10 +3672,10 @@
         <v>-1</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q29" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="S29" s="5">
         <v>2</v>
@@ -3095,7 +3687,7 @@
         <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W29" s="5">
         <v>0</v>
@@ -3103,16 +3695,16 @@
       <c r="Y29" s="5">
         <v>0</v>
       </c>
-      <c r="Z29" s="9" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z29" s="8" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26">
       <c r="C30" s="3">
         <v>10025</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="E30" s="4">
         <v>2</v>
@@ -3135,8 +3727,8 @@
       <c r="K30" s="4">
         <v>320165</v>
       </c>
-      <c r="L30" s="6" t="s">
-        <v>71</v>
+      <c r="L30" s="7" t="s">
+        <v>74</v>
       </c>
       <c r="M30" s="3">
         <v>0</v>
@@ -3148,11 +3740,11 @@
         <v>-1</v>
       </c>
       <c r="P30" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q30" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="Q30" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="S30" s="5">
         <v>2</v>
       </c>
@@ -3163,7 +3755,7 @@
         <v>0</v>
       </c>
       <c r="V30" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W30" s="5">
         <v>0</v>
@@ -3171,16 +3763,16 @@
       <c r="Y30" s="5">
         <v>0</v>
       </c>
-      <c r="Z30" s="9" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z30" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26">
       <c r="C31" s="3">
         <v>10026</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="E31" s="4">
         <v>2</v>
@@ -3203,8 +3795,8 @@
       <c r="K31" s="4">
         <v>330101</v>
       </c>
-      <c r="L31" s="6" t="s">
-        <v>74</v>
+      <c r="L31" s="7" t="s">
+        <v>77</v>
       </c>
       <c r="M31" s="3">
         <v>0</v>
@@ -3216,10 +3808,10 @@
         <v>-1</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q31" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="S31" s="5">
         <v>2</v>
@@ -3231,7 +3823,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W31" s="5">
         <v>0</v>
@@ -3239,16 +3831,16 @@
       <c r="Y31" s="5">
         <v>0</v>
       </c>
-      <c r="Z31" s="7" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z31" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26">
       <c r="C32" s="3">
         <v>10027</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="E32" s="4">
         <v>2</v>
@@ -3271,8 +3863,8 @@
       <c r="K32" s="4">
         <v>330102</v>
       </c>
-      <c r="L32" s="6" t="s">
-        <v>77</v>
+      <c r="L32" s="7" t="s">
+        <v>82</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -3284,10 +3876,10 @@
         <v>-1</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q32" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="S32" s="5">
         <v>2</v>
@@ -3299,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="V32" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W32" s="5">
         <v>0</v>
@@ -3307,16 +3899,16 @@
       <c r="Y32" s="5">
         <v>0</v>
       </c>
-      <c r="Z32" s="7" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="33" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z32" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="33" spans="3:26">
       <c r="C33" s="3">
         <v>10028</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="E33" s="4">
         <v>2</v>
@@ -3339,8 +3931,8 @@
       <c r="K33" s="4">
         <v>330103</v>
       </c>
-      <c r="L33" s="6" t="s">
-        <v>80</v>
+      <c r="L33" s="7" t="s">
+        <v>85</v>
       </c>
       <c r="M33" s="3">
         <v>0</v>
@@ -3352,10 +3944,10 @@
         <v>-1</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q33" s="3" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="S33" s="5">
         <v>2</v>
@@ -3367,7 +3959,7 @@
         <v>0</v>
       </c>
       <c r="V33" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W33" s="5">
         <v>0</v>
@@ -3375,16 +3967,16 @@
       <c r="Y33" s="5">
         <v>0</v>
       </c>
-      <c r="Z33" s="7" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="34" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z33" s="8" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="34" spans="3:26">
       <c r="C34" s="3">
         <v>10029</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="E34" s="4">
         <v>2</v>
@@ -3407,8 +3999,8 @@
       <c r="K34" s="4">
         <v>330104</v>
       </c>
-      <c r="L34" s="6" t="s">
-        <v>83</v>
+      <c r="L34" s="7" t="s">
+        <v>88</v>
       </c>
       <c r="M34" s="3">
         <v>0</v>
@@ -3420,10 +4012,10 @@
         <v>-1</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q34" s="3" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="S34" s="5">
         <v>2</v>
@@ -3435,7 +4027,7 @@
         <v>0</v>
       </c>
       <c r="V34" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W34" s="5">
         <v>0</v>
@@ -3443,16 +4035,16 @@
       <c r="Y34" s="5">
         <v>0</v>
       </c>
-      <c r="Z34" s="7" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="35" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z34" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="35" spans="3:26">
       <c r="C35" s="3">
         <v>10030</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="E35" s="4">
         <v>2</v>
@@ -3475,8 +4067,8 @@
       <c r="K35" s="4">
         <v>330105</v>
       </c>
-      <c r="L35" s="6" t="s">
-        <v>86</v>
+      <c r="L35" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="M35" s="3">
         <v>0</v>
@@ -3488,10 +4080,10 @@
         <v>-1</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q35" s="3" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="S35" s="5">
         <v>2</v>
@@ -3503,7 +4095,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W35" s="5">
         <v>0</v>
@@ -3511,16 +4103,16 @@
       <c r="Y35" s="5">
         <v>0</v>
       </c>
-      <c r="Z35" s="7" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="36" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z35" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="36" spans="3:26">
       <c r="C36" s="3">
         <v>10031</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="E36" s="4">
         <v>2</v>
@@ -3543,8 +4135,8 @@
       <c r="K36" s="4">
         <v>330106</v>
       </c>
-      <c r="L36" s="6" t="s">
-        <v>89</v>
+      <c r="L36" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="M36" s="3">
         <v>0</v>
@@ -3556,10 +4148,10 @@
         <v>-1</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q36" s="3" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="S36" s="5">
         <v>2</v>
@@ -3571,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="V36" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W36" s="5">
         <v>0</v>
@@ -3579,16 +4171,16 @@
       <c r="Y36" s="5">
         <v>0</v>
       </c>
-      <c r="Z36" s="7" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="37" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z36" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="37" spans="3:26">
       <c r="C37" s="3">
         <v>10032</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="E37" s="4">
         <v>2</v>
@@ -3611,8 +4203,8 @@
       <c r="K37" s="4">
         <v>330107</v>
       </c>
-      <c r="L37" s="6" t="s">
-        <v>71</v>
+      <c r="L37" s="7" t="s">
+        <v>74</v>
       </c>
       <c r="M37" s="3">
         <v>0</v>
@@ -3624,10 +4216,10 @@
         <v>-1</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q37" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="S37" s="5">
         <v>2</v>
@@ -3639,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="V37" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W37" s="5">
         <v>0</v>
@@ -3647,16 +4239,16 @@
       <c r="Y37" s="5">
         <v>0</v>
       </c>
-      <c r="Z37" s="7" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="38" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z37" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="38" spans="3:26">
       <c r="C38" s="3">
         <v>10033</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="E38" s="4">
         <v>2</v>
@@ -3679,8 +4271,8 @@
       <c r="K38" s="4">
         <v>330161</v>
       </c>
-      <c r="L38" s="6" t="s">
-        <v>111</v>
+      <c r="L38" s="7" t="s">
+        <v>129</v>
       </c>
       <c r="M38" s="3">
         <v>0</v>
@@ -3692,10 +4284,10 @@
         <v>-1</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q38" s="3" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="S38" s="5">
         <v>2</v>
@@ -3707,7 +4299,7 @@
         <v>0</v>
       </c>
       <c r="V38" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W38" s="5">
         <v>0</v>
@@ -3715,16 +4307,16 @@
       <c r="Y38" s="5">
         <v>0</v>
       </c>
-      <c r="Z38" s="9" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="39" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z38" s="8" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="39" spans="3:26">
       <c r="C39" s="3">
         <v>10034</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="E39" s="4">
         <v>2</v>
@@ -3747,8 +4339,8 @@
       <c r="K39" s="4">
         <v>330162</v>
       </c>
-      <c r="L39" s="6" t="s">
-        <v>51</v>
+      <c r="L39" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="M39" s="3">
         <v>0</v>
@@ -3760,10 +4352,10 @@
         <v>-1</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q39" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="S39" s="5">
         <v>2</v>
@@ -3775,7 +4367,7 @@
         <v>0</v>
       </c>
       <c r="V39" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W39" s="5">
         <v>0</v>
@@ -3783,16 +4375,16 @@
       <c r="Y39" s="5">
         <v>0</v>
       </c>
-      <c r="Z39" s="9" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="40" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z39" s="8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="40" spans="3:26">
       <c r="C40" s="3">
         <v>10035</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="E40" s="4">
         <v>2</v>
@@ -3815,8 +4407,8 @@
       <c r="K40" s="4">
         <v>330163</v>
       </c>
-      <c r="L40" s="6" t="s">
-        <v>57</v>
+      <c r="L40" s="7" t="s">
+        <v>58</v>
       </c>
       <c r="M40" s="3">
         <v>0</v>
@@ -3828,10 +4420,10 @@
         <v>-1</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q40" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S40" s="5">
         <v>2</v>
@@ -3843,7 +4435,7 @@
         <v>0</v>
       </c>
       <c r="V40" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W40" s="5">
         <v>0</v>
@@ -3851,16 +4443,16 @@
       <c r="Y40" s="5">
         <v>0</v>
       </c>
-      <c r="Z40" s="9" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="41" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z40" s="8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="41" spans="3:26">
       <c r="C41" s="3">
         <v>10036</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="E41" s="4">
         <v>2</v>
@@ -3883,8 +4475,8 @@
       <c r="K41" s="4">
         <v>330164</v>
       </c>
-      <c r="L41" s="6" t="s">
-        <v>60</v>
+      <c r="L41" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="M41" s="3">
         <v>0</v>
@@ -3896,10 +4488,10 @@
         <v>-1</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q41" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S41" s="5">
         <v>2</v>
@@ -3911,7 +4503,7 @@
         <v>0</v>
       </c>
       <c r="V41" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W41" s="5">
         <v>0</v>
@@ -3919,16 +4511,16 @@
       <c r="Y41" s="5">
         <v>0</v>
       </c>
-      <c r="Z41" s="9" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="42" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z41" s="8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="42" spans="3:26">
       <c r="C42" s="3">
         <v>10037</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="E42" s="4">
         <v>2</v>
@@ -3951,8 +4543,8 @@
       <c r="K42" s="4">
         <v>330165</v>
       </c>
-      <c r="L42" s="6" t="s">
-        <v>63</v>
+      <c r="L42" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="M42" s="3">
         <v>0</v>
@@ -3964,10 +4556,10 @@
         <v>-1</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q42" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S42" s="5">
         <v>2</v>
@@ -3979,7 +4571,7 @@
         <v>0</v>
       </c>
       <c r="V42" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W42" s="5">
         <v>0</v>
@@ -3987,16 +4579,16 @@
       <c r="Y42" s="5">
         <v>0</v>
       </c>
-      <c r="Z42" s="9" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="43" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z42" s="8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="43" spans="3:26">
       <c r="C43" s="3">
         <v>10038</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="E43" s="4">
         <v>2</v>
@@ -4019,8 +4611,8 @@
       <c r="K43" s="4">
         <v>340101</v>
       </c>
-      <c r="L43" s="6" t="s">
-        <v>65</v>
+      <c r="L43" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -4032,10 +4624,10 @@
         <v>-1</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q43" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="S43" s="5">
         <v>2</v>
@@ -4047,7 +4639,7 @@
         <v>0</v>
       </c>
       <c r="V43" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W43" s="5">
         <v>0</v>
@@ -4055,16 +4647,16 @@
       <c r="Y43" s="5">
         <v>0</v>
       </c>
-      <c r="Z43" s="7" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="44" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z43" s="8" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="44" spans="3:26">
       <c r="C44" s="3">
         <v>10039</v>
       </c>
-      <c r="D44" s="4" t="s">
-        <v>118</v>
+      <c r="D44" s="3" t="s">
+        <v>141</v>
       </c>
       <c r="E44" s="4">
         <v>2</v>
@@ -4087,8 +4679,8 @@
       <c r="K44" s="4">
         <v>340102</v>
       </c>
-      <c r="L44" s="6" t="s">
-        <v>51</v>
+      <c r="L44" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4100,10 +4692,10 @@
         <v>-1</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q44" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="S44" s="5">
         <v>2</v>
@@ -4115,7 +4707,7 @@
         <v>0</v>
       </c>
       <c r="V44" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W44" s="5">
         <v>0</v>
@@ -4123,16 +4715,16 @@
       <c r="Y44" s="5">
         <v>0</v>
       </c>
-      <c r="Z44" s="7" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="45" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z44" s="8" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="45" spans="3:26">
       <c r="C45" s="3">
         <v>10040</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="E45" s="4">
         <v>2</v>
@@ -4155,8 +4747,8 @@
       <c r="K45" s="4">
         <v>340103</v>
       </c>
-      <c r="L45" s="6" t="s">
-        <v>57</v>
+      <c r="L45" s="7" t="s">
+        <v>58</v>
       </c>
       <c r="M45" s="3">
         <v>0</v>
@@ -4168,10 +4760,10 @@
         <v>-1</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q45" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S45" s="5">
         <v>2</v>
@@ -4183,7 +4775,7 @@
         <v>0</v>
       </c>
       <c r="V45" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W45" s="5">
         <v>0</v>
@@ -4191,16 +4783,16 @@
       <c r="Y45" s="5">
         <v>0</v>
       </c>
-      <c r="Z45" s="7" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="46" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z45" s="8" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="46" spans="3:26">
       <c r="C46" s="3">
         <v>10041</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="E46" s="4">
         <v>2</v>
@@ -4223,8 +4815,8 @@
       <c r="K46" s="4">
         <v>340104</v>
       </c>
-      <c r="L46" s="6" t="s">
-        <v>60</v>
+      <c r="L46" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="M46" s="3">
         <v>0</v>
@@ -4236,10 +4828,10 @@
         <v>-1</v>
       </c>
       <c r="P46" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q46" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S46" s="5">
         <v>2</v>
@@ -4251,7 +4843,7 @@
         <v>0</v>
       </c>
       <c r="V46" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W46" s="5">
         <v>0</v>
@@ -4259,16 +4851,16 @@
       <c r="Y46" s="5">
         <v>0</v>
       </c>
-      <c r="Z46" s="7" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="47" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z46" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="47" spans="3:26">
       <c r="C47" s="3">
         <v>10042</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="E47" s="4">
         <v>2</v>
@@ -4291,8 +4883,8 @@
       <c r="K47" s="4">
         <v>340105</v>
       </c>
-      <c r="L47" s="6" t="s">
-        <v>63</v>
+      <c r="L47" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4304,10 +4896,10 @@
         <v>-1</v>
       </c>
       <c r="P47" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q47" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S47" s="5">
         <v>2</v>
@@ -4319,7 +4911,7 @@
         <v>0</v>
       </c>
       <c r="V47" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W47" s="5">
         <v>0</v>
@@ -4327,16 +4919,16 @@
       <c r="Y47" s="5">
         <v>0</v>
       </c>
-      <c r="Z47" s="7" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="48" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z47" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="48" spans="3:26">
       <c r="C48" s="3">
         <v>10043</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>122</v>
+        <v>147</v>
       </c>
       <c r="E48" s="4">
         <v>2</v>
@@ -4359,8 +4951,8 @@
       <c r="K48" s="4">
         <v>340106</v>
       </c>
-      <c r="L48" s="6" t="s">
-        <v>65</v>
+      <c r="L48" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
@@ -4372,10 +4964,10 @@
         <v>-1</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q48" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="S48" s="5">
         <v>2</v>
@@ -4387,7 +4979,7 @@
         <v>0</v>
       </c>
       <c r="V48" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W48" s="5">
         <v>0</v>
@@ -4395,16 +4987,16 @@
       <c r="Y48" s="5">
         <v>0</v>
       </c>
-      <c r="Z48" s="7" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z48" s="8" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26">
       <c r="C49" s="3">
         <v>10044</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="E49" s="4">
         <v>2</v>
@@ -4427,8 +5019,8 @@
       <c r="K49" s="4">
         <v>340107</v>
       </c>
-      <c r="L49" s="6" t="s">
-        <v>68</v>
+      <c r="L49" s="7" t="s">
+        <v>70</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -4440,10 +5032,10 @@
         <v>-1</v>
       </c>
       <c r="P49" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q49" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="S49" s="5">
         <v>2</v>
@@ -4455,7 +5047,7 @@
         <v>0</v>
       </c>
       <c r="V49" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W49" s="5">
         <v>0</v>
@@ -4463,16 +5055,16 @@
       <c r="Y49" s="5">
         <v>0</v>
       </c>
-      <c r="Z49" s="7" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z49" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26">
       <c r="C50" s="3">
         <v>10045</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="E50" s="4">
         <v>2</v>
@@ -4495,8 +5087,8 @@
       <c r="K50" s="4">
         <v>340161</v>
       </c>
-      <c r="L50" s="6" t="s">
-        <v>71</v>
+      <c r="L50" s="7" t="s">
+        <v>74</v>
       </c>
       <c r="M50" s="3">
         <v>0</v>
@@ -4508,11 +5100,11 @@
         <v>-1</v>
       </c>
       <c r="P50" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q50" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="Q50" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="S50" s="5">
         <v>2</v>
       </c>
@@ -4523,7 +5115,7 @@
         <v>0</v>
       </c>
       <c r="V50" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W50" s="5">
         <v>0</v>
@@ -4531,16 +5123,16 @@
       <c r="Y50" s="5">
         <v>0</v>
       </c>
-      <c r="Z50" s="9" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z50" s="8" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26">
       <c r="C51" s="3">
         <v>10046</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="E51" s="4">
         <v>2</v>
@@ -4563,8 +5155,8 @@
       <c r="K51" s="4">
         <v>340162</v>
       </c>
-      <c r="L51" s="6" t="s">
-        <v>74</v>
+      <c r="L51" s="7" t="s">
+        <v>77</v>
       </c>
       <c r="M51" s="3">
         <v>0</v>
@@ -4576,10 +5168,10 @@
         <v>-1</v>
       </c>
       <c r="P51" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q51" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="S51" s="5">
         <v>2</v>
@@ -4591,7 +5183,7 @@
         <v>0</v>
       </c>
       <c r="V51" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W51" s="5">
         <v>0</v>
@@ -4599,16 +5191,16 @@
       <c r="Y51" s="5">
         <v>0</v>
       </c>
-      <c r="Z51" s="9" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z51" s="8" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26">
       <c r="C52" s="3">
         <v>10047</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="E52" s="4">
         <v>2</v>
@@ -4631,8 +5223,8 @@
       <c r="K52" s="4">
         <v>340163</v>
       </c>
-      <c r="L52" s="6" t="s">
-        <v>77</v>
+      <c r="L52" s="7" t="s">
+        <v>82</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -4644,10 +5236,10 @@
         <v>-1</v>
       </c>
       <c r="P52" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q52" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="S52" s="5">
         <v>2</v>
@@ -4659,7 +5251,7 @@
         <v>0</v>
       </c>
       <c r="V52" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W52" s="5">
         <v>0</v>
@@ -4667,16 +5259,16 @@
       <c r="Y52" s="5">
         <v>0</v>
       </c>
-      <c r="Z52" s="9" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z52" s="8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26">
       <c r="C53" s="3">
         <v>10048</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="E53" s="4">
         <v>2</v>
@@ -4699,8 +5291,8 @@
       <c r="K53" s="4">
         <v>340164</v>
       </c>
-      <c r="L53" s="6" t="s">
-        <v>80</v>
+      <c r="L53" s="7" t="s">
+        <v>85</v>
       </c>
       <c r="M53" s="3">
         <v>0</v>
@@ -4712,10 +5304,10 @@
         <v>-1</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="S53" s="5">
         <v>2</v>
@@ -4727,7 +5319,7 @@
         <v>0</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W53" s="5">
         <v>0</v>
@@ -4735,16 +5327,16 @@
       <c r="Y53" s="5">
         <v>0</v>
       </c>
-      <c r="Z53" s="9" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z53" s="8" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26">
       <c r="C54" s="3">
         <v>10049</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>128</v>
+        <v>156</v>
       </c>
       <c r="E54" s="4">
         <v>2</v>
@@ -4767,8 +5359,8 @@
       <c r="K54" s="4">
         <v>340165</v>
       </c>
-      <c r="L54" s="6" t="s">
-        <v>83</v>
+      <c r="L54" s="7" t="s">
+        <v>88</v>
       </c>
       <c r="M54" s="3">
         <v>0</v>
@@ -4780,10 +5372,10 @@
         <v>-1</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q54" s="3" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="S54" s="5">
         <v>2</v>
@@ -4795,7 +5387,7 @@
         <v>0</v>
       </c>
       <c r="V54" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W54" s="5">
         <v>0</v>
@@ -4803,16 +5395,16 @@
       <c r="Y54" s="5">
         <v>0</v>
       </c>
-      <c r="Z54" s="9" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z54" s="8" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26">
       <c r="C55" s="3">
         <v>10050</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="E55" s="4">
         <v>2</v>
@@ -4835,8 +5427,8 @@
       <c r="K55" s="4">
         <v>350101</v>
       </c>
-      <c r="L55" s="6" t="s">
-        <v>86</v>
+      <c r="L55" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="M55" s="3">
         <v>0</v>
@@ -4848,10 +5440,10 @@
         <v>-1</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q55" s="3" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="S55" s="5">
         <v>2</v>
@@ -4863,7 +5455,7 @@
         <v>0</v>
       </c>
       <c r="V55" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W55" s="5">
         <v>0</v>
@@ -4871,16 +5463,16 @@
       <c r="Y55" s="5">
         <v>0</v>
       </c>
-      <c r="Z55" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z55" s="8" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="56" spans="3:26">
       <c r="C56" s="3">
         <v>10051</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="E56" s="4">
         <v>2</v>
@@ -4903,8 +5495,8 @@
       <c r="K56" s="4">
         <v>350102</v>
       </c>
-      <c r="L56" s="6" t="s">
-        <v>89</v>
+      <c r="L56" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="M56" s="3">
         <v>0</v>
@@ -4916,10 +5508,10 @@
         <v>-1</v>
       </c>
       <c r="P56" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q56" s="3" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="S56" s="5">
         <v>2</v>
@@ -4931,7 +5523,7 @@
         <v>0</v>
       </c>
       <c r="V56" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W56" s="5">
         <v>0</v>
@@ -4939,16 +5531,16 @@
       <c r="Y56" s="5">
         <v>0</v>
       </c>
-      <c r="Z56" s="7" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z56" s="8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="57" spans="3:26">
       <c r="C57" s="3">
         <v>10052</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>131</v>
+        <v>161</v>
       </c>
       <c r="E57" s="4">
         <v>2</v>
@@ -4971,8 +5563,8 @@
       <c r="K57" s="4">
         <v>350103</v>
       </c>
-      <c r="L57" s="6" t="s">
-        <v>71</v>
+      <c r="L57" s="7" t="s">
+        <v>74</v>
       </c>
       <c r="M57" s="3">
         <v>0</v>
@@ -4984,10 +5576,10 @@
         <v>-1</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q57" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="S57" s="5">
         <v>2</v>
@@ -4999,7 +5591,7 @@
         <v>0</v>
       </c>
       <c r="V57" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W57" s="5">
         <v>0</v>
@@ -5007,16 +5599,16 @@
       <c r="Y57" s="5">
         <v>0</v>
       </c>
-      <c r="Z57" s="7" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z57" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26">
       <c r="C58" s="3">
         <v>10053</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="E58" s="4">
         <v>2</v>
@@ -5039,8 +5631,8 @@
       <c r="K58" s="4">
         <v>350104</v>
       </c>
-      <c r="L58" s="6" t="s">
-        <v>111</v>
+      <c r="L58" s="7" t="s">
+        <v>129</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -5052,10 +5644,10 @@
         <v>-1</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q58" s="3" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="S58" s="5">
         <v>2</v>
@@ -5067,7 +5659,7 @@
         <v>0</v>
       </c>
       <c r="V58" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W58" s="5">
         <v>0</v>
@@ -5075,16 +5667,16 @@
       <c r="Y58" s="5">
         <v>0</v>
       </c>
-      <c r="Z58" s="7" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z58" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26">
       <c r="C59" s="3">
         <v>10054</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="E59" s="4">
         <v>2</v>
@@ -5107,8 +5699,8 @@
       <c r="K59" s="4">
         <v>350105</v>
       </c>
-      <c r="L59" s="6" t="s">
-        <v>51</v>
+      <c r="L59" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="M59" s="3">
         <v>0</v>
@@ -5120,10 +5712,10 @@
         <v>-1</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q59" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="S59" s="5">
         <v>2</v>
@@ -5135,7 +5727,7 @@
         <v>0</v>
       </c>
       <c r="V59" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W59" s="5">
         <v>0</v>
@@ -5143,16 +5735,16 @@
       <c r="Y59" s="5">
         <v>0</v>
       </c>
-      <c r="Z59" s="7" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z59" s="8" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26">
       <c r="C60" s="3">
         <v>10055</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="E60" s="4">
         <v>2</v>
@@ -5175,8 +5767,8 @@
       <c r="K60" s="4">
         <v>350106</v>
       </c>
-      <c r="L60" s="6" t="s">
-        <v>57</v>
+      <c r="L60" s="7" t="s">
+        <v>58</v>
       </c>
       <c r="M60" s="3">
         <v>0</v>
@@ -5188,10 +5780,10 @@
         <v>-1</v>
       </c>
       <c r="P60" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q60" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S60" s="5">
         <v>2</v>
@@ -5203,7 +5795,7 @@
         <v>0</v>
       </c>
       <c r="V60" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W60" s="5">
         <v>0</v>
@@ -5211,16 +5803,16 @@
       <c r="Y60" s="5">
         <v>0</v>
       </c>
-      <c r="Z60" s="7" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z60" s="8" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26">
       <c r="C61" s="3">
         <v>10056</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="E61" s="4">
         <v>2</v>
@@ -5243,8 +5835,8 @@
       <c r="K61" s="4">
         <v>350161</v>
       </c>
-      <c r="L61" s="6" t="s">
-        <v>60</v>
+      <c r="L61" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
@@ -5256,10 +5848,10 @@
         <v>-1</v>
       </c>
       <c r="P61" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q61" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S61" s="5">
         <v>2</v>
@@ -5271,7 +5863,7 @@
         <v>0</v>
       </c>
       <c r="V61" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W61" s="5">
         <v>0</v>
@@ -5279,16 +5871,16 @@
       <c r="Y61" s="5">
         <v>0</v>
       </c>
-      <c r="Z61" s="9" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z61" s="8" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26">
       <c r="C62" s="3">
         <v>10057</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>136</v>
+        <v>167</v>
       </c>
       <c r="E62" s="4">
         <v>2</v>
@@ -5311,8 +5903,8 @@
       <c r="K62" s="4">
         <v>350162</v>
       </c>
-      <c r="L62" s="6" t="s">
-        <v>63</v>
+      <c r="L62" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -5324,10 +5916,10 @@
         <v>-1</v>
       </c>
       <c r="P62" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q62" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S62" s="5">
         <v>2</v>
@@ -5339,7 +5931,7 @@
         <v>0</v>
       </c>
       <c r="V62" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W62" s="5">
         <v>0</v>
@@ -5347,16 +5939,16 @@
       <c r="Y62" s="5">
         <v>0</v>
       </c>
-      <c r="Z62" s="9" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z62" s="8" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26">
       <c r="C63" s="3">
         <v>10058</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="E63" s="4">
         <v>2</v>
@@ -5379,8 +5971,8 @@
       <c r="K63" s="4">
         <v>350163</v>
       </c>
-      <c r="L63" s="6" t="s">
-        <v>65</v>
+      <c r="L63" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="M63" s="3">
         <v>0</v>
@@ -5392,10 +5984,10 @@
         <v>-1</v>
       </c>
       <c r="P63" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q63" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="S63" s="5">
         <v>2</v>
@@ -5407,7 +5999,7 @@
         <v>0</v>
       </c>
       <c r="V63" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W63" s="5">
         <v>0</v>
@@ -5415,16 +6007,16 @@
       <c r="Y63" s="5">
         <v>0</v>
       </c>
-      <c r="Z63" s="9" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z63" s="8" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26">
       <c r="C64" s="3">
         <v>10059</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>138</v>
+        <v>171</v>
       </c>
       <c r="E64" s="4">
         <v>2</v>
@@ -5447,8 +6039,8 @@
       <c r="K64" s="4">
         <v>350164</v>
       </c>
-      <c r="L64" s="6" t="s">
-        <v>80</v>
+      <c r="L64" s="7" t="s">
+        <v>85</v>
       </c>
       <c r="M64" s="3">
         <v>0</v>
@@ -5460,10 +6052,10 @@
         <v>-1</v>
       </c>
       <c r="P64" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q64" s="3" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="S64" s="5">
         <v>2</v>
@@ -5475,7 +6067,7 @@
         <v>0</v>
       </c>
       <c r="V64" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W64" s="5">
         <v>0</v>
@@ -5483,16 +6075,16 @@
       <c r="Y64" s="5">
         <v>0</v>
       </c>
-      <c r="Z64" s="9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="65" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z64" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="65" spans="3:26">
       <c r="C65" s="3">
         <v>10060</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>139</v>
+        <v>172</v>
       </c>
       <c r="E65" s="4">
         <v>2</v>
@@ -5515,8 +6107,8 @@
       <c r="K65" s="4">
         <v>350165</v>
       </c>
-      <c r="L65" s="6" t="s">
-        <v>83</v>
+      <c r="L65" s="7" t="s">
+        <v>88</v>
       </c>
       <c r="M65" s="3">
         <v>0</v>
@@ -5528,10 +6120,10 @@
         <v>-1</v>
       </c>
       <c r="P65" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Q65" s="3" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="S65" s="5">
         <v>2</v>
@@ -5543,7 +6135,7 @@
         <v>0</v>
       </c>
       <c r="V65" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W65" s="5">
         <v>0</v>
@@ -5551,16 +6143,16 @@
       <c r="Y65" s="5">
         <v>0</v>
       </c>
-      <c r="Z65" s="9" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="66" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z65" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="66" spans="3:26">
       <c r="C66" s="3">
         <v>20001</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>140</v>
+        <v>174</v>
       </c>
       <c r="E66" s="3">
         <v>1</v>
@@ -5583,8 +6175,8 @@
       <c r="K66" s="3">
         <v>400001</v>
       </c>
-      <c r="L66" s="6" t="s">
-        <v>141</v>
+      <c r="L66" s="7" t="s">
+        <v>175</v>
       </c>
       <c r="M66" s="5">
         <v>0</v>
@@ -5593,10 +6185,10 @@
         <v>0</v>
       </c>
       <c r="P66" s="1" t="s">
-        <v>142</v>
+        <v>176</v>
       </c>
       <c r="Q66" s="3" t="s">
-        <v>143</v>
+        <v>177</v>
       </c>
       <c r="S66" s="5">
         <v>2</v>
@@ -5608,7 +6200,7 @@
         <v>0</v>
       </c>
       <c r="V66" s="1" t="s">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="W66" s="1">
         <v>0</v>
@@ -5616,16 +6208,16 @@
       <c r="Y66" s="1">
         <v>0</v>
       </c>
-      <c r="Z66" s="7" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="67" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z66" s="8" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="67" spans="3:26">
       <c r="C67" s="3">
         <v>20002</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>145</v>
+        <v>180</v>
       </c>
       <c r="E67" s="3">
         <v>1</v>
@@ -5648,8 +6240,8 @@
       <c r="K67" s="3">
         <v>400002</v>
       </c>
-      <c r="L67" s="6" t="s">
-        <v>71</v>
+      <c r="L67" s="7" t="s">
+        <v>74</v>
       </c>
       <c r="M67" s="5">
         <v>0</v>
@@ -5658,10 +6250,10 @@
         <v>0</v>
       </c>
       <c r="P67" s="1" t="s">
-        <v>142</v>
+        <v>176</v>
       </c>
       <c r="Q67" s="3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="S67" s="5">
         <v>2</v>
@@ -5673,7 +6265,7 @@
         <v>0</v>
       </c>
       <c r="V67" s="1" t="s">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="W67" s="1">
         <v>0</v>
@@ -5681,16 +6273,16 @@
       <c r="Y67" s="1">
         <v>0</v>
       </c>
-      <c r="Z67" s="7" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="68" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z67" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="68" spans="3:26">
       <c r="C68" s="3">
         <v>20003</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>146</v>
+        <v>181</v>
       </c>
       <c r="E68" s="3">
         <v>1</v>
@@ -5713,8 +6305,8 @@
       <c r="K68" s="3">
         <v>400003</v>
       </c>
-      <c r="L68" s="6" t="s">
-        <v>111</v>
+      <c r="L68" s="7" t="s">
+        <v>129</v>
       </c>
       <c r="M68" s="5">
         <v>0</v>
@@ -5723,10 +6315,10 @@
         <v>0</v>
       </c>
       <c r="P68" s="1" t="s">
-        <v>142</v>
+        <v>176</v>
       </c>
       <c r="Q68" s="3" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="S68" s="5">
         <v>2</v>
@@ -5738,7 +6330,7 @@
         <v>0</v>
       </c>
       <c r="V68" s="1" t="s">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="W68" s="1">
         <v>0</v>
@@ -5746,16 +6338,16 @@
       <c r="Y68" s="1">
         <v>0</v>
       </c>
-      <c r="Z68" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="69" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z68" s="8" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="69" spans="3:26">
       <c r="C69" s="3">
         <v>20004</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>147</v>
+        <v>182</v>
       </c>
       <c r="E69" s="3">
         <v>1</v>
@@ -5778,8 +6370,8 @@
       <c r="K69" s="3">
         <v>400004</v>
       </c>
-      <c r="L69" s="6" t="s">
-        <v>60</v>
+      <c r="L69" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="M69" s="5">
         <v>0</v>
@@ -5788,10 +6380,10 @@
         <v>0</v>
       </c>
       <c r="P69" s="1" t="s">
-        <v>142</v>
+        <v>176</v>
       </c>
       <c r="Q69" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S69" s="5">
         <v>2</v>
@@ -5803,7 +6395,7 @@
         <v>0</v>
       </c>
       <c r="V69" s="1" t="s">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="W69" s="1">
         <v>0</v>
@@ -5811,16 +6403,16 @@
       <c r="Y69" s="1">
         <v>0</v>
       </c>
-      <c r="Z69" s="7" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="70" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z69" s="8" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="70" spans="3:26">
       <c r="C70" s="3">
         <v>20005</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>148</v>
+        <v>183</v>
       </c>
       <c r="E70" s="3">
         <v>1</v>
@@ -5843,8 +6435,8 @@
       <c r="K70" s="3">
         <v>400005</v>
       </c>
-      <c r="L70" s="6" t="s">
-        <v>63</v>
+      <c r="L70" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="M70" s="5">
         <v>0</v>
@@ -5853,10 +6445,10 @@
         <v>0</v>
       </c>
       <c r="P70" s="1" t="s">
-        <v>142</v>
+        <v>176</v>
       </c>
       <c r="Q70" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S70" s="5">
         <v>2</v>
@@ -5868,7 +6460,7 @@
         <v>0</v>
       </c>
       <c r="V70" s="1" t="s">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="W70" s="1">
         <v>0</v>
@@ -5876,16 +6468,16 @@
       <c r="Y70" s="1">
         <v>0</v>
       </c>
-      <c r="Z70" s="7" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="71" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z70" s="8" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="71" spans="3:26">
       <c r="C71" s="3">
         <v>20006</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>149</v>
+        <v>184</v>
       </c>
       <c r="E71" s="3">
         <v>1</v>
@@ -5908,8 +6500,8 @@
       <c r="K71" s="3">
         <v>400006</v>
       </c>
-      <c r="L71" s="6" t="s">
-        <v>86</v>
+      <c r="L71" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="M71" s="5">
         <v>0</v>
@@ -5918,10 +6510,10 @@
         <v>0</v>
       </c>
       <c r="P71" s="1" t="s">
-        <v>142</v>
+        <v>176</v>
       </c>
       <c r="Q71" s="3" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="S71" s="5">
         <v>2</v>
@@ -5933,7 +6525,7 @@
         <v>0</v>
       </c>
       <c r="V71" s="1" t="s">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="W71" s="1">
         <v>0</v>
@@ -5941,16 +6533,16 @@
       <c r="Y71" s="1">
         <v>0</v>
       </c>
-      <c r="Z71" s="7" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="72" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z71" s="8" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="72" spans="3:26">
       <c r="C72" s="3">
         <v>20007</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>150</v>
+        <v>186</v>
       </c>
       <c r="E72" s="3">
         <v>1</v>
@@ -5973,8 +6565,8 @@
       <c r="K72" s="3">
         <v>400007</v>
       </c>
-      <c r="L72" s="6" t="s">
-        <v>151</v>
+      <c r="L72" s="7" t="s">
+        <v>187</v>
       </c>
       <c r="M72" s="5">
         <v>0</v>
@@ -5983,10 +6575,10 @@
         <v>0</v>
       </c>
       <c r="P72" s="1" t="s">
-        <v>142</v>
+        <v>176</v>
       </c>
       <c r="Q72" s="3" t="s">
-        <v>152</v>
+        <v>188</v>
       </c>
       <c r="S72" s="5">
         <v>2</v>
@@ -5998,7 +6590,7 @@
         <v>0</v>
       </c>
       <c r="V72" s="1" t="s">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="W72" s="1">
         <v>0</v>
@@ -6006,16 +6598,16 @@
       <c r="Y72" s="1">
         <v>0</v>
       </c>
-      <c r="Z72" s="7" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="73" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z72" s="8" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="73" spans="3:26">
       <c r="C73" s="3">
         <v>20008</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>153</v>
+        <v>189</v>
       </c>
       <c r="E73" s="3">
         <v>1</v>
@@ -6038,8 +6630,8 @@
       <c r="K73" s="3">
         <v>400008</v>
       </c>
-      <c r="L73" s="6" t="s">
-        <v>57</v>
+      <c r="L73" s="7" t="s">
+        <v>58</v>
       </c>
       <c r="M73" s="5">
         <v>0</v>
@@ -6048,10 +6640,10 @@
         <v>0</v>
       </c>
       <c r="P73" s="1" t="s">
-        <v>142</v>
+        <v>176</v>
       </c>
       <c r="Q73" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="S73" s="5">
         <v>2</v>
@@ -6063,7 +6655,7 @@
         <v>0</v>
       </c>
       <c r="V73" s="1" t="s">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="W73" s="1">
         <v>0</v>
@@ -6071,119 +6663,119 @@
       <c r="Y73" s="1">
         <v>0</v>
       </c>
-      <c r="Z73" s="7" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="74" spans="3:26" x14ac:dyDescent="0.3">
+      <c r="Z73" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="74" spans="4:4">
       <c r="D74" s="4"/>
     </row>
-    <row r="75" spans="3:26" x14ac:dyDescent="0.3">
+    <row r="75" spans="4:4">
       <c r="D75" s="4"/>
     </row>
-    <row r="76" spans="3:26" x14ac:dyDescent="0.3">
+    <row r="76" spans="4:4">
       <c r="D76" s="4"/>
     </row>
-    <row r="77" spans="3:26" x14ac:dyDescent="0.3">
+    <row r="77" spans="4:4">
       <c r="D77" s="4"/>
     </row>
-    <row r="78" spans="3:26" x14ac:dyDescent="0.3">
+    <row r="78" spans="4:4">
       <c r="D78" s="4"/>
     </row>
-    <row r="79" spans="3:26" x14ac:dyDescent="0.3">
+    <row r="79" spans="4:4">
       <c r="D79" s="4"/>
     </row>
-    <row r="80" spans="3:26" x14ac:dyDescent="0.3">
+    <row r="80" spans="4:4">
       <c r="D80" s="4"/>
     </row>
-    <row r="81" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="4:4">
       <c r="D81" s="4"/>
     </row>
-    <row r="82" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="4:4">
       <c r="D82" s="4"/>
     </row>
-    <row r="83" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="4:4">
       <c r="D83" s="4"/>
     </row>
-    <row r="84" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="4:4">
       <c r="D84" s="4"/>
     </row>
-    <row r="85" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="4:4">
       <c r="D85" s="4"/>
     </row>
-    <row r="86" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="4:4">
       <c r="D86" s="4"/>
     </row>
-    <row r="87" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="4:4">
       <c r="D87" s="4"/>
     </row>
-    <row r="88" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="4:4">
       <c r="D88" s="4"/>
     </row>
-    <row r="89" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="4:4">
       <c r="D89" s="4"/>
     </row>
-    <row r="90" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="4:4">
       <c r="D90" s="4"/>
     </row>
-    <row r="91" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="4:4">
       <c r="D91" s="4"/>
     </row>
-    <row r="92" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="4:4">
       <c r="D92" s="4"/>
     </row>
-    <row r="93" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="4:4">
       <c r="D93" s="4"/>
     </row>
-    <row r="94" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="4:4">
       <c r="D94" s="4"/>
     </row>
-    <row r="95" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="4:4">
       <c r="D95" s="4"/>
     </row>
-    <row r="96" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="4:4">
       <c r="D96" s="4"/>
     </row>
-    <row r="97" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="4:4">
       <c r="D97" s="4"/>
     </row>
-    <row r="98" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="4:4">
       <c r="D98" s="4"/>
     </row>
-    <row r="99" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="4:4">
       <c r="D99" s="4"/>
     </row>
-    <row r="100" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="4:4">
       <c r="D100" s="4"/>
     </row>
-    <row r="101" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="4:4">
       <c r="D101" s="4"/>
     </row>
-    <row r="102" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="4:4">
       <c r="D102" s="4"/>
     </row>
-    <row r="103" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="4:4">
       <c r="D103" s="4"/>
     </row>
-    <row r="104" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="4:4">
       <c r="D104" s="4"/>
     </row>
-    <row r="105" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="4:4">
       <c r="D105" s="4"/>
     </row>
-    <row r="106" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="4:4">
       <c r="D106" s="4"/>
     </row>
-    <row r="107" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="4:4">
       <c r="D107" s="4"/>
     </row>
-    <row r="108" spans="4:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="4:4">
       <c r="D108" s="4"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Unity/Assets/Config/Excel/JingLingConfig.xlsx
+++ b/Unity/Assets/Config/Excel/JingLingConfig.xlsx
@@ -1,39 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitMengJing\Unity\Assets\Config\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FB02C76-2E11-476A-AAB4-56B6A5F21E31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12795"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JingLingProto" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Admin</author>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="G3" authorId="0">
+    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -57,7 +50,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0">
+    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -82,7 +75,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O3" authorId="1">
+    <comment ref="O3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -105,7 +98,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W3" authorId="1">
+    <comment ref="W3" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -124,7 +117,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E4" authorId="0">
+    <comment ref="E4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -147,7 +140,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F4" authorId="0">
+    <comment ref="F4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -290,476 +283,473 @@
     <t>Lv</t>
   </si>
   <si>
+    <t>Des</t>
+  </si>
+  <si>
+    <t>size</t>
+  </si>
+  <si>
+    <t>MoveX</t>
+  </si>
+  <si>
+    <t>MoveY</t>
+  </si>
+  <si>
+    <t>GetDes</t>
+  </si>
+  <si>
+    <t>FunctionType</t>
+  </si>
+  <si>
+    <t>FunctionValue</t>
+  </si>
+  <si>
+    <t>AutoPick</t>
+  </si>
+  <si>
+    <t>ModelShowPosi</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>int[]</t>
+  </si>
+  <si>
+    <t>double</t>
+  </si>
+  <si>
+    <t>史莱姆</t>
+  </si>
+  <si>
+    <t>100403;50</t>
+  </si>
+  <si>
+    <t>怪物级</t>
+  </si>
+  <si>
+    <t>攻击提升50点</t>
+  </si>
+  <si>
+    <t>击败怪物有一定怪物激活</t>
+  </si>
+  <si>
+    <t>0,110,400,60,0</t>
+  </si>
+  <si>
+    <t>森灵小妖</t>
+  </si>
+  <si>
+    <t>100203;500</t>
+  </si>
+  <si>
+    <t>生命上限+500点</t>
+  </si>
+  <si>
+    <t>森灵小猪</t>
+  </si>
+  <si>
+    <t>202103;0.01</t>
+  </si>
+  <si>
+    <t>重击概率+1%</t>
+  </si>
+  <si>
+    <t>绿林熊妖</t>
+  </si>
+  <si>
+    <t>100202;0.01</t>
+  </si>
+  <si>
+    <t>生命上限+1%</t>
+  </si>
+  <si>
+    <t>119303;50</t>
+  </si>
+  <si>
+    <t>命中等级提升50点</t>
+  </si>
+  <si>
+    <t>森林蜘蛛</t>
+  </si>
+  <si>
+    <t>200903;0.05</t>
+  </si>
+  <si>
+    <t>伤害加成+5%</t>
+  </si>
+  <si>
+    <t>森林熊</t>
+  </si>
+  <si>
+    <t>200303;0.01</t>
+  </si>
+  <si>
+    <t>闪避概率+1%</t>
+  </si>
+  <si>
+    <t>獠牙猪妖</t>
+  </si>
+  <si>
+    <t>120703;100</t>
+  </si>
+  <si>
+    <t>领主级</t>
+  </si>
+  <si>
+    <t>法术强度提升100点</t>
+  </si>
+  <si>
+    <t>100403;100</t>
+  </si>
+  <si>
+    <t>攻击提升100点</t>
+  </si>
+  <si>
+    <t>恶魔猪王</t>
+  </si>
+  <si>
+    <t>100203;1000</t>
+  </si>
+  <si>
+    <t>生命上限+1000点</t>
+  </si>
+  <si>
+    <t>邪能之主</t>
+  </si>
+  <si>
+    <t>120603;100</t>
+  </si>
+  <si>
+    <t>攻击强度提升100点</t>
+  </si>
+  <si>
+    <t>森灵之树</t>
+  </si>
+  <si>
+    <t>200403;0.01</t>
+  </si>
+  <si>
+    <t>抗暴率+1%</t>
+  </si>
+  <si>
+    <t>漠灵风暴之王</t>
+  </si>
+  <si>
+    <t>100603;100</t>
+  </si>
+  <si>
+    <t>物防提升100点</t>
+  </si>
+  <si>
+    <t>绿洲龟</t>
+  </si>
+  <si>
+    <t>绿洲恐龙</t>
+  </si>
+  <si>
+    <t>绿洲蜗牛</t>
+  </si>
+  <si>
+    <t>荒漠鹰</t>
+  </si>
+  <si>
+    <t>迅捷恐龙</t>
+  </si>
+  <si>
+    <t>遗迹火焰</t>
+  </si>
+  <si>
+    <t>遗迹弓手</t>
+  </si>
+  <si>
+    <t>荒漠巨蟹</t>
+  </si>
+  <si>
+    <t>沙漠之鳄</t>
+  </si>
+  <si>
+    <t>绿洲龟王</t>
+  </si>
+  <si>
+    <t>遗迹守护者</t>
+  </si>
+  <si>
+    <t>遗迹之王</t>
+  </si>
+  <si>
+    <t>螃蟹护卫</t>
+  </si>
+  <si>
+    <t>猛虎</t>
+  </si>
+  <si>
+    <t>丛林虎</t>
+  </si>
+  <si>
+    <t>兽人护卫</t>
+  </si>
+  <si>
+    <t>地精守卫</t>
+  </si>
+  <si>
+    <t>兽人骑兵</t>
+  </si>
+  <si>
+    <t>岩石护卫</t>
+  </si>
+  <si>
+    <t>蛤蟆守护者</t>
+  </si>
+  <si>
+    <t>200103;0.01</t>
+  </si>
+  <si>
+    <t>暴击概率+1%</t>
+  </si>
+  <si>
+    <t>森林之王</t>
+  </si>
+  <si>
+    <t>地下巨鳄</t>
+  </si>
+  <si>
+    <t>地下兽人祭祀</t>
+  </si>
+  <si>
+    <t>地灵牛头之王</t>
+  </si>
+  <si>
+    <t>冰灵蜘蛛</t>
+  </si>
+  <si>
+    <t>雪狼</t>
+  </si>
+  <si>
+    <t>冰灵山羊</t>
+  </si>
+  <si>
+    <t>冰封蜗牛</t>
+  </si>
+  <si>
+    <t>冰块士兵</t>
+  </si>
+  <si>
+    <t>冰灵</t>
+  </si>
+  <si>
+    <t>冰块护卫</t>
+  </si>
+  <si>
+    <t>冰封蛛王</t>
+  </si>
+  <si>
+    <t>冰灵之王</t>
+  </si>
+  <si>
+    <t>冰岩巨人</t>
+  </si>
+  <si>
+    <t>冰雪之主</t>
+  </si>
+  <si>
+    <t>冰封巨龙</t>
+  </si>
+  <si>
+    <t>精灵蝴蝶</t>
+  </si>
+  <si>
+    <t>影月护卫</t>
+  </si>
+  <si>
+    <t>影月弓手</t>
+  </si>
+  <si>
+    <t>影月骑兵</t>
+  </si>
+  <si>
+    <t>暗灵士兵</t>
+  </si>
+  <si>
+    <t>熔岩护卫</t>
+  </si>
+  <si>
+    <t>影月碟王</t>
+  </si>
+  <si>
+    <t>影月女王</t>
+  </si>
+  <si>
+    <t>暗灵守卫者</t>
+  </si>
+  <si>
+    <t>暗灵狮鹫</t>
+  </si>
+  <si>
+    <t>暗灵之主</t>
+  </si>
+  <si>
+    <t>邪恶鳄鱼</t>
+  </si>
+  <si>
+    <t>100403;30</t>
+  </si>
+  <si>
+    <t>野外奇遇</t>
+  </si>
+  <si>
+    <t>攻击提升30点</t>
+  </si>
+  <si>
+    <t>野外有一定几率遇到,可以抓捕它哟！</t>
+  </si>
+  <si>
+    <t>火焰松鼠</t>
+  </si>
+  <si>
+    <t>白羽蝴蝶</t>
+  </si>
+  <si>
+    <t>冰雪人</t>
+  </si>
+  <si>
+    <t>火焰之树</t>
+  </si>
+  <si>
+    <t>天空守卫</t>
+  </si>
+  <si>
+    <t>熔岩之魔</t>
+  </si>
+  <si>
+    <t>200903;0.01</t>
+  </si>
+  <si>
+    <t>伤害加成+1%</t>
+  </si>
+  <si>
+    <t>天狼蜘蛛</t>
+  </si>
+  <si>
     <t>ProDes</t>
-  </si>
-  <si>
-    <t>Des</t>
-  </si>
-  <si>
-    <t>size</t>
-  </si>
-  <si>
-    <t>MoveX</t>
-  </si>
-  <si>
-    <t>MoveY</t>
-  </si>
-  <si>
-    <t>GetDes</t>
-  </si>
-  <si>
-    <t>FunctionType</t>
-  </si>
-  <si>
-    <t>FunctionValue</t>
-  </si>
-  <si>
-    <t>AutoPick</t>
-  </si>
-  <si>
-    <t>ModelShowPosi</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>int[]</t>
-  </si>
-  <si>
-    <t>double</t>
-  </si>
-  <si>
-    <t>软泥怪</t>
-  </si>
-  <si>
-    <t>100403;50</t>
-  </si>
-  <si>
-    <t>怪物级</t>
-  </si>
-  <si>
-    <t>攻击提升50点</t>
-  </si>
-  <si>
-    <t>击败怪物有一定怪物激活</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,110,250,60,0</t>
   </si>
   <si>
     <t>0,60,250,35,0</t>
   </si>
   <si>
-    <t>森灵小妖</t>
-  </si>
-  <si>
-    <t>100203;500</t>
-  </si>
-  <si>
-    <t>生命上限+500点</t>
-  </si>
-  <si>
-    <t>森灵小猪</t>
-  </si>
-  <si>
-    <t>202103;0.01</t>
-  </si>
-  <si>
-    <t>重击概率+1%</t>
-  </si>
-  <si>
-    <t>绿林熊妖</t>
-  </si>
-  <si>
-    <t>100202;0.01</t>
-  </si>
-  <si>
-    <t>生命上限+1%</t>
+    <t>0,60,250,40,0</t>
+  </si>
+  <si>
+    <t>0,80,250,50,0</t>
+  </si>
+  <si>
+    <t>0,60,250,30,0</t>
+  </si>
+  <si>
+    <t>0,90,250,50,0</t>
+  </si>
+  <si>
+    <t>0,90,250,60,0</t>
+  </si>
+  <si>
+    <t>0,70,250,40,0</t>
+  </si>
+  <si>
+    <t>0,80,250,45,0</t>
+  </si>
+  <si>
+    <t>0,90,250,55,0</t>
+  </si>
+  <si>
+    <t>0,90,250,40,0</t>
+  </si>
+  <si>
+    <t>0,90,250,45,35</t>
+  </si>
+  <si>
+    <t>0,80,250,40,0</t>
+  </si>
+  <si>
+    <t>0,220,400,80,0</t>
+  </si>
+  <si>
+    <t>0,125,400,65,0</t>
+  </si>
+  <si>
+    <t>0,170,400,60,0</t>
+  </si>
+  <si>
+    <t>0,135,400,70,0</t>
+  </si>
+  <si>
+    <t>0,190,500,70,-60</t>
+  </si>
+  <si>
+    <t>0,150,400,80,0</t>
+  </si>
+  <si>
+    <t>0,200,400,80,0</t>
+  </si>
+  <si>
+    <t>0,120,400,70,0</t>
+  </si>
+  <si>
+    <t>0,125,400,70,0</t>
+  </si>
+  <si>
+    <t>0,280,400,70,0</t>
+  </si>
+  <si>
+    <t>0,130,400,80,-60</t>
+  </si>
+  <si>
+    <t>0,140,400,65,0</t>
+  </si>
+  <si>
+    <t>0,150,400,60,0</t>
+  </si>
+  <si>
+    <t>0,140,400,70,0</t>
+  </si>
+  <si>
+    <t>0,160,400,65,0</t>
+  </si>
+  <si>
+    <t>0,550,400,100,-60</t>
+  </si>
+  <si>
+    <t>0,250,400,80,0</t>
+  </si>
+  <si>
+    <t>0,150,400,70,0</t>
+  </si>
+  <si>
+    <t>0,90,400,50,0</t>
+  </si>
+  <si>
+    <t>0,170,400,75,0</t>
   </si>
   <si>
     <t>绿石怪</t>
-  </si>
-  <si>
-    <t>119303;50</t>
-  </si>
-  <si>
-    <t>命中等级提升50点</t>
-  </si>
-  <si>
-    <t>森林蜘蛛</t>
-  </si>
-  <si>
-    <t>200903;0.05</t>
-  </si>
-  <si>
-    <t>伤害加成+5%</t>
-  </si>
-  <si>
-    <t>0,60,250,40,0</t>
-  </si>
-  <si>
-    <t>森林熊</t>
-  </si>
-  <si>
-    <t>200303;0.01</t>
-  </si>
-  <si>
-    <t>闪避概率+1%</t>
-  </si>
-  <si>
-    <t>獠牙猪妖</t>
-  </si>
-  <si>
-    <t>120703;100</t>
-  </si>
-  <si>
-    <t>领主级</t>
-  </si>
-  <si>
-    <t>法术强度提升100点</t>
-  </si>
-  <si>
-    <t>0,110,400,60,0</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>森灵守卫者</t>
-  </si>
-  <si>
-    <t>100403;100</t>
-  </si>
-  <si>
-    <t>攻击提升100点</t>
-  </si>
-  <si>
-    <t>恶魔猪王</t>
-  </si>
-  <si>
-    <t>100203;1000</t>
-  </si>
-  <si>
-    <t>生命上限+1000点</t>
-  </si>
-  <si>
-    <t>邪能之主</t>
-  </si>
-  <si>
-    <t>120603;100</t>
-  </si>
-  <si>
-    <t>攻击强度提升100点</t>
-  </si>
-  <si>
-    <t>0,220,400,80,0</t>
-  </si>
-  <si>
-    <t>森灵之树</t>
-  </si>
-  <si>
-    <t>200403;0.01</t>
-  </si>
-  <si>
-    <t>抗暴率+1%</t>
-  </si>
-  <si>
-    <t>0,125,400,65,0</t>
-  </si>
-  <si>
-    <t>漠灵风暴之王</t>
-  </si>
-  <si>
-    <t>100603;100</t>
-  </si>
-  <si>
-    <t>物防提升100点</t>
-  </si>
-  <si>
-    <t>0,170,400,60,0</t>
-  </si>
-  <si>
-    <t>绿洲龟</t>
-  </si>
-  <si>
-    <t>绿洲恐龙</t>
-  </si>
-  <si>
-    <t>0,110,250,60,0</t>
-  </si>
-  <si>
-    <t>绿洲蜗牛</t>
-  </si>
-  <si>
-    <t>荒漠鹰</t>
-  </si>
-  <si>
-    <t>0,80,250,50,0</t>
-  </si>
-  <si>
-    <t>迅捷恐龙</t>
-  </si>
-  <si>
-    <t>遗迹火焰</t>
-  </si>
-  <si>
-    <t>0,60,250,30,0</t>
-  </si>
-  <si>
-    <t>遗迹弓手</t>
-  </si>
-  <si>
-    <t>荒漠巨蟹</t>
-  </si>
-  <si>
-    <t>0,135,400,70,0</t>
-  </si>
-  <si>
-    <t>沙漠之鳄</t>
-  </si>
-  <si>
-    <t>0,190,500,70,-60</t>
-  </si>
-  <si>
-    <t>绿洲龟王</t>
-  </si>
-  <si>
-    <t>0,150,400,80,0</t>
-  </si>
-  <si>
-    <t>遗迹守护者</t>
-  </si>
-  <si>
-    <t>0,200,400,80,0</t>
-  </si>
-  <si>
-    <t>遗迹之王</t>
-  </si>
-  <si>
-    <t>0,120,400,70,0</t>
-  </si>
-  <si>
-    <t>螃蟹护卫</t>
-  </si>
-  <si>
-    <t>0,90,250,50,0</t>
-  </si>
-  <si>
-    <t>猛虎</t>
-  </si>
-  <si>
-    <t>丛林虎</t>
-  </si>
-  <si>
-    <t>兽人护卫</t>
-  </si>
-  <si>
-    <t>地精守卫</t>
-  </si>
-  <si>
-    <t>兽人骑兵</t>
-  </si>
-  <si>
-    <t>0,90,250,60,0</t>
-  </si>
-  <si>
-    <t>岩石护卫</t>
-  </si>
-  <si>
-    <t>蛤蟆守护者</t>
-  </si>
-  <si>
-    <t>200103;0.01</t>
-  </si>
-  <si>
-    <t>暴击概率+1%</t>
-  </si>
-  <si>
-    <t>0,125,400,70,0</t>
-  </si>
-  <si>
-    <t>森林之王</t>
-  </si>
-  <si>
-    <t>0,280,400,70,0</t>
-  </si>
-  <si>
-    <t>地下巨鳄</t>
-  </si>
-  <si>
-    <t>0,130,400,80,-60</t>
-  </si>
-  <si>
-    <t>地下兽人祭祀</t>
-  </si>
-  <si>
-    <t>0,140,400,65,0</t>
-  </si>
-  <si>
-    <t>地灵牛头之王</t>
-  </si>
-  <si>
-    <t>冰灵蜘蛛</t>
-  </si>
-  <si>
-    <t>0,70,250,40,0</t>
-  </si>
-  <si>
-    <t>冰狼</t>
-  </si>
-  <si>
-    <t>0,80,250,45,0</t>
-  </si>
-  <si>
-    <t>冰灵山羊</t>
-  </si>
-  <si>
-    <t>0,90,250,55,0</t>
-  </si>
-  <si>
-    <t>冰封蜗牛</t>
-  </si>
-  <si>
-    <t>冰块士兵</t>
-  </si>
-  <si>
-    <t>冰灵</t>
-  </si>
-  <si>
-    <t>冰块护卫</t>
-  </si>
-  <si>
-    <t>冰封蛛王</t>
-  </si>
-  <si>
-    <t>冰灵之王</t>
-  </si>
-  <si>
-    <t>0,150,400,60,0</t>
-  </si>
-  <si>
-    <t>冰岩巨人</t>
-  </si>
-  <si>
-    <t>0,140,400,70,0</t>
-  </si>
-  <si>
-    <t>冰雪之主</t>
-  </si>
-  <si>
-    <t>0,160,400,65,0</t>
-  </si>
-  <si>
-    <t>冰封巨龙</t>
-  </si>
-  <si>
-    <t>0,550,400,100,-60</t>
-  </si>
-  <si>
-    <t>精灵蝴蝶</t>
-  </si>
-  <si>
-    <t>0,90,250,40,0</t>
-  </si>
-  <si>
-    <t>影月护卫</t>
-  </si>
-  <si>
-    <t>影月弓手</t>
-  </si>
-  <si>
-    <t>影月骑兵</t>
-  </si>
-  <si>
-    <t>暗灵士兵</t>
-  </si>
-  <si>
-    <t>熔岩护卫</t>
-  </si>
-  <si>
-    <t>影月碟王</t>
-  </si>
-  <si>
-    <t>0,250,400,80,0</t>
-  </si>
-  <si>
-    <t>影月女王</t>
-  </si>
-  <si>
-    <t>0,150,400,70,0</t>
-  </si>
-  <si>
-    <t>暗灵守卫者</t>
-  </si>
-  <si>
-    <t>0,90,400,50,0</t>
-  </si>
-  <si>
-    <t>暗灵狮鹫</t>
-  </si>
-  <si>
-    <t>暗灵之主</t>
-  </si>
-  <si>
-    <t>0,170,400,75,0</t>
-  </si>
-  <si>
-    <t>邪恶鳄鱼</t>
-  </si>
-  <si>
-    <t>100403;30</t>
-  </si>
-  <si>
-    <t>野外奇遇</t>
-  </si>
-  <si>
-    <t>攻击提升30点</t>
-  </si>
-  <si>
-    <t>野外有一定几率遇到,可以抓捕它哟！</t>
-  </si>
-  <si>
-    <t>0,90,250,45,35</t>
-  </si>
-  <si>
-    <t>火焰松鼠</t>
-  </si>
-  <si>
-    <t>白羽蝴蝶</t>
-  </si>
-  <si>
-    <t>冰雪人</t>
-  </si>
-  <si>
-    <t>火焰之树</t>
-  </si>
-  <si>
-    <t>天空守卫</t>
-  </si>
-  <si>
-    <t>0,80,250,40,0</t>
-  </si>
-  <si>
-    <t>熔岩之魔</t>
-  </si>
-  <si>
-    <t>200903;0.01</t>
-  </si>
-  <si>
-    <t>伤害加成+1%</t>
-  </si>
-  <si>
-    <t>天狼蜘蛛</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="26">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -794,148 +784,10 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="10"/>
+      <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -948,8 +800,30 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="36">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -964,7 +838,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.149906918546098"/>
+        <fgColor theme="0" tint="-0.14990691854609822"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -974,194 +848,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1195,253 +883,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1456,71 +902,33 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="4" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1807,14 +1215,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="C1:Z108"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="1" customWidth="1"/>
@@ -1839,13 +1247,13 @@
     <col min="27" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.1" customHeight="1"/>
-    <row r="2" ht="20.1" customHeight="1" spans="25:25">
+    <row r="1" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Y2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="20.1" customHeight="1" spans="3:26">
+    <row r="3" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1919,7 +1327,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" ht="20.1" customHeight="1" spans="3:26">
+    <row r="4" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="2" t="s">
         <v>1</v>
       </c>
@@ -1962,117 +1370,117 @@
       <c r="P4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="Q4" s="2" t="s">
+      <c r="Q4" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="R4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="R4" s="2" t="s">
+      <c r="S4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="S4" s="2" t="s">
+      <c r="T4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="T4" s="2" t="s">
+      <c r="U4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="U4" s="2" t="s">
+      <c r="V4" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="V4" s="2" t="s">
+      <c r="W4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W4" s="2" t="s">
+      <c r="X4" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="X4" s="2" t="s">
+      <c r="Y4" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="Y4" s="2" t="s">
+      <c r="Z4" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="Z4" s="2" t="s">
+    </row>
+    <row r="5" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C5" s="2" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="5" ht="20.1" customHeight="1" spans="3:26">
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="G5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="L5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="S5" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="T5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="V5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I5" s="2" t="s">
+      <c r="W5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="X5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="Y5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="U5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="V5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="W5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="X5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="Z5" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" ht="20.1" customHeight="1" spans="3:26">
+    </row>
+    <row r="6" spans="3:26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C6" s="3">
         <v>10001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E6" s="4">
         <v>2</v>
@@ -2095,8 +1503,8 @@
       <c r="K6" s="4">
         <v>310101</v>
       </c>
-      <c r="L6" s="7" t="s">
-        <v>52</v>
+      <c r="L6" s="6" t="s">
+        <v>51</v>
       </c>
       <c r="M6" s="3">
         <v>0</v>
@@ -2108,39 +1516,39 @@
         <v>-1</v>
       </c>
       <c r="P6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q6" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="Q6" s="3" t="s">
+      <c r="S6" s="5">
+        <v>2</v>
+      </c>
+      <c r="T6" s="5">
+        <v>0</v>
+      </c>
+      <c r="U6" s="5">
+        <v>0</v>
+      </c>
+      <c r="V6" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="S6" s="5">
-        <v>2</v>
-      </c>
-      <c r="T6" s="5">
-        <v>0</v>
-      </c>
-      <c r="U6" s="5">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="W6" s="5">
         <v>0</v>
       </c>
       <c r="Y6" s="5">
         <v>0</v>
       </c>
-      <c r="Z6" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="3:26">
+      <c r="Z6" s="7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C7" s="3">
         <v>10002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E7" s="4">
         <v>2</v>
@@ -2163,8 +1571,8 @@
       <c r="K7" s="4">
         <v>310102</v>
       </c>
-      <c r="L7" s="7" t="s">
-        <v>58</v>
+      <c r="L7" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="M7" s="3">
         <v>0</v>
@@ -2176,10 +1584,10 @@
         <v>-1</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S7" s="5">
         <v>2</v>
@@ -2191,7 +1599,7 @@
         <v>0</v>
       </c>
       <c r="V7" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W7" s="5">
         <v>0</v>
@@ -2199,16 +1607,16 @@
       <c r="Y7" s="5">
         <v>0</v>
       </c>
-      <c r="Z7" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="3:26">
+      <c r="Z7" s="7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="8" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C8" s="3">
         <v>10003</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E8" s="4">
         <v>2</v>
@@ -2231,8 +1639,8 @@
       <c r="K8" s="4">
         <v>310103</v>
       </c>
-      <c r="L8" s="7" t="s">
-        <v>61</v>
+      <c r="L8" s="6" t="s">
+        <v>60</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -2244,10 +1652,10 @@
         <v>-1</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S8" s="5">
         <v>2</v>
@@ -2259,7 +1667,7 @@
         <v>0</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W8" s="5">
         <v>0</v>
@@ -2267,16 +1675,16 @@
       <c r="Y8" s="5">
         <v>0</v>
       </c>
-      <c r="Z8" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="3:26">
+      <c r="Z8" s="7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="9" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C9" s="3">
         <v>10004</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E9" s="4">
         <v>2</v>
@@ -2299,8 +1707,8 @@
       <c r="K9" s="4">
         <v>310104</v>
       </c>
-      <c r="L9" s="7" t="s">
-        <v>64</v>
+      <c r="L9" s="6" t="s">
+        <v>63</v>
       </c>
       <c r="M9" s="3">
         <v>0</v>
@@ -2312,10 +1720,10 @@
         <v>-1</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S9" s="5">
         <v>2</v>
@@ -2327,7 +1735,7 @@
         <v>0</v>
       </c>
       <c r="V9" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W9" s="5">
         <v>0</v>
@@ -2335,16 +1743,16 @@
       <c r="Y9" s="5">
         <v>0</v>
       </c>
-      <c r="Z9" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="3:26">
+      <c r="Z9" s="7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="10" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C10" s="3">
         <v>10005</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>66</v>
+      <c r="D10" s="10" t="s">
+        <v>188</v>
       </c>
       <c r="E10" s="4">
         <v>2</v>
@@ -2367,8 +1775,8 @@
       <c r="K10" s="4">
         <v>310105</v>
       </c>
-      <c r="L10" s="7" t="s">
-        <v>67</v>
+      <c r="L10" s="6" t="s">
+        <v>65</v>
       </c>
       <c r="M10" s="3">
         <v>0</v>
@@ -2380,10 +1788,10 @@
         <v>-1</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="S10" s="5">
         <v>2</v>
@@ -2395,7 +1803,7 @@
         <v>0</v>
       </c>
       <c r="V10" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W10" s="5">
         <v>0</v>
@@ -2403,16 +1811,16 @@
       <c r="Y10" s="5">
         <v>0</v>
       </c>
-      <c r="Z10" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" spans="3:26">
+      <c r="Z10" s="7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="11" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C11" s="3">
         <v>10006</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E11" s="4">
         <v>2</v>
@@ -2435,8 +1843,8 @@
       <c r="K11" s="4">
         <v>310106</v>
       </c>
-      <c r="L11" s="7" t="s">
-        <v>70</v>
+      <c r="L11" s="6" t="s">
+        <v>68</v>
       </c>
       <c r="M11" s="3">
         <v>0</v>
@@ -2448,10 +1856,10 @@
         <v>-1</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="S11" s="5">
         <v>2</v>
@@ -2463,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W11" s="5">
         <v>0</v>
@@ -2471,16 +1879,16 @@
       <c r="Y11" s="5">
         <v>0</v>
       </c>
-      <c r="Z11" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12" spans="3:26">
+      <c r="Z11" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="12" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C12" s="3">
         <v>10007</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E12" s="4">
         <v>2</v>
@@ -2503,8 +1911,8 @@
       <c r="K12" s="4">
         <v>310107</v>
       </c>
-      <c r="L12" s="7" t="s">
-        <v>74</v>
+      <c r="L12" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="M12" s="3">
         <v>0</v>
@@ -2516,10 +1924,10 @@
         <v>-1</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="S12" s="5">
         <v>2</v>
@@ -2531,7 +1939,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W12" s="5">
         <v>0</v>
@@ -2539,16 +1947,16 @@
       <c r="Y12" s="5">
         <v>0</v>
       </c>
-      <c r="Z12" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="13" spans="3:26">
+      <c r="Z12" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="13" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C13" s="3">
         <v>10008</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E13" s="4">
         <v>2</v>
@@ -2571,8 +1979,8 @@
       <c r="K13" s="4">
         <v>310160</v>
       </c>
-      <c r="L13" s="7" t="s">
-        <v>77</v>
+      <c r="L13" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="M13" s="3">
         <v>0</v>
@@ -2584,10 +1992,10 @@
         <v>-1</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S13" s="5">
         <v>2</v>
@@ -2599,24 +2007,24 @@
         <v>0</v>
       </c>
       <c r="V13" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="W13" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="W13" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="14" spans="3:26">
+    </row>
+    <row r="14" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C14" s="3">
         <v>10009</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>81</v>
+      <c r="D14" s="10" t="s">
+        <v>189</v>
       </c>
       <c r="E14" s="4">
         <v>2</v>
@@ -2639,8 +2047,8 @@
       <c r="K14" s="4">
         <v>310161</v>
       </c>
-      <c r="L14" s="7" t="s">
-        <v>82</v>
+      <c r="L14" s="6" t="s">
+        <v>77</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -2652,11 +2060,11 @@
         <v>-1</v>
       </c>
       <c r="P14" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q14" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="S14" s="5">
         <v>2</v>
       </c>
@@ -2667,24 +2075,24 @@
         <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="W14" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="W14" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="15" spans="3:26">
+    </row>
+    <row r="15" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C15" s="3">
         <v>10010</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="E15" s="4">
         <v>2</v>
@@ -2707,8 +2115,8 @@
       <c r="K15" s="4">
         <v>310162</v>
       </c>
-      <c r="L15" s="7" t="s">
-        <v>85</v>
+      <c r="L15" s="6" t="s">
+        <v>80</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -2720,10 +2128,10 @@
         <v>-1</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="S15" s="5">
         <v>2</v>
@@ -2735,24 +2143,24 @@
         <v>0</v>
       </c>
       <c r="V15" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="W15" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="W15" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="16" spans="3:26">
+    </row>
+    <row r="16" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C16" s="3">
         <v>10011</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E16" s="4">
         <v>2</v>
@@ -2775,8 +2183,8 @@
       <c r="K16" s="4">
         <v>310163</v>
       </c>
-      <c r="L16" s="7" t="s">
-        <v>88</v>
+      <c r="L16" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="M16" s="3">
         <v>0</v>
@@ -2788,10 +2196,10 @@
         <v>-1</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="S16" s="5">
         <v>2</v>
@@ -2803,7 +2211,7 @@
         <v>0</v>
       </c>
       <c r="V16" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W16" s="5">
         <v>0</v>
@@ -2811,16 +2219,16 @@
       <c r="Y16" s="5">
         <v>0</v>
       </c>
-      <c r="Z16" s="8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="17" spans="3:26">
+      <c r="Z16" s="9" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C17" s="3">
         <v>10012</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E17" s="4">
         <v>2</v>
@@ -2843,8 +2251,8 @@
       <c r="K17" s="4">
         <v>310164</v>
       </c>
-      <c r="L17" s="7" t="s">
-        <v>92</v>
+      <c r="L17" s="6" t="s">
+        <v>86</v>
       </c>
       <c r="M17" s="3">
         <v>0</v>
@@ -2856,10 +2264,10 @@
         <v>-1</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="S17" s="5">
         <v>2</v>
@@ -2871,7 +2279,7 @@
         <v>0</v>
       </c>
       <c r="V17" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W17" s="5">
         <v>0</v>
@@ -2879,16 +2287,16 @@
       <c r="Y17" s="5">
         <v>0</v>
       </c>
-      <c r="Z17" s="8" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="18" spans="3:26">
+      <c r="Z17" s="9" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C18" s="3">
         <v>10013</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="E18" s="4">
         <v>2</v>
@@ -2911,8 +2319,8 @@
       <c r="K18" s="4">
         <v>310165</v>
       </c>
-      <c r="L18" s="7" t="s">
-        <v>96</v>
+      <c r="L18" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="M18" s="3">
         <v>0</v>
@@ -2924,10 +2332,10 @@
         <v>-1</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="S18" s="5">
         <v>2</v>
@@ -2939,7 +2347,7 @@
         <v>0</v>
       </c>
       <c r="V18" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W18" s="5">
         <v>0</v>
@@ -2947,16 +2355,16 @@
       <c r="Y18" s="5">
         <v>0</v>
       </c>
-      <c r="Z18" s="8" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="19" spans="3:26">
+      <c r="Z18" s="9" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C19" s="3">
         <v>10014</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="E19" s="4">
         <v>2</v>
@@ -2979,8 +2387,8 @@
       <c r="K19" s="4">
         <v>320101</v>
       </c>
-      <c r="L19" s="7" t="s">
-        <v>52</v>
+      <c r="L19" s="6" t="s">
+        <v>51</v>
       </c>
       <c r="M19" s="3">
         <v>0</v>
@@ -2992,39 +2400,39 @@
         <v>-1</v>
       </c>
       <c r="P19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q19" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="Q19" s="3" t="s">
+      <c r="S19" s="5">
+        <v>2</v>
+      </c>
+      <c r="T19" s="5">
+        <v>0</v>
+      </c>
+      <c r="U19" s="5">
+        <v>0</v>
+      </c>
+      <c r="V19" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="S19" s="5">
-        <v>2</v>
-      </c>
-      <c r="T19" s="5">
-        <v>0</v>
-      </c>
-      <c r="U19" s="5">
-        <v>0</v>
-      </c>
-      <c r="V19" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="W19" s="5">
         <v>0</v>
       </c>
       <c r="Y19" s="5">
         <v>0</v>
       </c>
-      <c r="Z19" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="20" spans="3:26">
+      <c r="Z19" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C20" s="3">
         <v>10015</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E20" s="4">
         <v>2</v>
@@ -3047,8 +2455,8 @@
       <c r="K20" s="4">
         <v>320102</v>
       </c>
-      <c r="L20" s="7" t="s">
-        <v>58</v>
+      <c r="L20" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -3060,10 +2468,10 @@
         <v>-1</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S20" s="5">
         <v>2</v>
@@ -3075,7 +2483,7 @@
         <v>0</v>
       </c>
       <c r="V20" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W20" s="5">
         <v>0</v>
@@ -3083,16 +2491,16 @@
       <c r="Y20" s="5">
         <v>0</v>
       </c>
-      <c r="Z20" s="8" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="21" spans="3:26">
+      <c r="Z20" s="7" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C21" s="3">
         <v>10016</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="E21" s="4">
         <v>2</v>
@@ -3115,8 +2523,8 @@
       <c r="K21" s="4">
         <v>320103</v>
       </c>
-      <c r="L21" s="7" t="s">
-        <v>61</v>
+      <c r="L21" s="6" t="s">
+        <v>60</v>
       </c>
       <c r="M21" s="3">
         <v>0</v>
@@ -3128,10 +2536,10 @@
         <v>-1</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S21" s="5">
         <v>2</v>
@@ -3143,7 +2551,7 @@
         <v>0</v>
       </c>
       <c r="V21" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W21" s="5">
         <v>0</v>
@@ -3151,16 +2559,16 @@
       <c r="Y21" s="5">
         <v>0</v>
       </c>
-      <c r="Z21" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="22" spans="3:26">
+      <c r="Z21" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C22" s="3">
         <v>10017</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="E22" s="4">
         <v>2</v>
@@ -3183,8 +2591,8 @@
       <c r="K22" s="4">
         <v>320104</v>
       </c>
-      <c r="L22" s="7" t="s">
-        <v>64</v>
+      <c r="L22" s="6" t="s">
+        <v>63</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -3196,10 +2604,10 @@
         <v>-1</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S22" s="5">
         <v>2</v>
@@ -3211,7 +2619,7 @@
         <v>0</v>
       </c>
       <c r="V22" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W22" s="5">
         <v>0</v>
@@ -3219,16 +2627,16 @@
       <c r="Y22" s="5">
         <v>0</v>
       </c>
-      <c r="Z22" s="8" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="23" spans="3:26">
+      <c r="Z22" s="7" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C23" s="3">
         <v>10018</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E23" s="4">
         <v>2</v>
@@ -3251,8 +2659,8 @@
       <c r="K23" s="4">
         <v>320105</v>
       </c>
-      <c r="L23" s="7" t="s">
-        <v>67</v>
+      <c r="L23" s="6" t="s">
+        <v>65</v>
       </c>
       <c r="M23" s="3">
         <v>0</v>
@@ -3264,10 +2672,10 @@
         <v>-1</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="S23" s="5">
         <v>2</v>
@@ -3279,7 +2687,7 @@
         <v>0</v>
       </c>
       <c r="V23" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W23" s="5">
         <v>0</v>
@@ -3287,16 +2695,16 @@
       <c r="Y23" s="5">
         <v>0</v>
       </c>
-      <c r="Z23" s="8" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="24" spans="3:26">
+      <c r="Z23" s="7" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C24" s="3">
         <v>10019</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="E24" s="4">
         <v>2</v>
@@ -3319,8 +2727,8 @@
       <c r="K24" s="4">
         <v>320106</v>
       </c>
-      <c r="L24" s="7" t="s">
-        <v>52</v>
+      <c r="L24" s="6" t="s">
+        <v>51</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -3332,39 +2740,39 @@
         <v>-1</v>
       </c>
       <c r="P24" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q24" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="Q24" s="3" t="s">
+      <c r="S24" s="5">
+        <v>2</v>
+      </c>
+      <c r="T24" s="5">
+        <v>0</v>
+      </c>
+      <c r="U24" s="5">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="S24" s="5">
-        <v>2</v>
-      </c>
-      <c r="T24" s="5">
-        <v>0</v>
-      </c>
-      <c r="U24" s="5">
-        <v>0</v>
-      </c>
-      <c r="V24" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="W24" s="5">
         <v>0</v>
       </c>
       <c r="Y24" s="5">
         <v>0</v>
       </c>
-      <c r="Z24" s="8" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="25" spans="3:26">
+      <c r="Z24" s="7" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C25" s="3">
         <v>10020</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="E25" s="4">
         <v>2</v>
@@ -3387,8 +2795,8 @@
       <c r="K25" s="4">
         <v>320107</v>
       </c>
-      <c r="L25" s="7" t="s">
-        <v>58</v>
+      <c r="L25" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="M25" s="3">
         <v>0</v>
@@ -3400,10 +2808,10 @@
         <v>-1</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q25" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S25" s="5">
         <v>2</v>
@@ -3415,7 +2823,7 @@
         <v>0</v>
       </c>
       <c r="V25" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W25" s="5">
         <v>0</v>
@@ -3423,16 +2831,16 @@
       <c r="Y25" s="5">
         <v>0</v>
       </c>
-      <c r="Z25" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="26" spans="3:26">
+      <c r="Z25" s="7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C26" s="3">
         <v>10021</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="E26" s="4">
         <v>2</v>
@@ -3455,8 +2863,8 @@
       <c r="K26" s="4">
         <v>320161</v>
       </c>
-      <c r="L26" s="7" t="s">
-        <v>61</v>
+      <c r="L26" s="6" t="s">
+        <v>60</v>
       </c>
       <c r="M26" s="3">
         <v>0</v>
@@ -3468,10 +2876,10 @@
         <v>-1</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q26" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S26" s="5">
         <v>2</v>
@@ -3483,7 +2891,7 @@
         <v>0</v>
       </c>
       <c r="V26" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W26" s="5">
         <v>0</v>
@@ -3491,16 +2899,16 @@
       <c r="Y26" s="5">
         <v>0</v>
       </c>
-      <c r="Z26" s="8" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="27" spans="3:26">
+      <c r="Z26" s="9" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C27" s="3">
         <v>10022</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="E27" s="4">
         <v>2</v>
@@ -3523,8 +2931,8 @@
       <c r="K27" s="4">
         <v>320162</v>
       </c>
-      <c r="L27" s="7" t="s">
-        <v>64</v>
+      <c r="L27" s="6" t="s">
+        <v>63</v>
       </c>
       <c r="M27" s="3">
         <v>0</v>
@@ -3536,10 +2944,10 @@
         <v>-1</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S27" s="5">
         <v>2</v>
@@ -3551,7 +2959,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W27" s="5">
         <v>0</v>
@@ -3559,16 +2967,16 @@
       <c r="Y27" s="5">
         <v>0</v>
       </c>
-      <c r="Z27" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="28" spans="3:26">
+      <c r="Z27" s="9" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C28" s="3">
         <v>10023</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="E28" s="4">
         <v>2</v>
@@ -3591,8 +2999,8 @@
       <c r="K28" s="4">
         <v>320163</v>
       </c>
-      <c r="L28" s="7" t="s">
-        <v>67</v>
+      <c r="L28" s="6" t="s">
+        <v>65</v>
       </c>
       <c r="M28" s="3">
         <v>0</v>
@@ -3604,10 +3012,10 @@
         <v>-1</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q28" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="S28" s="5">
         <v>2</v>
@@ -3619,7 +3027,7 @@
         <v>0</v>
       </c>
       <c r="V28" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W28" s="5">
         <v>0</v>
@@ -3627,16 +3035,16 @@
       <c r="Y28" s="5">
         <v>0</v>
       </c>
-      <c r="Z28" s="8" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="29" spans="3:26">
+      <c r="Z28" s="9" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C29" s="3">
         <v>10024</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="E29" s="4">
         <v>2</v>
@@ -3659,8 +3067,8 @@
       <c r="K29" s="4">
         <v>320164</v>
       </c>
-      <c r="L29" s="7" t="s">
-        <v>70</v>
+      <c r="L29" s="6" t="s">
+        <v>68</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -3672,10 +3080,10 @@
         <v>-1</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q29" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="S29" s="5">
         <v>2</v>
@@ -3687,7 +3095,7 @@
         <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W29" s="5">
         <v>0</v>
@@ -3695,16 +3103,16 @@
       <c r="Y29" s="5">
         <v>0</v>
       </c>
-      <c r="Z29" s="8" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="30" spans="3:26">
+      <c r="Z29" s="9" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C30" s="3">
         <v>10025</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="E30" s="4">
         <v>2</v>
@@ -3727,8 +3135,8 @@
       <c r="K30" s="4">
         <v>320165</v>
       </c>
-      <c r="L30" s="7" t="s">
-        <v>74</v>
+      <c r="L30" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="M30" s="3">
         <v>0</v>
@@ -3740,10 +3148,10 @@
         <v>-1</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q30" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="S30" s="5">
         <v>2</v>
@@ -3755,7 +3163,7 @@
         <v>0</v>
       </c>
       <c r="V30" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W30" s="5">
         <v>0</v>
@@ -3763,16 +3171,16 @@
       <c r="Y30" s="5">
         <v>0</v>
       </c>
-      <c r="Z30" s="8" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="31" spans="3:26">
+      <c r="Z30" s="9" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C31" s="3">
         <v>10026</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="E31" s="4">
         <v>2</v>
@@ -3795,8 +3203,8 @@
       <c r="K31" s="4">
         <v>330101</v>
       </c>
-      <c r="L31" s="7" t="s">
-        <v>77</v>
+      <c r="L31" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="M31" s="3">
         <v>0</v>
@@ -3808,10 +3216,10 @@
         <v>-1</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q31" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S31" s="5">
         <v>2</v>
@@ -3823,7 +3231,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W31" s="5">
         <v>0</v>
@@ -3831,16 +3239,16 @@
       <c r="Y31" s="5">
         <v>0</v>
       </c>
-      <c r="Z31" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="32" spans="3:26">
+      <c r="Z31" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C32" s="3">
         <v>10027</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="E32" s="4">
         <v>2</v>
@@ -3863,8 +3271,8 @@
       <c r="K32" s="4">
         <v>330102</v>
       </c>
-      <c r="L32" s="7" t="s">
-        <v>82</v>
+      <c r="L32" s="6" t="s">
+        <v>77</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -3876,10 +3284,10 @@
         <v>-1</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q32" s="3" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="S32" s="5">
         <v>2</v>
@@ -3891,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="V32" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W32" s="5">
         <v>0</v>
@@ -3899,16 +3307,16 @@
       <c r="Y32" s="5">
         <v>0</v>
       </c>
-      <c r="Z32" s="8" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="33" spans="3:26">
+      <c r="Z32" s="7" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="33" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C33" s="3">
         <v>10028</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="E33" s="4">
         <v>2</v>
@@ -3931,8 +3339,8 @@
       <c r="K33" s="4">
         <v>330103</v>
       </c>
-      <c r="L33" s="7" t="s">
-        <v>85</v>
+      <c r="L33" s="6" t="s">
+        <v>80</v>
       </c>
       <c r="M33" s="3">
         <v>0</v>
@@ -3944,10 +3352,10 @@
         <v>-1</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q33" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="S33" s="5">
         <v>2</v>
@@ -3959,7 +3367,7 @@
         <v>0</v>
       </c>
       <c r="V33" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W33" s="5">
         <v>0</v>
@@ -3967,16 +3375,16 @@
       <c r="Y33" s="5">
         <v>0</v>
       </c>
-      <c r="Z33" s="8" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="34" spans="3:26">
+      <c r="Z33" s="7" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="34" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C34" s="3">
         <v>10029</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="E34" s="4">
         <v>2</v>
@@ -3999,8 +3407,8 @@
       <c r="K34" s="4">
         <v>330104</v>
       </c>
-      <c r="L34" s="7" t="s">
-        <v>88</v>
+      <c r="L34" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="M34" s="3">
         <v>0</v>
@@ -4012,10 +3420,10 @@
         <v>-1</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q34" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="S34" s="5">
         <v>2</v>
@@ -4027,7 +3435,7 @@
         <v>0</v>
       </c>
       <c r="V34" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W34" s="5">
         <v>0</v>
@@ -4035,16 +3443,16 @@
       <c r="Y34" s="5">
         <v>0</v>
       </c>
-      <c r="Z34" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="35" spans="3:26">
+      <c r="Z34" s="7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="35" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C35" s="3">
         <v>10030</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="E35" s="4">
         <v>2</v>
@@ -4067,8 +3475,8 @@
       <c r="K35" s="4">
         <v>330105</v>
       </c>
-      <c r="L35" s="7" t="s">
-        <v>92</v>
+      <c r="L35" s="6" t="s">
+        <v>86</v>
       </c>
       <c r="M35" s="3">
         <v>0</v>
@@ -4080,10 +3488,10 @@
         <v>-1</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q35" s="3" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="S35" s="5">
         <v>2</v>
@@ -4095,7 +3503,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W35" s="5">
         <v>0</v>
@@ -4103,16 +3511,16 @@
       <c r="Y35" s="5">
         <v>0</v>
       </c>
-      <c r="Z35" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="36" spans="3:26">
+      <c r="Z35" s="7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="36" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C36" s="3">
         <v>10031</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="E36" s="4">
         <v>2</v>
@@ -4135,8 +3543,8 @@
       <c r="K36" s="4">
         <v>330106</v>
       </c>
-      <c r="L36" s="7" t="s">
-        <v>96</v>
+      <c r="L36" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="M36" s="3">
         <v>0</v>
@@ -4148,10 +3556,10 @@
         <v>-1</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q36" s="3" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="S36" s="5">
         <v>2</v>
@@ -4163,7 +3571,7 @@
         <v>0</v>
       </c>
       <c r="V36" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W36" s="5">
         <v>0</v>
@@ -4171,16 +3579,16 @@
       <c r="Y36" s="5">
         <v>0</v>
       </c>
-      <c r="Z36" s="8" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="37" spans="3:26">
+      <c r="Z36" s="7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="37" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C37" s="3">
         <v>10032</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="E37" s="4">
         <v>2</v>
@@ -4203,8 +3611,8 @@
       <c r="K37" s="4">
         <v>330107</v>
       </c>
-      <c r="L37" s="7" t="s">
-        <v>74</v>
+      <c r="L37" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="M37" s="3">
         <v>0</v>
@@ -4216,10 +3624,10 @@
         <v>-1</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q37" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="S37" s="5">
         <v>2</v>
@@ -4231,7 +3639,7 @@
         <v>0</v>
       </c>
       <c r="V37" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W37" s="5">
         <v>0</v>
@@ -4239,16 +3647,16 @@
       <c r="Y37" s="5">
         <v>0</v>
       </c>
-      <c r="Z37" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="38" spans="3:26">
+      <c r="Z37" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="38" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C38" s="3">
         <v>10033</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="E38" s="4">
         <v>2</v>
@@ -4271,8 +3679,8 @@
       <c r="K38" s="4">
         <v>330161</v>
       </c>
-      <c r="L38" s="7" t="s">
-        <v>129</v>
+      <c r="L38" s="6" t="s">
+        <v>111</v>
       </c>
       <c r="M38" s="3">
         <v>0</v>
@@ -4284,10 +3692,10 @@
         <v>-1</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q38" s="3" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="S38" s="5">
         <v>2</v>
@@ -4299,7 +3707,7 @@
         <v>0</v>
       </c>
       <c r="V38" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W38" s="5">
         <v>0</v>
@@ -4307,16 +3715,16 @@
       <c r="Y38" s="5">
         <v>0</v>
       </c>
-      <c r="Z38" s="8" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="39" spans="3:26">
+      <c r="Z38" s="9" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="39" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C39" s="3">
         <v>10034</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="E39" s="4">
         <v>2</v>
@@ -4339,8 +3747,8 @@
       <c r="K39" s="4">
         <v>330162</v>
       </c>
-      <c r="L39" s="7" t="s">
-        <v>52</v>
+      <c r="L39" s="6" t="s">
+        <v>51</v>
       </c>
       <c r="M39" s="3">
         <v>0</v>
@@ -4352,39 +3760,39 @@
         <v>-1</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q39" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="S39" s="5">
+        <v>2</v>
+      </c>
+      <c r="T39" s="5">
+        <v>0</v>
+      </c>
+      <c r="U39" s="5">
+        <v>0</v>
+      </c>
+      <c r="V39" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="S39" s="5">
-        <v>2</v>
-      </c>
-      <c r="T39" s="5">
-        <v>0</v>
-      </c>
-      <c r="U39" s="5">
-        <v>0</v>
-      </c>
-      <c r="V39" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="W39" s="5">
         <v>0</v>
       </c>
       <c r="Y39" s="5">
         <v>0</v>
       </c>
-      <c r="Z39" s="8" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="40" spans="3:26">
+      <c r="Z39" s="9" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="40" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C40" s="3">
         <v>10035</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="E40" s="4">
         <v>2</v>
@@ -4407,8 +3815,8 @@
       <c r="K40" s="4">
         <v>330163</v>
       </c>
-      <c r="L40" s="7" t="s">
-        <v>58</v>
+      <c r="L40" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="M40" s="3">
         <v>0</v>
@@ -4420,10 +3828,10 @@
         <v>-1</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q40" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S40" s="5">
         <v>2</v>
@@ -4435,7 +3843,7 @@
         <v>0</v>
       </c>
       <c r="V40" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W40" s="5">
         <v>0</v>
@@ -4443,16 +3851,16 @@
       <c r="Y40" s="5">
         <v>0</v>
       </c>
-      <c r="Z40" s="8" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="41" spans="3:26">
+      <c r="Z40" s="9" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="41" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C41" s="3">
         <v>10036</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="E41" s="4">
         <v>2</v>
@@ -4475,8 +3883,8 @@
       <c r="K41" s="4">
         <v>330164</v>
       </c>
-      <c r="L41" s="7" t="s">
-        <v>61</v>
+      <c r="L41" s="6" t="s">
+        <v>60</v>
       </c>
       <c r="M41" s="3">
         <v>0</v>
@@ -4488,10 +3896,10 @@
         <v>-1</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q41" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S41" s="5">
         <v>2</v>
@@ -4503,7 +3911,7 @@
         <v>0</v>
       </c>
       <c r="V41" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W41" s="5">
         <v>0</v>
@@ -4511,16 +3919,16 @@
       <c r="Y41" s="5">
         <v>0</v>
       </c>
-      <c r="Z41" s="8" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="42" spans="3:26">
+      <c r="Z41" s="9" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="42" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C42" s="3">
         <v>10037</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="E42" s="4">
         <v>2</v>
@@ -4543,8 +3951,8 @@
       <c r="K42" s="4">
         <v>330165</v>
       </c>
-      <c r="L42" s="7" t="s">
-        <v>64</v>
+      <c r="L42" s="6" t="s">
+        <v>63</v>
       </c>
       <c r="M42" s="3">
         <v>0</v>
@@ -4556,10 +3964,10 @@
         <v>-1</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q42" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S42" s="5">
         <v>2</v>
@@ -4571,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="V42" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W42" s="5">
         <v>0</v>
@@ -4579,16 +3987,16 @@
       <c r="Y42" s="5">
         <v>0</v>
       </c>
-      <c r="Z42" s="8" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="43" spans="3:26">
+      <c r="Z42" s="9" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="43" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C43" s="3">
         <v>10038</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="E43" s="4">
         <v>2</v>
@@ -4611,8 +4019,8 @@
       <c r="K43" s="4">
         <v>340101</v>
       </c>
-      <c r="L43" s="7" t="s">
-        <v>67</v>
+      <c r="L43" s="6" t="s">
+        <v>65</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -4624,10 +4032,10 @@
         <v>-1</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q43" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="S43" s="5">
         <v>2</v>
@@ -4639,7 +4047,7 @@
         <v>0</v>
       </c>
       <c r="V43" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W43" s="5">
         <v>0</v>
@@ -4647,16 +4055,16 @@
       <c r="Y43" s="5">
         <v>0</v>
       </c>
-      <c r="Z43" s="8" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="44" spans="3:26">
+      <c r="Z43" s="7" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="44" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C44" s="3">
         <v>10039</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>141</v>
+      <c r="D44" s="4" t="s">
+        <v>118</v>
       </c>
       <c r="E44" s="4">
         <v>2</v>
@@ -4679,8 +4087,8 @@
       <c r="K44" s="4">
         <v>340102</v>
       </c>
-      <c r="L44" s="7" t="s">
-        <v>52</v>
+      <c r="L44" s="6" t="s">
+        <v>51</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4692,39 +4100,39 @@
         <v>-1</v>
       </c>
       <c r="P44" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q44" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="Q44" s="3" t="s">
+      <c r="S44" s="5">
+        <v>2</v>
+      </c>
+      <c r="T44" s="5">
+        <v>0</v>
+      </c>
+      <c r="U44" s="5">
+        <v>0</v>
+      </c>
+      <c r="V44" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="S44" s="5">
-        <v>2</v>
-      </c>
-      <c r="T44" s="5">
-        <v>0</v>
-      </c>
-      <c r="U44" s="5">
-        <v>0</v>
-      </c>
-      <c r="V44" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="W44" s="5">
         <v>0</v>
       </c>
       <c r="Y44" s="5">
         <v>0</v>
       </c>
-      <c r="Z44" s="8" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="45" spans="3:26">
+      <c r="Z44" s="7" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="45" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C45" s="3">
         <v>10040</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="E45" s="4">
         <v>2</v>
@@ -4747,8 +4155,8 @@
       <c r="K45" s="4">
         <v>340103</v>
       </c>
-      <c r="L45" s="7" t="s">
-        <v>58</v>
+      <c r="L45" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="M45" s="3">
         <v>0</v>
@@ -4760,10 +4168,10 @@
         <v>-1</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q45" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S45" s="5">
         <v>2</v>
@@ -4775,7 +4183,7 @@
         <v>0</v>
       </c>
       <c r="V45" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W45" s="5">
         <v>0</v>
@@ -4783,16 +4191,16 @@
       <c r="Y45" s="5">
         <v>0</v>
       </c>
-      <c r="Z45" s="8" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="46" spans="3:26">
+      <c r="Z45" s="7" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="46" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C46" s="3">
         <v>10041</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="E46" s="4">
         <v>2</v>
@@ -4815,8 +4223,8 @@
       <c r="K46" s="4">
         <v>340104</v>
       </c>
-      <c r="L46" s="7" t="s">
-        <v>61</v>
+      <c r="L46" s="6" t="s">
+        <v>60</v>
       </c>
       <c r="M46" s="3">
         <v>0</v>
@@ -4828,10 +4236,10 @@
         <v>-1</v>
       </c>
       <c r="P46" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q46" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S46" s="5">
         <v>2</v>
@@ -4843,7 +4251,7 @@
         <v>0</v>
       </c>
       <c r="V46" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W46" s="5">
         <v>0</v>
@@ -4851,16 +4259,16 @@
       <c r="Y46" s="5">
         <v>0</v>
       </c>
-      <c r="Z46" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="47" spans="3:26">
+      <c r="Z46" s="7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="47" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C47" s="3">
         <v>10042</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="E47" s="4">
         <v>2</v>
@@ -4883,8 +4291,8 @@
       <c r="K47" s="4">
         <v>340105</v>
       </c>
-      <c r="L47" s="7" t="s">
-        <v>64</v>
+      <c r="L47" s="6" t="s">
+        <v>63</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4896,10 +4304,10 @@
         <v>-1</v>
       </c>
       <c r="P47" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q47" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S47" s="5">
         <v>2</v>
@@ -4911,7 +4319,7 @@
         <v>0</v>
       </c>
       <c r="V47" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W47" s="5">
         <v>0</v>
@@ -4919,16 +4327,16 @@
       <c r="Y47" s="5">
         <v>0</v>
       </c>
-      <c r="Z47" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="48" spans="3:26">
+      <c r="Z47" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="48" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C48" s="3">
         <v>10043</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>147</v>
+        <v>122</v>
       </c>
       <c r="E48" s="4">
         <v>2</v>
@@ -4951,8 +4359,8 @@
       <c r="K48" s="4">
         <v>340106</v>
       </c>
-      <c r="L48" s="7" t="s">
-        <v>67</v>
+      <c r="L48" s="6" t="s">
+        <v>65</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
@@ -4964,10 +4372,10 @@
         <v>-1</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q48" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="S48" s="5">
         <v>2</v>
@@ -4979,7 +4387,7 @@
         <v>0</v>
       </c>
       <c r="V48" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W48" s="5">
         <v>0</v>
@@ -4987,16 +4395,16 @@
       <c r="Y48" s="5">
         <v>0</v>
       </c>
-      <c r="Z48" s="8" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="49" spans="3:26">
+      <c r="Z48" s="7" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C49" s="3">
         <v>10044</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="E49" s="4">
         <v>2</v>
@@ -5019,8 +4427,8 @@
       <c r="K49" s="4">
         <v>340107</v>
       </c>
-      <c r="L49" s="7" t="s">
-        <v>70</v>
+      <c r="L49" s="6" t="s">
+        <v>68</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -5032,10 +4440,10 @@
         <v>-1</v>
       </c>
       <c r="P49" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q49" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="S49" s="5">
         <v>2</v>
@@ -5047,7 +4455,7 @@
         <v>0</v>
       </c>
       <c r="V49" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W49" s="5">
         <v>0</v>
@@ -5055,16 +4463,16 @@
       <c r="Y49" s="5">
         <v>0</v>
       </c>
-      <c r="Z49" s="8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="50" spans="3:26">
+      <c r="Z49" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C50" s="3">
         <v>10045</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="E50" s="4">
         <v>2</v>
@@ -5087,8 +4495,8 @@
       <c r="K50" s="4">
         <v>340161</v>
       </c>
-      <c r="L50" s="7" t="s">
-        <v>74</v>
+      <c r="L50" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="M50" s="3">
         <v>0</v>
@@ -5100,10 +4508,10 @@
         <v>-1</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q50" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="S50" s="5">
         <v>2</v>
@@ -5115,7 +4523,7 @@
         <v>0</v>
       </c>
       <c r="V50" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W50" s="5">
         <v>0</v>
@@ -5123,16 +4531,16 @@
       <c r="Y50" s="5">
         <v>0</v>
       </c>
-      <c r="Z50" s="8" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="51" spans="3:26">
+      <c r="Z50" s="9" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C51" s="3">
         <v>10046</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="E51" s="4">
         <v>2</v>
@@ -5155,8 +4563,8 @@
       <c r="K51" s="4">
         <v>340162</v>
       </c>
-      <c r="L51" s="7" t="s">
-        <v>77</v>
+      <c r="L51" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="M51" s="3">
         <v>0</v>
@@ -5168,10 +4576,10 @@
         <v>-1</v>
       </c>
       <c r="P51" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q51" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S51" s="5">
         <v>2</v>
@@ -5183,7 +4591,7 @@
         <v>0</v>
       </c>
       <c r="V51" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W51" s="5">
         <v>0</v>
@@ -5191,16 +4599,16 @@
       <c r="Y51" s="5">
         <v>0</v>
       </c>
-      <c r="Z51" s="8" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="52" spans="3:26">
+      <c r="Z51" s="9" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C52" s="3">
         <v>10047</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="E52" s="4">
         <v>2</v>
@@ -5223,8 +4631,8 @@
       <c r="K52" s="4">
         <v>340163</v>
       </c>
-      <c r="L52" s="7" t="s">
-        <v>82</v>
+      <c r="L52" s="6" t="s">
+        <v>77</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -5236,11 +4644,11 @@
         <v>-1</v>
       </c>
       <c r="P52" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q52" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="S52" s="5">
         <v>2</v>
       </c>
@@ -5251,7 +4659,7 @@
         <v>0</v>
       </c>
       <c r="V52" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W52" s="5">
         <v>0</v>
@@ -5259,16 +4667,16 @@
       <c r="Y52" s="5">
         <v>0</v>
       </c>
-      <c r="Z52" s="8" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="53" spans="3:26">
+      <c r="Z52" s="9" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C53" s="3">
         <v>10048</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>154</v>
+        <v>127</v>
       </c>
       <c r="E53" s="4">
         <v>2</v>
@@ -5291,8 +4699,8 @@
       <c r="K53" s="4">
         <v>340164</v>
       </c>
-      <c r="L53" s="7" t="s">
-        <v>85</v>
+      <c r="L53" s="6" t="s">
+        <v>80</v>
       </c>
       <c r="M53" s="3">
         <v>0</v>
@@ -5304,10 +4712,10 @@
         <v>-1</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="S53" s="5">
         <v>2</v>
@@ -5319,7 +4727,7 @@
         <v>0</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W53" s="5">
         <v>0</v>
@@ -5327,16 +4735,16 @@
       <c r="Y53" s="5">
         <v>0</v>
       </c>
-      <c r="Z53" s="8" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="54" spans="3:26">
+      <c r="Z53" s="9" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C54" s="3">
         <v>10049</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>156</v>
+        <v>128</v>
       </c>
       <c r="E54" s="4">
         <v>2</v>
@@ -5359,8 +4767,8 @@
       <c r="K54" s="4">
         <v>340165</v>
       </c>
-      <c r="L54" s="7" t="s">
-        <v>88</v>
+      <c r="L54" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="M54" s="3">
         <v>0</v>
@@ -5372,10 +4780,10 @@
         <v>-1</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q54" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="S54" s="5">
         <v>2</v>
@@ -5387,7 +4795,7 @@
         <v>0</v>
       </c>
       <c r="V54" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W54" s="5">
         <v>0</v>
@@ -5395,16 +4803,16 @@
       <c r="Y54" s="5">
         <v>0</v>
       </c>
-      <c r="Z54" s="8" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="55" spans="3:26">
+      <c r="Z54" s="9" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C55" s="3">
         <v>10050</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>158</v>
+        <v>129</v>
       </c>
       <c r="E55" s="4">
         <v>2</v>
@@ -5427,8 +4835,8 @@
       <c r="K55" s="4">
         <v>350101</v>
       </c>
-      <c r="L55" s="7" t="s">
-        <v>92</v>
+      <c r="L55" s="6" t="s">
+        <v>86</v>
       </c>
       <c r="M55" s="3">
         <v>0</v>
@@ -5440,10 +4848,10 @@
         <v>-1</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q55" s="3" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="S55" s="5">
         <v>2</v>
@@ -5455,7 +4863,7 @@
         <v>0</v>
       </c>
       <c r="V55" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W55" s="5">
         <v>0</v>
@@ -5463,16 +4871,16 @@
       <c r="Y55" s="5">
         <v>0</v>
       </c>
-      <c r="Z55" s="8" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="56" spans="3:26">
+      <c r="Z55" s="7" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C56" s="3">
         <v>10051</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="E56" s="4">
         <v>2</v>
@@ -5495,8 +4903,8 @@
       <c r="K56" s="4">
         <v>350102</v>
       </c>
-      <c r="L56" s="7" t="s">
-        <v>96</v>
+      <c r="L56" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="M56" s="3">
         <v>0</v>
@@ -5508,10 +4916,10 @@
         <v>-1</v>
       </c>
       <c r="P56" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q56" s="3" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="S56" s="5">
         <v>2</v>
@@ -5523,7 +4931,7 @@
         <v>0</v>
       </c>
       <c r="V56" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W56" s="5">
         <v>0</v>
@@ -5531,16 +4939,16 @@
       <c r="Y56" s="5">
         <v>0</v>
       </c>
-      <c r="Z56" s="8" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="57" spans="3:26">
+      <c r="Z56" s="7" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C57" s="3">
         <v>10052</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="E57" s="4">
         <v>2</v>
@@ -5563,8 +4971,8 @@
       <c r="K57" s="4">
         <v>350103</v>
       </c>
-      <c r="L57" s="7" t="s">
-        <v>74</v>
+      <c r="L57" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="M57" s="3">
         <v>0</v>
@@ -5576,10 +4984,10 @@
         <v>-1</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q57" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="S57" s="5">
         <v>2</v>
@@ -5591,7 +4999,7 @@
         <v>0</v>
       </c>
       <c r="V57" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W57" s="5">
         <v>0</v>
@@ -5599,16 +5007,16 @@
       <c r="Y57" s="5">
         <v>0</v>
       </c>
-      <c r="Z57" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="58" spans="3:26">
+      <c r="Z57" s="7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C58" s="3">
         <v>10053</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>162</v>
+        <v>132</v>
       </c>
       <c r="E58" s="4">
         <v>2</v>
@@ -5631,8 +5039,8 @@
       <c r="K58" s="4">
         <v>350104</v>
       </c>
-      <c r="L58" s="7" t="s">
-        <v>129</v>
+      <c r="L58" s="6" t="s">
+        <v>111</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -5644,10 +5052,10 @@
         <v>-1</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q58" s="3" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="S58" s="5">
         <v>2</v>
@@ -5659,7 +5067,7 @@
         <v>0</v>
       </c>
       <c r="V58" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W58" s="5">
         <v>0</v>
@@ -5667,16 +5075,16 @@
       <c r="Y58" s="5">
         <v>0</v>
       </c>
-      <c r="Z58" s="8" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="59" spans="3:26">
+      <c r="Z58" s="7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C59" s="3">
         <v>10054</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="E59" s="4">
         <v>2</v>
@@ -5699,8 +5107,8 @@
       <c r="K59" s="4">
         <v>350105</v>
       </c>
-      <c r="L59" s="7" t="s">
-        <v>52</v>
+      <c r="L59" s="6" t="s">
+        <v>51</v>
       </c>
       <c r="M59" s="3">
         <v>0</v>
@@ -5712,39 +5120,39 @@
         <v>-1</v>
       </c>
       <c r="P59" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q59" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="Q59" s="3" t="s">
+      <c r="S59" s="5">
+        <v>2</v>
+      </c>
+      <c r="T59" s="5">
+        <v>0</v>
+      </c>
+      <c r="U59" s="5">
+        <v>0</v>
+      </c>
+      <c r="V59" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="S59" s="5">
-        <v>2</v>
-      </c>
-      <c r="T59" s="5">
-        <v>0</v>
-      </c>
-      <c r="U59" s="5">
-        <v>0</v>
-      </c>
-      <c r="V59" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="W59" s="5">
         <v>0</v>
       </c>
       <c r="Y59" s="5">
         <v>0</v>
       </c>
-      <c r="Z59" s="8" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="60" spans="3:26">
+      <c r="Z59" s="7" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C60" s="3">
         <v>10055</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>164</v>
+        <v>134</v>
       </c>
       <c r="E60" s="4">
         <v>2</v>
@@ -5767,8 +5175,8 @@
       <c r="K60" s="4">
         <v>350106</v>
       </c>
-      <c r="L60" s="7" t="s">
-        <v>58</v>
+      <c r="L60" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="M60" s="3">
         <v>0</v>
@@ -5780,10 +5188,10 @@
         <v>-1</v>
       </c>
       <c r="P60" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q60" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S60" s="5">
         <v>2</v>
@@ -5795,7 +5203,7 @@
         <v>0</v>
       </c>
       <c r="V60" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W60" s="5">
         <v>0</v>
@@ -5803,16 +5211,16 @@
       <c r="Y60" s="5">
         <v>0</v>
       </c>
-      <c r="Z60" s="8" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="61" spans="3:26">
+      <c r="Z60" s="7" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C61" s="3">
         <v>10056</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="E61" s="4">
         <v>2</v>
@@ -5835,8 +5243,8 @@
       <c r="K61" s="4">
         <v>350161</v>
       </c>
-      <c r="L61" s="7" t="s">
-        <v>61</v>
+      <c r="L61" s="6" t="s">
+        <v>60</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
@@ -5848,10 +5256,10 @@
         <v>-1</v>
       </c>
       <c r="P61" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q61" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S61" s="5">
         <v>2</v>
@@ -5863,7 +5271,7 @@
         <v>0</v>
       </c>
       <c r="V61" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W61" s="5">
         <v>0</v>
@@ -5871,16 +5279,16 @@
       <c r="Y61" s="5">
         <v>0</v>
       </c>
-      <c r="Z61" s="8" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="62" spans="3:26">
+      <c r="Z61" s="9" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C62" s="3">
         <v>10057</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>167</v>
+        <v>136</v>
       </c>
       <c r="E62" s="4">
         <v>2</v>
@@ -5903,8 +5311,8 @@
       <c r="K62" s="4">
         <v>350162</v>
       </c>
-      <c r="L62" s="7" t="s">
-        <v>64</v>
+      <c r="L62" s="6" t="s">
+        <v>63</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -5916,10 +5324,10 @@
         <v>-1</v>
       </c>
       <c r="P62" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q62" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S62" s="5">
         <v>2</v>
@@ -5931,7 +5339,7 @@
         <v>0</v>
       </c>
       <c r="V62" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W62" s="5">
         <v>0</v>
@@ -5939,16 +5347,16 @@
       <c r="Y62" s="5">
         <v>0</v>
       </c>
-      <c r="Z62" s="8" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="63" spans="3:26">
+      <c r="Z62" s="9" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C63" s="3">
         <v>10058</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>169</v>
+        <v>137</v>
       </c>
       <c r="E63" s="4">
         <v>2</v>
@@ -5971,8 +5379,8 @@
       <c r="K63" s="4">
         <v>350163</v>
       </c>
-      <c r="L63" s="7" t="s">
-        <v>67</v>
+      <c r="L63" s="6" t="s">
+        <v>65</v>
       </c>
       <c r="M63" s="3">
         <v>0</v>
@@ -5984,10 +5392,10 @@
         <v>-1</v>
       </c>
       <c r="P63" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q63" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="S63" s="5">
         <v>2</v>
@@ -5999,7 +5407,7 @@
         <v>0</v>
       </c>
       <c r="V63" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W63" s="5">
         <v>0</v>
@@ -6007,16 +5415,16 @@
       <c r="Y63" s="5">
         <v>0</v>
       </c>
-      <c r="Z63" s="8" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="64" spans="3:26">
+      <c r="Z63" s="9" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C64" s="3">
         <v>10059</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>171</v>
+        <v>138</v>
       </c>
       <c r="E64" s="4">
         <v>2</v>
@@ -6039,8 +5447,8 @@
       <c r="K64" s="4">
         <v>350164</v>
       </c>
-      <c r="L64" s="7" t="s">
-        <v>85</v>
+      <c r="L64" s="6" t="s">
+        <v>80</v>
       </c>
       <c r="M64" s="3">
         <v>0</v>
@@ -6052,10 +5460,10 @@
         <v>-1</v>
       </c>
       <c r="P64" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q64" s="3" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="S64" s="5">
         <v>2</v>
@@ -6067,24 +5475,24 @@
         <v>0</v>
       </c>
       <c r="V64" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="W64" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="W64" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y64" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z64" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="65" spans="3:26">
+    </row>
+    <row r="65" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C65" s="3">
         <v>10060</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="E65" s="4">
         <v>2</v>
@@ -6107,8 +5515,8 @@
       <c r="K65" s="4">
         <v>350165</v>
       </c>
-      <c r="L65" s="7" t="s">
-        <v>88</v>
+      <c r="L65" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="M65" s="3">
         <v>0</v>
@@ -6120,10 +5528,10 @@
         <v>-1</v>
       </c>
       <c r="P65" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="Q65" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="S65" s="5">
         <v>2</v>
@@ -6135,7 +5543,7 @@
         <v>0</v>
       </c>
       <c r="V65" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="W65" s="5">
         <v>0</v>
@@ -6143,16 +5551,16 @@
       <c r="Y65" s="5">
         <v>0</v>
       </c>
-      <c r="Z65" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="66" spans="3:26">
+      <c r="Z65" s="9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="66" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C66" s="3">
         <v>20001</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>174</v>
+        <v>140</v>
       </c>
       <c r="E66" s="3">
         <v>1</v>
@@ -6175,8 +5583,8 @@
       <c r="K66" s="3">
         <v>400001</v>
       </c>
-      <c r="L66" s="7" t="s">
-        <v>175</v>
+      <c r="L66" s="6" t="s">
+        <v>141</v>
       </c>
       <c r="M66" s="5">
         <v>0</v>
@@ -6185,10 +5593,10 @@
         <v>0</v>
       </c>
       <c r="P66" s="1" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
       <c r="Q66" s="3" t="s">
-        <v>177</v>
+        <v>143</v>
       </c>
       <c r="S66" s="5">
         <v>2</v>
@@ -6200,7 +5608,7 @@
         <v>0</v>
       </c>
       <c r="V66" s="1" t="s">
-        <v>178</v>
+        <v>144</v>
       </c>
       <c r="W66" s="1">
         <v>0</v>
@@ -6208,16 +5616,16 @@
       <c r="Y66" s="1">
         <v>0</v>
       </c>
-      <c r="Z66" s="8" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="67" spans="3:26">
+      <c r="Z66" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="67" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C67" s="3">
         <v>20002</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>180</v>
+        <v>145</v>
       </c>
       <c r="E67" s="3">
         <v>1</v>
@@ -6240,8 +5648,8 @@
       <c r="K67" s="3">
         <v>400002</v>
       </c>
-      <c r="L67" s="7" t="s">
-        <v>74</v>
+      <c r="L67" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="M67" s="5">
         <v>0</v>
@@ -6250,10 +5658,10 @@
         <v>0</v>
       </c>
       <c r="P67" s="1" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
       <c r="Q67" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="S67" s="5">
         <v>2</v>
@@ -6265,7 +5673,7 @@
         <v>0</v>
       </c>
       <c r="V67" s="1" t="s">
-        <v>178</v>
+        <v>144</v>
       </c>
       <c r="W67" s="1">
         <v>0</v>
@@ -6273,16 +5681,16 @@
       <c r="Y67" s="1">
         <v>0</v>
       </c>
-      <c r="Z67" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="68" spans="3:26">
+      <c r="Z67" s="7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="68" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C68" s="3">
         <v>20003</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>181</v>
+        <v>146</v>
       </c>
       <c r="E68" s="3">
         <v>1</v>
@@ -6305,8 +5713,8 @@
       <c r="K68" s="3">
         <v>400003</v>
       </c>
-      <c r="L68" s="7" t="s">
-        <v>129</v>
+      <c r="L68" s="6" t="s">
+        <v>111</v>
       </c>
       <c r="M68" s="5">
         <v>0</v>
@@ -6315,10 +5723,10 @@
         <v>0</v>
       </c>
       <c r="P68" s="1" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
       <c r="Q68" s="3" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="S68" s="5">
         <v>2</v>
@@ -6330,7 +5738,7 @@
         <v>0</v>
       </c>
       <c r="V68" s="1" t="s">
-        <v>178</v>
+        <v>144</v>
       </c>
       <c r="W68" s="1">
         <v>0</v>
@@ -6338,16 +5746,16 @@
       <c r="Y68" s="1">
         <v>0</v>
       </c>
-      <c r="Z68" s="8" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="69" spans="3:26">
+      <c r="Z68" s="7" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="69" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C69" s="3">
         <v>20004</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>182</v>
+        <v>147</v>
       </c>
       <c r="E69" s="3">
         <v>1</v>
@@ -6370,21 +5778,21 @@
       <c r="K69" s="3">
         <v>400004</v>
       </c>
-      <c r="L69" s="7" t="s">
+      <c r="L69" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="M69" s="5">
+        <v>0</v>
+      </c>
+      <c r="N69" s="1">
+        <v>0</v>
+      </c>
+      <c r="P69" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q69" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="M69" s="5">
-        <v>0</v>
-      </c>
-      <c r="N69" s="1">
-        <v>0</v>
-      </c>
-      <c r="P69" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q69" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="S69" s="5">
         <v>2</v>
       </c>
@@ -6395,7 +5803,7 @@
         <v>0</v>
       </c>
       <c r="V69" s="1" t="s">
-        <v>178</v>
+        <v>144</v>
       </c>
       <c r="W69" s="1">
         <v>0</v>
@@ -6403,16 +5811,16 @@
       <c r="Y69" s="1">
         <v>0</v>
       </c>
-      <c r="Z69" s="8" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="70" spans="3:26">
+      <c r="Z69" s="7" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="70" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C70" s="3">
         <v>20005</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>183</v>
+        <v>148</v>
       </c>
       <c r="E70" s="3">
         <v>1</v>
@@ -6435,21 +5843,21 @@
       <c r="K70" s="3">
         <v>400005</v>
       </c>
-      <c r="L70" s="7" t="s">
+      <c r="L70" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="M70" s="5">
+        <v>0</v>
+      </c>
+      <c r="N70" s="1">
+        <v>0</v>
+      </c>
+      <c r="P70" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q70" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="M70" s="5">
-        <v>0</v>
-      </c>
-      <c r="N70" s="1">
-        <v>0</v>
-      </c>
-      <c r="P70" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q70" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="S70" s="5">
         <v>2</v>
       </c>
@@ -6460,7 +5868,7 @@
         <v>0</v>
       </c>
       <c r="V70" s="1" t="s">
-        <v>178</v>
+        <v>144</v>
       </c>
       <c r="W70" s="1">
         <v>0</v>
@@ -6468,16 +5876,16 @@
       <c r="Y70" s="1">
         <v>0</v>
       </c>
-      <c r="Z70" s="8" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="71" spans="3:26">
+      <c r="Z70" s="7" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="71" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C71" s="3">
         <v>20006</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>184</v>
+        <v>149</v>
       </c>
       <c r="E71" s="3">
         <v>1</v>
@@ -6500,8 +5908,8 @@
       <c r="K71" s="3">
         <v>400006</v>
       </c>
-      <c r="L71" s="7" t="s">
-        <v>92</v>
+      <c r="L71" s="6" t="s">
+        <v>86</v>
       </c>
       <c r="M71" s="5">
         <v>0</v>
@@ -6510,10 +5918,10 @@
         <v>0</v>
       </c>
       <c r="P71" s="1" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
       <c r="Q71" s="3" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="S71" s="5">
         <v>2</v>
@@ -6525,7 +5933,7 @@
         <v>0</v>
       </c>
       <c r="V71" s="1" t="s">
-        <v>178</v>
+        <v>144</v>
       </c>
       <c r="W71" s="1">
         <v>0</v>
@@ -6533,16 +5941,16 @@
       <c r="Y71" s="1">
         <v>0</v>
       </c>
-      <c r="Z71" s="8" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="72" spans="3:26">
+      <c r="Z71" s="7" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="72" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C72" s="3">
         <v>20007</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>186</v>
+        <v>150</v>
       </c>
       <c r="E72" s="3">
         <v>1</v>
@@ -6565,8 +5973,8 @@
       <c r="K72" s="3">
         <v>400007</v>
       </c>
-      <c r="L72" s="7" t="s">
-        <v>187</v>
+      <c r="L72" s="6" t="s">
+        <v>151</v>
       </c>
       <c r="M72" s="5">
         <v>0</v>
@@ -6575,10 +5983,10 @@
         <v>0</v>
       </c>
       <c r="P72" s="1" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
       <c r="Q72" s="3" t="s">
-        <v>188</v>
+        <v>152</v>
       </c>
       <c r="S72" s="5">
         <v>2</v>
@@ -6590,7 +5998,7 @@
         <v>0</v>
       </c>
       <c r="V72" s="1" t="s">
-        <v>178</v>
+        <v>144</v>
       </c>
       <c r="W72" s="1">
         <v>0</v>
@@ -6598,16 +6006,16 @@
       <c r="Y72" s="1">
         <v>0</v>
       </c>
-      <c r="Z72" s="8" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="73" spans="3:26">
+      <c r="Z72" s="7" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="73" spans="3:26" x14ac:dyDescent="0.3">
       <c r="C73" s="3">
         <v>20008</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>189</v>
+        <v>153</v>
       </c>
       <c r="E73" s="3">
         <v>1</v>
@@ -6630,21 +6038,21 @@
       <c r="K73" s="3">
         <v>400008</v>
       </c>
-      <c r="L73" s="7" t="s">
+      <c r="L73" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="M73" s="5">
+        <v>0</v>
+      </c>
+      <c r="N73" s="1">
+        <v>0</v>
+      </c>
+      <c r="P73" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q73" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="M73" s="5">
-        <v>0</v>
-      </c>
-      <c r="N73" s="1">
-        <v>0</v>
-      </c>
-      <c r="P73" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q73" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="S73" s="5">
         <v>2</v>
       </c>
@@ -6655,7 +6063,7 @@
         <v>0</v>
       </c>
       <c r="V73" s="1" t="s">
-        <v>178</v>
+        <v>144</v>
       </c>
       <c r="W73" s="1">
         <v>0</v>
@@ -6663,119 +6071,119 @@
       <c r="Y73" s="1">
         <v>0</v>
       </c>
-      <c r="Z73" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="74" spans="4:4">
+      <c r="Z73" s="7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="74" spans="3:26" x14ac:dyDescent="0.3">
       <c r="D74" s="4"/>
     </row>
-    <row r="75" spans="4:4">
+    <row r="75" spans="3:26" x14ac:dyDescent="0.3">
       <c r="D75" s="4"/>
     </row>
-    <row r="76" spans="4:4">
+    <row r="76" spans="3:26" x14ac:dyDescent="0.3">
       <c r="D76" s="4"/>
     </row>
-    <row r="77" spans="4:4">
+    <row r="77" spans="3:26" x14ac:dyDescent="0.3">
       <c r="D77" s="4"/>
     </row>
-    <row r="78" spans="4:4">
+    <row r="78" spans="3:26" x14ac:dyDescent="0.3">
       <c r="D78" s="4"/>
     </row>
-    <row r="79" spans="4:4">
+    <row r="79" spans="3:26" x14ac:dyDescent="0.3">
       <c r="D79" s="4"/>
     </row>
-    <row r="80" spans="4:4">
+    <row r="80" spans="3:26" x14ac:dyDescent="0.3">
       <c r="D80" s="4"/>
     </row>
-    <row r="81" spans="4:4">
+    <row r="81" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D81" s="4"/>
     </row>
-    <row r="82" spans="4:4">
+    <row r="82" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D82" s="4"/>
     </row>
-    <row r="83" spans="4:4">
+    <row r="83" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D83" s="4"/>
     </row>
-    <row r="84" spans="4:4">
+    <row r="84" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D84" s="4"/>
     </row>
-    <row r="85" spans="4:4">
+    <row r="85" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D85" s="4"/>
     </row>
-    <row r="86" spans="4:4">
+    <row r="86" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D86" s="4"/>
     </row>
-    <row r="87" spans="4:4">
+    <row r="87" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D87" s="4"/>
     </row>
-    <row r="88" spans="4:4">
+    <row r="88" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D88" s="4"/>
     </row>
-    <row r="89" spans="4:4">
+    <row r="89" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D89" s="4"/>
     </row>
-    <row r="90" spans="4:4">
+    <row r="90" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D90" s="4"/>
     </row>
-    <row r="91" spans="4:4">
+    <row r="91" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D91" s="4"/>
     </row>
-    <row r="92" spans="4:4">
+    <row r="92" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D92" s="4"/>
     </row>
-    <row r="93" spans="4:4">
+    <row r="93" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D93" s="4"/>
     </row>
-    <row r="94" spans="4:4">
+    <row r="94" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D94" s="4"/>
     </row>
-    <row r="95" spans="4:4">
+    <row r="95" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D95" s="4"/>
     </row>
-    <row r="96" spans="4:4">
+    <row r="96" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D96" s="4"/>
     </row>
-    <row r="97" spans="4:4">
+    <row r="97" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D97" s="4"/>
     </row>
-    <row r="98" spans="4:4">
+    <row r="98" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D98" s="4"/>
     </row>
-    <row r="99" spans="4:4">
+    <row r="99" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D99" s="4"/>
     </row>
-    <row r="100" spans="4:4">
+    <row r="100" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D100" s="4"/>
     </row>
-    <row r="101" spans="4:4">
+    <row r="101" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D101" s="4"/>
     </row>
-    <row r="102" spans="4:4">
+    <row r="102" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D102" s="4"/>
     </row>
-    <row r="103" spans="4:4">
+    <row r="103" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D103" s="4"/>
     </row>
-    <row r="104" spans="4:4">
+    <row r="104" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D104" s="4"/>
     </row>
-    <row r="105" spans="4:4">
+    <row r="105" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D105" s="4"/>
     </row>
-    <row r="106" spans="4:4">
+    <row r="106" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D106" s="4"/>
     </row>
-    <row r="107" spans="4:4">
+    <row r="107" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D107" s="4"/>
     </row>
-    <row r="108" spans="4:4">
+    <row r="108" spans="4:4" x14ac:dyDescent="0.3">
       <c r="D108" s="4"/>
     </row>
   </sheetData>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Unity/Assets/Config/Excel/JingLingConfig.xlsx
+++ b/Unity/Assets/Config/Excel/JingLingConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitMengJing\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FB02C76-2E11-476A-AAB4-56B6A5F21E31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E63EF601-8EE2-4436-A27D-45159CB87045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,6 +33,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:</t>
@@ -41,6 +42,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -57,6 +59,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:</t>
@@ -65,6 +68,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -82,6 +86,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -90,6 +95,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -105,6 +111,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>1.每天随机给东西   参数:掉落ID
@@ -124,6 +131,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:</t>
@@ -132,6 +140,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -147,6 +156,7 @@
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Admin:</t>
@@ -155,6 +165,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -322,9 +333,6 @@
     <t>double</t>
   </si>
   <si>
-    <t>史莱姆</t>
-  </si>
-  <si>
     <t>100403;50</t>
   </si>
   <si>
@@ -524,9 +532,6 @@
   </si>
   <si>
     <t>冰灵蜘蛛</t>
-  </si>
-  <si>
-    <t>雪狼</t>
   </si>
   <si>
     <t>冰灵山羊</t>
@@ -742,6 +747,14 @@
   </si>
   <si>
     <t>森灵守卫者</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>软泥怪</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰狼</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -761,6 +774,7 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -768,12 +782,14 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -781,23 +797,27 @@
       <sz val="10"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1371,7 +1391,7 @@
         <v>36</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="R4" s="2" t="s">
         <v>37</v>
@@ -1480,7 +1500,7 @@
         <v>10001</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>50</v>
+        <v>188</v>
       </c>
       <c r="E6" s="4">
         <v>2</v>
@@ -1504,7 +1524,7 @@
         <v>310101</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M6" s="3">
         <v>0</v>
@@ -1516,23 +1536,23 @@
         <v>-1</v>
       </c>
       <c r="P6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q6" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="Q6" s="3" t="s">
+      <c r="S6" s="5">
+        <v>2</v>
+      </c>
+      <c r="T6" s="5">
+        <v>0</v>
+      </c>
+      <c r="U6" s="5">
+        <v>0</v>
+      </c>
+      <c r="V6" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="S6" s="5">
-        <v>2</v>
-      </c>
-      <c r="T6" s="5">
-        <v>0</v>
-      </c>
-      <c r="U6" s="5">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="W6" s="5">
         <v>0</v>
       </c>
@@ -1540,7 +1560,7 @@
         <v>0</v>
       </c>
       <c r="Z6" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="3:26" x14ac:dyDescent="0.3">
@@ -1548,7 +1568,7 @@
         <v>10002</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E7" s="4">
         <v>2</v>
@@ -1572,7 +1592,7 @@
         <v>310102</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M7" s="3">
         <v>0</v>
@@ -1584,10 +1604,10 @@
         <v>-1</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="S7" s="5">
         <v>2</v>
@@ -1599,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="V7" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W7" s="5">
         <v>0</v>
@@ -1608,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="Z7" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="3:26" x14ac:dyDescent="0.3">
@@ -1616,7 +1636,7 @@
         <v>10003</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E8" s="4">
         <v>2</v>
@@ -1640,7 +1660,7 @@
         <v>310103</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -1652,10 +1672,10 @@
         <v>-1</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S8" s="5">
         <v>2</v>
@@ -1667,7 +1687,7 @@
         <v>0</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W8" s="5">
         <v>0</v>
@@ -1676,7 +1696,7 @@
         <v>0</v>
       </c>
       <c r="Z8" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="3:26" x14ac:dyDescent="0.3">
@@ -1684,7 +1704,7 @@
         <v>10004</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E9" s="4">
         <v>2</v>
@@ -1708,7 +1728,7 @@
         <v>310104</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M9" s="3">
         <v>0</v>
@@ -1720,10 +1740,10 @@
         <v>-1</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S9" s="5">
         <v>2</v>
@@ -1735,7 +1755,7 @@
         <v>0</v>
       </c>
       <c r="V9" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W9" s="5">
         <v>0</v>
@@ -1744,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="Z9" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="3:26" x14ac:dyDescent="0.3">
@@ -1752,7 +1772,7 @@
         <v>10005</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E10" s="4">
         <v>2</v>
@@ -1776,7 +1796,7 @@
         <v>310105</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M10" s="3">
         <v>0</v>
@@ -1788,10 +1808,10 @@
         <v>-1</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="S10" s="5">
         <v>2</v>
@@ -1803,7 +1823,7 @@
         <v>0</v>
       </c>
       <c r="V10" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W10" s="5">
         <v>0</v>
@@ -1812,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="Z10" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="3:26" x14ac:dyDescent="0.3">
@@ -1820,7 +1840,7 @@
         <v>10006</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E11" s="4">
         <v>2</v>
@@ -1844,7 +1864,7 @@
         <v>310106</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M11" s="3">
         <v>0</v>
@@ -1856,10 +1876,10 @@
         <v>-1</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S11" s="5">
         <v>2</v>
@@ -1871,7 +1891,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W11" s="5">
         <v>0</v>
@@ -1880,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="Z11" s="7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="3:26" x14ac:dyDescent="0.3">
@@ -1888,7 +1908,7 @@
         <v>10007</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E12" s="4">
         <v>2</v>
@@ -1912,7 +1932,7 @@
         <v>310107</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M12" s="3">
         <v>0</v>
@@ -1924,10 +1944,10 @@
         <v>-1</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S12" s="5">
         <v>2</v>
@@ -1939,7 +1959,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W12" s="5">
         <v>0</v>
@@ -1948,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="Z12" s="7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="3:26" x14ac:dyDescent="0.3">
@@ -1956,7 +1976,7 @@
         <v>10008</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E13" s="4">
         <v>2</v>
@@ -1980,7 +2000,7 @@
         <v>310160</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M13" s="3">
         <v>0</v>
@@ -1992,11 +2012,11 @@
         <v>-1</v>
       </c>
       <c r="P13" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q13" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="Q13" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="S13" s="5">
         <v>2</v>
       </c>
@@ -2007,16 +2027,16 @@
         <v>0</v>
       </c>
       <c r="V13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="W13" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="9" t="s">
         <v>54</v>
-      </c>
-      <c r="W13" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="9" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="14" spans="3:26" x14ac:dyDescent="0.3">
@@ -2024,7 +2044,7 @@
         <v>10009</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="E14" s="4">
         <v>2</v>
@@ -2048,7 +2068,7 @@
         <v>310161</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -2060,10 +2080,10 @@
         <v>-1</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S14" s="5">
         <v>2</v>
@@ -2075,16 +2095,16 @@
         <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="W14" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="9" t="s">
         <v>54</v>
-      </c>
-      <c r="W14" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="9" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="15" spans="3:26" x14ac:dyDescent="0.3">
@@ -2092,7 +2112,7 @@
         <v>10010</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E15" s="4">
         <v>2</v>
@@ -2116,7 +2136,7 @@
         <v>310162</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -2128,10 +2148,10 @@
         <v>-1</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S15" s="5">
         <v>2</v>
@@ -2143,16 +2163,16 @@
         <v>0</v>
       </c>
       <c r="V15" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="W15" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="9" t="s">
         <v>54</v>
-      </c>
-      <c r="W15" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="9" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="16" spans="3:26" x14ac:dyDescent="0.3">
@@ -2160,7 +2180,7 @@
         <v>10011</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E16" s="4">
         <v>2</v>
@@ -2184,7 +2204,7 @@
         <v>310163</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M16" s="3">
         <v>0</v>
@@ -2196,10 +2216,10 @@
         <v>-1</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S16" s="5">
         <v>2</v>
@@ -2211,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="V16" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W16" s="5">
         <v>0</v>
@@ -2220,7 +2240,7 @@
         <v>0</v>
       </c>
       <c r="Z16" s="9" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="17" spans="3:26" x14ac:dyDescent="0.3">
@@ -2228,7 +2248,7 @@
         <v>10012</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E17" s="4">
         <v>2</v>
@@ -2252,7 +2272,7 @@
         <v>310164</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M17" s="3">
         <v>0</v>
@@ -2264,10 +2284,10 @@
         <v>-1</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="S17" s="5">
         <v>2</v>
@@ -2279,7 +2299,7 @@
         <v>0</v>
       </c>
       <c r="V17" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W17" s="5">
         <v>0</v>
@@ -2288,7 +2308,7 @@
         <v>0</v>
       </c>
       <c r="Z17" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18" spans="3:26" x14ac:dyDescent="0.3">
@@ -2296,7 +2316,7 @@
         <v>10013</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E18" s="4">
         <v>2</v>
@@ -2320,7 +2340,7 @@
         <v>310165</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M18" s="3">
         <v>0</v>
@@ -2332,10 +2352,10 @@
         <v>-1</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="S18" s="5">
         <v>2</v>
@@ -2347,7 +2367,7 @@
         <v>0</v>
       </c>
       <c r="V18" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W18" s="5">
         <v>0</v>
@@ -2356,7 +2376,7 @@
         <v>0</v>
       </c>
       <c r="Z18" s="9" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="19" spans="3:26" x14ac:dyDescent="0.3">
@@ -2364,7 +2384,7 @@
         <v>10014</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E19" s="4">
         <v>2</v>
@@ -2388,7 +2408,7 @@
         <v>320101</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M19" s="3">
         <v>0</v>
@@ -2400,23 +2420,23 @@
         <v>-1</v>
       </c>
       <c r="P19" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q19" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="Q19" s="3" t="s">
+      <c r="S19" s="5">
+        <v>2</v>
+      </c>
+      <c r="T19" s="5">
+        <v>0</v>
+      </c>
+      <c r="U19" s="5">
+        <v>0</v>
+      </c>
+      <c r="V19" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="S19" s="5">
-        <v>2</v>
-      </c>
-      <c r="T19" s="5">
-        <v>0</v>
-      </c>
-      <c r="U19" s="5">
-        <v>0</v>
-      </c>
-      <c r="V19" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="W19" s="5">
         <v>0</v>
       </c>
@@ -2424,7 +2444,7 @@
         <v>0</v>
       </c>
       <c r="Z19" s="7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="20" spans="3:26" x14ac:dyDescent="0.3">
@@ -2432,7 +2452,7 @@
         <v>10015</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E20" s="4">
         <v>2</v>
@@ -2456,7 +2476,7 @@
         <v>320102</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -2468,10 +2488,10 @@
         <v>-1</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="S20" s="5">
         <v>2</v>
@@ -2483,7 +2503,7 @@
         <v>0</v>
       </c>
       <c r="V20" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W20" s="5">
         <v>0</v>
@@ -2492,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="Z20" s="7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21" spans="3:26" x14ac:dyDescent="0.3">
@@ -2500,7 +2520,7 @@
         <v>10016</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E21" s="4">
         <v>2</v>
@@ -2524,7 +2544,7 @@
         <v>320103</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M21" s="3">
         <v>0</v>
@@ -2536,10 +2556,10 @@
         <v>-1</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S21" s="5">
         <v>2</v>
@@ -2551,7 +2571,7 @@
         <v>0</v>
       </c>
       <c r="V21" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W21" s="5">
         <v>0</v>
@@ -2560,7 +2580,7 @@
         <v>0</v>
       </c>
       <c r="Z21" s="7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="22" spans="3:26" x14ac:dyDescent="0.3">
@@ -2568,7 +2588,7 @@
         <v>10017</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E22" s="4">
         <v>2</v>
@@ -2592,7 +2612,7 @@
         <v>320104</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -2604,10 +2624,10 @@
         <v>-1</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S22" s="5">
         <v>2</v>
@@ -2619,7 +2639,7 @@
         <v>0</v>
       </c>
       <c r="V22" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W22" s="5">
         <v>0</v>
@@ -2628,7 +2648,7 @@
         <v>0</v>
       </c>
       <c r="Z22" s="7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" spans="3:26" x14ac:dyDescent="0.3">
@@ -2636,7 +2656,7 @@
         <v>10018</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E23" s="4">
         <v>2</v>
@@ -2660,7 +2680,7 @@
         <v>320105</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M23" s="3">
         <v>0</v>
@@ -2672,10 +2692,10 @@
         <v>-1</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="S23" s="5">
         <v>2</v>
@@ -2687,7 +2707,7 @@
         <v>0</v>
       </c>
       <c r="V23" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W23" s="5">
         <v>0</v>
@@ -2696,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="Z23" s="7" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="24" spans="3:26" x14ac:dyDescent="0.3">
@@ -2704,7 +2724,7 @@
         <v>10019</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E24" s="4">
         <v>2</v>
@@ -2728,7 +2748,7 @@
         <v>320106</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -2740,23 +2760,23 @@
         <v>-1</v>
       </c>
       <c r="P24" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q24" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="Q24" s="3" t="s">
+      <c r="S24" s="5">
+        <v>2</v>
+      </c>
+      <c r="T24" s="5">
+        <v>0</v>
+      </c>
+      <c r="U24" s="5">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="S24" s="5">
-        <v>2</v>
-      </c>
-      <c r="T24" s="5">
-        <v>0</v>
-      </c>
-      <c r="U24" s="5">
-        <v>0</v>
-      </c>
-      <c r="V24" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="W24" s="5">
         <v>0</v>
       </c>
@@ -2764,7 +2784,7 @@
         <v>0</v>
       </c>
       <c r="Z24" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="25" spans="3:26" x14ac:dyDescent="0.3">
@@ -2772,7 +2792,7 @@
         <v>10020</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E25" s="4">
         <v>2</v>
@@ -2796,7 +2816,7 @@
         <v>320107</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M25" s="3">
         <v>0</v>
@@ -2808,10 +2828,10 @@
         <v>-1</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q25" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="S25" s="5">
         <v>2</v>
@@ -2823,7 +2843,7 @@
         <v>0</v>
       </c>
       <c r="V25" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W25" s="5">
         <v>0</v>
@@ -2832,7 +2852,7 @@
         <v>0</v>
       </c>
       <c r="Z25" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26" spans="3:26" x14ac:dyDescent="0.3">
@@ -2840,7 +2860,7 @@
         <v>10021</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E26" s="4">
         <v>2</v>
@@ -2864,7 +2884,7 @@
         <v>320161</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M26" s="3">
         <v>0</v>
@@ -2876,10 +2896,10 @@
         <v>-1</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q26" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S26" s="5">
         <v>2</v>
@@ -2891,7 +2911,7 @@
         <v>0</v>
       </c>
       <c r="V26" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W26" s="5">
         <v>0</v>
@@ -2900,7 +2920,7 @@
         <v>0</v>
       </c>
       <c r="Z26" s="9" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="3:26" x14ac:dyDescent="0.3">
@@ -2908,7 +2928,7 @@
         <v>10022</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E27" s="4">
         <v>2</v>
@@ -2932,7 +2952,7 @@
         <v>320162</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M27" s="3">
         <v>0</v>
@@ -2944,10 +2964,10 @@
         <v>-1</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S27" s="5">
         <v>2</v>
@@ -2959,7 +2979,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W27" s="5">
         <v>0</v>
@@ -2968,7 +2988,7 @@
         <v>0</v>
       </c>
       <c r="Z27" s="9" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="28" spans="3:26" x14ac:dyDescent="0.3">
@@ -2976,7 +2996,7 @@
         <v>10023</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E28" s="4">
         <v>2</v>
@@ -3000,7 +3020,7 @@
         <v>320163</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M28" s="3">
         <v>0</v>
@@ -3012,10 +3032,10 @@
         <v>-1</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q28" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="S28" s="5">
         <v>2</v>
@@ -3027,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="V28" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W28" s="5">
         <v>0</v>
@@ -3036,7 +3056,7 @@
         <v>0</v>
       </c>
       <c r="Z28" s="9" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="29" spans="3:26" x14ac:dyDescent="0.3">
@@ -3044,7 +3064,7 @@
         <v>10024</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E29" s="4">
         <v>2</v>
@@ -3068,7 +3088,7 @@
         <v>320164</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -3080,10 +3100,10 @@
         <v>-1</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q29" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S29" s="5">
         <v>2</v>
@@ -3095,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W29" s="5">
         <v>0</v>
@@ -3104,7 +3124,7 @@
         <v>0</v>
       </c>
       <c r="Z29" s="9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="30" spans="3:26" x14ac:dyDescent="0.3">
@@ -3112,7 +3132,7 @@
         <v>10025</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E30" s="4">
         <v>2</v>
@@ -3136,7 +3156,7 @@
         <v>320165</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M30" s="3">
         <v>0</v>
@@ -3148,10 +3168,10 @@
         <v>-1</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q30" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S30" s="5">
         <v>2</v>
@@ -3163,7 +3183,7 @@
         <v>0</v>
       </c>
       <c r="V30" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W30" s="5">
         <v>0</v>
@@ -3172,7 +3192,7 @@
         <v>0</v>
       </c>
       <c r="Z30" s="9" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="31" spans="3:26" x14ac:dyDescent="0.3">
@@ -3180,7 +3200,7 @@
         <v>10026</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E31" s="4">
         <v>2</v>
@@ -3204,7 +3224,7 @@
         <v>330101</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M31" s="3">
         <v>0</v>
@@ -3216,10 +3236,10 @@
         <v>-1</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q31" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="S31" s="5">
         <v>2</v>
@@ -3231,7 +3251,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W31" s="5">
         <v>0</v>
@@ -3240,7 +3260,7 @@
         <v>0</v>
       </c>
       <c r="Z31" s="7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="32" spans="3:26" x14ac:dyDescent="0.3">
@@ -3248,7 +3268,7 @@
         <v>10027</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E32" s="4">
         <v>2</v>
@@ -3272,7 +3292,7 @@
         <v>330102</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -3284,10 +3304,10 @@
         <v>-1</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q32" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S32" s="5">
         <v>2</v>
@@ -3299,7 +3319,7 @@
         <v>0</v>
       </c>
       <c r="V32" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W32" s="5">
         <v>0</v>
@@ -3308,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="Z32" s="7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="33" spans="3:26" x14ac:dyDescent="0.3">
@@ -3316,7 +3336,7 @@
         <v>10028</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E33" s="4">
         <v>2</v>
@@ -3340,7 +3360,7 @@
         <v>330103</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M33" s="3">
         <v>0</v>
@@ -3352,10 +3372,10 @@
         <v>-1</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q33" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S33" s="5">
         <v>2</v>
@@ -3367,7 +3387,7 @@
         <v>0</v>
       </c>
       <c r="V33" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W33" s="5">
         <v>0</v>
@@ -3376,7 +3396,7 @@
         <v>0</v>
       </c>
       <c r="Z33" s="7" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="34" spans="3:26" x14ac:dyDescent="0.3">
@@ -3384,7 +3404,7 @@
         <v>10029</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E34" s="4">
         <v>2</v>
@@ -3408,7 +3428,7 @@
         <v>330104</v>
       </c>
       <c r="L34" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M34" s="3">
         <v>0</v>
@@ -3420,10 +3440,10 @@
         <v>-1</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q34" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S34" s="5">
         <v>2</v>
@@ -3435,7 +3455,7 @@
         <v>0</v>
       </c>
       <c r="V34" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W34" s="5">
         <v>0</v>
@@ -3444,7 +3464,7 @@
         <v>0</v>
       </c>
       <c r="Z34" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="35" spans="3:26" x14ac:dyDescent="0.3">
@@ -3452,7 +3472,7 @@
         <v>10030</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E35" s="4">
         <v>2</v>
@@ -3476,7 +3496,7 @@
         <v>330105</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M35" s="3">
         <v>0</v>
@@ -3488,10 +3508,10 @@
         <v>-1</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q35" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="S35" s="5">
         <v>2</v>
@@ -3503,7 +3523,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W35" s="5">
         <v>0</v>
@@ -3512,7 +3532,7 @@
         <v>0</v>
       </c>
       <c r="Z35" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="36" spans="3:26" x14ac:dyDescent="0.3">
@@ -3520,7 +3540,7 @@
         <v>10031</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E36" s="4">
         <v>2</v>
@@ -3544,7 +3564,7 @@
         <v>330106</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M36" s="3">
         <v>0</v>
@@ -3556,10 +3576,10 @@
         <v>-1</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q36" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="S36" s="5">
         <v>2</v>
@@ -3571,7 +3591,7 @@
         <v>0</v>
       </c>
       <c r="V36" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W36" s="5">
         <v>0</v>
@@ -3580,7 +3600,7 @@
         <v>0</v>
       </c>
       <c r="Z36" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="37" spans="3:26" x14ac:dyDescent="0.3">
@@ -3588,7 +3608,7 @@
         <v>10032</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E37" s="4">
         <v>2</v>
@@ -3612,7 +3632,7 @@
         <v>330107</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M37" s="3">
         <v>0</v>
@@ -3624,10 +3644,10 @@
         <v>-1</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q37" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S37" s="5">
         <v>2</v>
@@ -3639,7 +3659,7 @@
         <v>0</v>
       </c>
       <c r="V37" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W37" s="5">
         <v>0</v>
@@ -3648,7 +3668,7 @@
         <v>0</v>
       </c>
       <c r="Z37" s="7" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="38" spans="3:26" x14ac:dyDescent="0.3">
@@ -3656,7 +3676,7 @@
         <v>10033</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E38" s="4">
         <v>2</v>
@@ -3680,7 +3700,7 @@
         <v>330161</v>
       </c>
       <c r="L38" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M38" s="3">
         <v>0</v>
@@ -3692,10 +3712,10 @@
         <v>-1</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q38" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="S38" s="5">
         <v>2</v>
@@ -3707,7 +3727,7 @@
         <v>0</v>
       </c>
       <c r="V38" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W38" s="5">
         <v>0</v>
@@ -3716,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="Z38" s="9" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="39" spans="3:26" x14ac:dyDescent="0.3">
@@ -3724,7 +3744,7 @@
         <v>10034</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E39" s="4">
         <v>2</v>
@@ -3748,7 +3768,7 @@
         <v>330162</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M39" s="3">
         <v>0</v>
@@ -3760,23 +3780,23 @@
         <v>-1</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q39" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="S39" s="5">
+        <v>2</v>
+      </c>
+      <c r="T39" s="5">
+        <v>0</v>
+      </c>
+      <c r="U39" s="5">
+        <v>0</v>
+      </c>
+      <c r="V39" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="S39" s="5">
-        <v>2</v>
-      </c>
-      <c r="T39" s="5">
-        <v>0</v>
-      </c>
-      <c r="U39" s="5">
-        <v>0</v>
-      </c>
-      <c r="V39" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="W39" s="5">
         <v>0</v>
       </c>
@@ -3784,7 +3804,7 @@
         <v>0</v>
       </c>
       <c r="Z39" s="9" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="40" spans="3:26" x14ac:dyDescent="0.3">
@@ -3792,7 +3812,7 @@
         <v>10035</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E40" s="4">
         <v>2</v>
@@ -3816,7 +3836,7 @@
         <v>330163</v>
       </c>
       <c r="L40" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M40" s="3">
         <v>0</v>
@@ -3828,10 +3848,10 @@
         <v>-1</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q40" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="S40" s="5">
         <v>2</v>
@@ -3843,7 +3863,7 @@
         <v>0</v>
       </c>
       <c r="V40" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W40" s="5">
         <v>0</v>
@@ -3852,7 +3872,7 @@
         <v>0</v>
       </c>
       <c r="Z40" s="9" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="41" spans="3:26" x14ac:dyDescent="0.3">
@@ -3860,7 +3880,7 @@
         <v>10036</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E41" s="4">
         <v>2</v>
@@ -3884,7 +3904,7 @@
         <v>330164</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M41" s="3">
         <v>0</v>
@@ -3896,10 +3916,10 @@
         <v>-1</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q41" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S41" s="5">
         <v>2</v>
@@ -3911,7 +3931,7 @@
         <v>0</v>
       </c>
       <c r="V41" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W41" s="5">
         <v>0</v>
@@ -3920,7 +3940,7 @@
         <v>0</v>
       </c>
       <c r="Z41" s="9" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="42" spans="3:26" x14ac:dyDescent="0.3">
@@ -3928,7 +3948,7 @@
         <v>10037</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E42" s="4">
         <v>2</v>
@@ -3952,7 +3972,7 @@
         <v>330165</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M42" s="3">
         <v>0</v>
@@ -3964,10 +3984,10 @@
         <v>-1</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q42" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S42" s="5">
         <v>2</v>
@@ -3979,7 +3999,7 @@
         <v>0</v>
       </c>
       <c r="V42" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W42" s="5">
         <v>0</v>
@@ -3988,7 +4008,7 @@
         <v>0</v>
       </c>
       <c r="Z42" s="9" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="43" spans="3:26" x14ac:dyDescent="0.3">
@@ -3996,7 +4016,7 @@
         <v>10038</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E43" s="4">
         <v>2</v>
@@ -4020,7 +4040,7 @@
         <v>340101</v>
       </c>
       <c r="L43" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -4032,10 +4052,10 @@
         <v>-1</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q43" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="S43" s="5">
         <v>2</v>
@@ -4047,7 +4067,7 @@
         <v>0</v>
       </c>
       <c r="V43" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W43" s="5">
         <v>0</v>
@@ -4056,7 +4076,7 @@
         <v>0</v>
       </c>
       <c r="Z43" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="44" spans="3:26" x14ac:dyDescent="0.3">
@@ -4064,7 +4084,7 @@
         <v>10039</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>118</v>
+        <v>189</v>
       </c>
       <c r="E44" s="4">
         <v>2</v>
@@ -4088,7 +4108,7 @@
         <v>340102</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4100,23 +4120,23 @@
         <v>-1</v>
       </c>
       <c r="P44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q44" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="Q44" s="3" t="s">
+      <c r="S44" s="5">
+        <v>2</v>
+      </c>
+      <c r="T44" s="5">
+        <v>0</v>
+      </c>
+      <c r="U44" s="5">
+        <v>0</v>
+      </c>
+      <c r="V44" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="S44" s="5">
-        <v>2</v>
-      </c>
-      <c r="T44" s="5">
-        <v>0</v>
-      </c>
-      <c r="U44" s="5">
-        <v>0</v>
-      </c>
-      <c r="V44" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="W44" s="5">
         <v>0</v>
       </c>
@@ -4124,7 +4144,7 @@
         <v>0</v>
       </c>
       <c r="Z44" s="7" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="45" spans="3:26" x14ac:dyDescent="0.3">
@@ -4132,7 +4152,7 @@
         <v>10040</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E45" s="4">
         <v>2</v>
@@ -4156,7 +4176,7 @@
         <v>340103</v>
       </c>
       <c r="L45" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M45" s="3">
         <v>0</v>
@@ -4168,10 +4188,10 @@
         <v>-1</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q45" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="S45" s="5">
         <v>2</v>
@@ -4183,7 +4203,7 @@
         <v>0</v>
       </c>
       <c r="V45" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W45" s="5">
         <v>0</v>
@@ -4192,7 +4212,7 @@
         <v>0</v>
       </c>
       <c r="Z45" s="7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="46" spans="3:26" x14ac:dyDescent="0.3">
@@ -4200,7 +4220,7 @@
         <v>10041</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E46" s="4">
         <v>2</v>
@@ -4224,7 +4244,7 @@
         <v>340104</v>
       </c>
       <c r="L46" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M46" s="3">
         <v>0</v>
@@ -4236,10 +4256,10 @@
         <v>-1</v>
       </c>
       <c r="P46" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q46" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S46" s="5">
         <v>2</v>
@@ -4251,7 +4271,7 @@
         <v>0</v>
       </c>
       <c r="V46" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W46" s="5">
         <v>0</v>
@@ -4260,7 +4280,7 @@
         <v>0</v>
       </c>
       <c r="Z46" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="47" spans="3:26" x14ac:dyDescent="0.3">
@@ -4268,7 +4288,7 @@
         <v>10042</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E47" s="4">
         <v>2</v>
@@ -4292,7 +4312,7 @@
         <v>340105</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4304,10 +4324,10 @@
         <v>-1</v>
       </c>
       <c r="P47" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q47" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S47" s="5">
         <v>2</v>
@@ -4319,7 +4339,7 @@
         <v>0</v>
       </c>
       <c r="V47" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W47" s="5">
         <v>0</v>
@@ -4328,7 +4348,7 @@
         <v>0</v>
       </c>
       <c r="Z47" s="7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="48" spans="3:26" x14ac:dyDescent="0.3">
@@ -4336,7 +4356,7 @@
         <v>10043</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E48" s="4">
         <v>2</v>
@@ -4360,7 +4380,7 @@
         <v>340106</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M48" s="3">
         <v>0</v>
@@ -4372,10 +4392,10 @@
         <v>-1</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q48" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="S48" s="5">
         <v>2</v>
@@ -4387,7 +4407,7 @@
         <v>0</v>
       </c>
       <c r="V48" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W48" s="5">
         <v>0</v>
@@ -4396,7 +4416,7 @@
         <v>0</v>
       </c>
       <c r="Z48" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="49" spans="3:26" x14ac:dyDescent="0.3">
@@ -4404,7 +4424,7 @@
         <v>10044</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E49" s="4">
         <v>2</v>
@@ -4428,7 +4448,7 @@
         <v>340107</v>
       </c>
       <c r="L49" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M49" s="3">
         <v>0</v>
@@ -4440,10 +4460,10 @@
         <v>-1</v>
       </c>
       <c r="P49" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q49" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S49" s="5">
         <v>2</v>
@@ -4455,7 +4475,7 @@
         <v>0</v>
       </c>
       <c r="V49" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W49" s="5">
         <v>0</v>
@@ -4464,7 +4484,7 @@
         <v>0</v>
       </c>
       <c r="Z49" s="7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="50" spans="3:26" x14ac:dyDescent="0.3">
@@ -4472,7 +4492,7 @@
         <v>10045</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E50" s="4">
         <v>2</v>
@@ -4496,7 +4516,7 @@
         <v>340161</v>
       </c>
       <c r="L50" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M50" s="3">
         <v>0</v>
@@ -4508,10 +4528,10 @@
         <v>-1</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q50" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S50" s="5">
         <v>2</v>
@@ -4523,7 +4543,7 @@
         <v>0</v>
       </c>
       <c r="V50" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W50" s="5">
         <v>0</v>
@@ -4532,7 +4552,7 @@
         <v>0</v>
       </c>
       <c r="Z50" s="9" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="51" spans="3:26" x14ac:dyDescent="0.3">
@@ -4540,7 +4560,7 @@
         <v>10046</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E51" s="4">
         <v>2</v>
@@ -4564,7 +4584,7 @@
         <v>340162</v>
       </c>
       <c r="L51" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M51" s="3">
         <v>0</v>
@@ -4576,11 +4596,11 @@
         <v>-1</v>
       </c>
       <c r="P51" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q51" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="Q51" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="S51" s="5">
         <v>2</v>
       </c>
@@ -4591,7 +4611,7 @@
         <v>0</v>
       </c>
       <c r="V51" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W51" s="5">
         <v>0</v>
@@ -4600,7 +4620,7 @@
         <v>0</v>
       </c>
       <c r="Z51" s="9" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="52" spans="3:26" x14ac:dyDescent="0.3">
@@ -4608,7 +4628,7 @@
         <v>10047</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E52" s="4">
         <v>2</v>
@@ -4632,7 +4652,7 @@
         <v>340163</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -4644,10 +4664,10 @@
         <v>-1</v>
       </c>
       <c r="P52" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q52" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S52" s="5">
         <v>2</v>
@@ -4659,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="V52" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W52" s="5">
         <v>0</v>
@@ -4668,7 +4688,7 @@
         <v>0</v>
       </c>
       <c r="Z52" s="9" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="53" spans="3:26" x14ac:dyDescent="0.3">
@@ -4676,7 +4696,7 @@
         <v>10048</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E53" s="4">
         <v>2</v>
@@ -4700,7 +4720,7 @@
         <v>340164</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M53" s="3">
         <v>0</v>
@@ -4712,10 +4732,10 @@
         <v>-1</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S53" s="5">
         <v>2</v>
@@ -4727,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="V53" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W53" s="5">
         <v>0</v>
@@ -4736,7 +4756,7 @@
         <v>0</v>
       </c>
       <c r="Z53" s="9" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="54" spans="3:26" x14ac:dyDescent="0.3">
@@ -4744,7 +4764,7 @@
         <v>10049</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E54" s="4">
         <v>2</v>
@@ -4768,7 +4788,7 @@
         <v>340165</v>
       </c>
       <c r="L54" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M54" s="3">
         <v>0</v>
@@ -4780,10 +4800,10 @@
         <v>-1</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q54" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S54" s="5">
         <v>2</v>
@@ -4795,7 +4815,7 @@
         <v>0</v>
       </c>
       <c r="V54" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W54" s="5">
         <v>0</v>
@@ -4804,7 +4824,7 @@
         <v>0</v>
       </c>
       <c r="Z54" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="55" spans="3:26" x14ac:dyDescent="0.3">
@@ -4812,7 +4832,7 @@
         <v>10050</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E55" s="4">
         <v>2</v>
@@ -4836,7 +4856,7 @@
         <v>350101</v>
       </c>
       <c r="L55" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M55" s="3">
         <v>0</v>
@@ -4848,10 +4868,10 @@
         <v>-1</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q55" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="S55" s="5">
         <v>2</v>
@@ -4863,7 +4883,7 @@
         <v>0</v>
       </c>
       <c r="V55" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W55" s="5">
         <v>0</v>
@@ -4872,7 +4892,7 @@
         <v>0</v>
       </c>
       <c r="Z55" s="7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="56" spans="3:26" x14ac:dyDescent="0.3">
@@ -4880,7 +4900,7 @@
         <v>10051</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E56" s="4">
         <v>2</v>
@@ -4904,7 +4924,7 @@
         <v>350102</v>
       </c>
       <c r="L56" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M56" s="3">
         <v>0</v>
@@ -4916,10 +4936,10 @@
         <v>-1</v>
       </c>
       <c r="P56" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q56" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="S56" s="5">
         <v>2</v>
@@ -4931,7 +4951,7 @@
         <v>0</v>
       </c>
       <c r="V56" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W56" s="5">
         <v>0</v>
@@ -4940,7 +4960,7 @@
         <v>0</v>
       </c>
       <c r="Z56" s="7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="57" spans="3:26" x14ac:dyDescent="0.3">
@@ -4948,7 +4968,7 @@
         <v>10052</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E57" s="4">
         <v>2</v>
@@ -4972,7 +4992,7 @@
         <v>350103</v>
       </c>
       <c r="L57" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M57" s="3">
         <v>0</v>
@@ -4984,10 +5004,10 @@
         <v>-1</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q57" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S57" s="5">
         <v>2</v>
@@ -4999,7 +5019,7 @@
         <v>0</v>
       </c>
       <c r="V57" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W57" s="5">
         <v>0</v>
@@ -5008,7 +5028,7 @@
         <v>0</v>
       </c>
       <c r="Z57" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="58" spans="3:26" x14ac:dyDescent="0.3">
@@ -5016,7 +5036,7 @@
         <v>10053</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E58" s="4">
         <v>2</v>
@@ -5040,7 +5060,7 @@
         <v>350104</v>
       </c>
       <c r="L58" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -5052,10 +5072,10 @@
         <v>-1</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q58" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="S58" s="5">
         <v>2</v>
@@ -5067,7 +5087,7 @@
         <v>0</v>
       </c>
       <c r="V58" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W58" s="5">
         <v>0</v>
@@ -5076,7 +5096,7 @@
         <v>0</v>
       </c>
       <c r="Z58" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="59" spans="3:26" x14ac:dyDescent="0.3">
@@ -5084,7 +5104,7 @@
         <v>10054</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E59" s="4">
         <v>2</v>
@@ -5108,7 +5128,7 @@
         <v>350105</v>
       </c>
       <c r="L59" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M59" s="3">
         <v>0</v>
@@ -5120,23 +5140,23 @@
         <v>-1</v>
       </c>
       <c r="P59" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q59" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="Q59" s="3" t="s">
+      <c r="S59" s="5">
+        <v>2</v>
+      </c>
+      <c r="T59" s="5">
+        <v>0</v>
+      </c>
+      <c r="U59" s="5">
+        <v>0</v>
+      </c>
+      <c r="V59" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="S59" s="5">
-        <v>2</v>
-      </c>
-      <c r="T59" s="5">
-        <v>0</v>
-      </c>
-      <c r="U59" s="5">
-        <v>0</v>
-      </c>
-      <c r="V59" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="W59" s="5">
         <v>0</v>
       </c>
@@ -5144,7 +5164,7 @@
         <v>0</v>
       </c>
       <c r="Z59" s="7" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="60" spans="3:26" x14ac:dyDescent="0.3">
@@ -5152,7 +5172,7 @@
         <v>10055</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E60" s="4">
         <v>2</v>
@@ -5176,7 +5196,7 @@
         <v>350106</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M60" s="3">
         <v>0</v>
@@ -5188,10 +5208,10 @@
         <v>-1</v>
       </c>
       <c r="P60" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Q60" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="S60" s="5">
         <v>2</v>
@@ -5203,7 +5223,7 @@
         <v>0</v>
       </c>
       <c r="V60" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W60" s="5">
         <v>0</v>
@@ -5212,7 +5232,7 @@
         <v>0</v>
       </c>
       <c r="Z60" s="7" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="61" spans="3:26" x14ac:dyDescent="0.3">
@@ -5220,7 +5240,7 @@
         <v>10056</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E61" s="4">
         <v>2</v>
@@ -5244,7 +5264,7 @@
         <v>350161</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
@@ -5256,10 +5276,10 @@
         <v>-1</v>
       </c>
       <c r="P61" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q61" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S61" s="5">
         <v>2</v>
@@ -5271,7 +5291,7 @@
         <v>0</v>
       </c>
       <c r="V61" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W61" s="5">
         <v>0</v>
@@ -5280,7 +5300,7 @@
         <v>0</v>
       </c>
       <c r="Z61" s="9" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="62" spans="3:26" x14ac:dyDescent="0.3">
@@ -5288,7 +5308,7 @@
         <v>10057</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E62" s="4">
         <v>2</v>
@@ -5312,7 +5332,7 @@
         <v>350162</v>
       </c>
       <c r="L62" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M62" s="3">
         <v>0</v>
@@ -5324,10 +5344,10 @@
         <v>-1</v>
       </c>
       <c r="P62" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q62" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S62" s="5">
         <v>2</v>
@@ -5339,7 +5359,7 @@
         <v>0</v>
       </c>
       <c r="V62" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W62" s="5">
         <v>0</v>
@@ -5348,7 +5368,7 @@
         <v>0</v>
       </c>
       <c r="Z62" s="9" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="63" spans="3:26" x14ac:dyDescent="0.3">
@@ -5356,7 +5376,7 @@
         <v>10058</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E63" s="4">
         <v>2</v>
@@ -5380,7 +5400,7 @@
         <v>350163</v>
       </c>
       <c r="L63" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M63" s="3">
         <v>0</v>
@@ -5392,10 +5412,10 @@
         <v>-1</v>
       </c>
       <c r="P63" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q63" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="S63" s="5">
         <v>2</v>
@@ -5407,7 +5427,7 @@
         <v>0</v>
       </c>
       <c r="V63" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W63" s="5">
         <v>0</v>
@@ -5416,7 +5436,7 @@
         <v>0</v>
       </c>
       <c r="Z63" s="9" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="64" spans="3:26" x14ac:dyDescent="0.3">
@@ -5424,7 +5444,7 @@
         <v>10059</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E64" s="4">
         <v>2</v>
@@ -5448,7 +5468,7 @@
         <v>350164</v>
       </c>
       <c r="L64" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M64" s="3">
         <v>0</v>
@@ -5460,10 +5480,10 @@
         <v>-1</v>
       </c>
       <c r="P64" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q64" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S64" s="5">
         <v>2</v>
@@ -5475,16 +5495,16 @@
         <v>0</v>
       </c>
       <c r="V64" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="W64" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="9" t="s">
         <v>54</v>
-      </c>
-      <c r="W64" s="5">
-        <v>0</v>
-      </c>
-      <c r="Y64" s="5">
-        <v>0</v>
-      </c>
-      <c r="Z64" s="9" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="65" spans="3:26" x14ac:dyDescent="0.3">
@@ -5492,7 +5512,7 @@
         <v>10060</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E65" s="4">
         <v>2</v>
@@ -5516,7 +5536,7 @@
         <v>350165</v>
       </c>
       <c r="L65" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M65" s="3">
         <v>0</v>
@@ -5528,10 +5548,10 @@
         <v>-1</v>
       </c>
       <c r="P65" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="Q65" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S65" s="5">
         <v>2</v>
@@ -5543,7 +5563,7 @@
         <v>0</v>
       </c>
       <c r="V65" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="W65" s="5">
         <v>0</v>
@@ -5552,7 +5572,7 @@
         <v>0</v>
       </c>
       <c r="Z65" s="9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="66" spans="3:26" x14ac:dyDescent="0.3">
@@ -5560,7 +5580,7 @@
         <v>20001</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E66" s="3">
         <v>1</v>
@@ -5584,32 +5604,32 @@
         <v>400001</v>
       </c>
       <c r="L66" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="M66" s="5">
+        <v>0</v>
+      </c>
+      <c r="N66" s="1">
+        <v>0</v>
+      </c>
+      <c r="P66" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q66" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="M66" s="5">
-        <v>0</v>
-      </c>
-      <c r="N66" s="1">
-        <v>0</v>
-      </c>
-      <c r="P66" s="1" t="s">
+      <c r="S66" s="5">
+        <v>2</v>
+      </c>
+      <c r="T66" s="5">
+        <v>0</v>
+      </c>
+      <c r="U66" s="5">
+        <v>0</v>
+      </c>
+      <c r="V66" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="S66" s="5">
-        <v>2</v>
-      </c>
-      <c r="T66" s="5">
-        <v>0</v>
-      </c>
-      <c r="U66" s="5">
-        <v>0</v>
-      </c>
-      <c r="V66" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="W66" s="1">
         <v>0</v>
       </c>
@@ -5617,7 +5637,7 @@
         <v>0</v>
       </c>
       <c r="Z66" s="7" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="67" spans="3:26" x14ac:dyDescent="0.3">
@@ -5625,7 +5645,7 @@
         <v>20002</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E67" s="3">
         <v>1</v>
@@ -5649,32 +5669,32 @@
         <v>400002</v>
       </c>
       <c r="L67" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="M67" s="5">
+        <v>0</v>
+      </c>
+      <c r="N67" s="1">
+        <v>0</v>
+      </c>
+      <c r="P67" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q67" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="M67" s="5">
-        <v>0</v>
-      </c>
-      <c r="N67" s="1">
-        <v>0</v>
-      </c>
-      <c r="P67" s="1" t="s">
+      <c r="S67" s="5">
+        <v>2</v>
+      </c>
+      <c r="T67" s="5">
+        <v>0</v>
+      </c>
+      <c r="U67" s="5">
+        <v>0</v>
+      </c>
+      <c r="V67" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="Q67" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="S67" s="5">
-        <v>2</v>
-      </c>
-      <c r="T67" s="5">
-        <v>0</v>
-      </c>
-      <c r="U67" s="5">
-        <v>0</v>
-      </c>
-      <c r="V67" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="W67" s="1">
         <v>0</v>
       </c>
@@ -5682,7 +5702,7 @@
         <v>0</v>
       </c>
       <c r="Z67" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="68" spans="3:26" x14ac:dyDescent="0.3">
@@ -5690,7 +5710,7 @@
         <v>20003</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E68" s="3">
         <v>1</v>
@@ -5714,32 +5734,32 @@
         <v>400003</v>
       </c>
       <c r="L68" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="M68" s="5">
+        <v>0</v>
+      </c>
+      <c r="N68" s="1">
+        <v>0</v>
+      </c>
+      <c r="P68" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q68" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="M68" s="5">
-        <v>0</v>
-      </c>
-      <c r="N68" s="1">
-        <v>0</v>
-      </c>
-      <c r="P68" s="1" t="s">
+      <c r="S68" s="5">
+        <v>2</v>
+      </c>
+      <c r="T68" s="5">
+        <v>0</v>
+      </c>
+      <c r="U68" s="5">
+        <v>0</v>
+      </c>
+      <c r="V68" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="Q68" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="S68" s="5">
-        <v>2</v>
-      </c>
-      <c r="T68" s="5">
-        <v>0</v>
-      </c>
-      <c r="U68" s="5">
-        <v>0</v>
-      </c>
-      <c r="V68" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="W68" s="1">
         <v>0</v>
       </c>
@@ -5747,7 +5767,7 @@
         <v>0</v>
       </c>
       <c r="Z68" s="7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="69" spans="3:26" x14ac:dyDescent="0.3">
@@ -5755,7 +5775,7 @@
         <v>20004</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E69" s="3">
         <v>1</v>
@@ -5779,32 +5799,32 @@
         <v>400004</v>
       </c>
       <c r="L69" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="M69" s="5">
+        <v>0</v>
+      </c>
+      <c r="N69" s="1">
+        <v>0</v>
+      </c>
+      <c r="P69" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q69" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="M69" s="5">
-        <v>0</v>
-      </c>
-      <c r="N69" s="1">
-        <v>0</v>
-      </c>
-      <c r="P69" s="1" t="s">
+      <c r="S69" s="5">
+        <v>2</v>
+      </c>
+      <c r="T69" s="5">
+        <v>0</v>
+      </c>
+      <c r="U69" s="5">
+        <v>0</v>
+      </c>
+      <c r="V69" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="Q69" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="S69" s="5">
-        <v>2</v>
-      </c>
-      <c r="T69" s="5">
-        <v>0</v>
-      </c>
-      <c r="U69" s="5">
-        <v>0</v>
-      </c>
-      <c r="V69" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="W69" s="1">
         <v>0</v>
       </c>
@@ -5812,7 +5832,7 @@
         <v>0</v>
       </c>
       <c r="Z69" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="70" spans="3:26" x14ac:dyDescent="0.3">
@@ -5820,7 +5840,7 @@
         <v>20005</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E70" s="3">
         <v>1</v>
@@ -5844,32 +5864,32 @@
         <v>400005</v>
       </c>
       <c r="L70" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="M70" s="5">
+        <v>0</v>
+      </c>
+      <c r="N70" s="1">
+        <v>0</v>
+      </c>
+      <c r="P70" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q70" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="M70" s="5">
-        <v>0</v>
-      </c>
-      <c r="N70" s="1">
-        <v>0</v>
-      </c>
-      <c r="P70" s="1" t="s">
+      <c r="S70" s="5">
+        <v>2</v>
+      </c>
+      <c r="T70" s="5">
+        <v>0</v>
+      </c>
+      <c r="U70" s="5">
+        <v>0</v>
+      </c>
+      <c r="V70" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="Q70" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="S70" s="5">
-        <v>2</v>
-      </c>
-      <c r="T70" s="5">
-        <v>0</v>
-      </c>
-      <c r="U70" s="5">
-        <v>0</v>
-      </c>
-      <c r="V70" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="W70" s="1">
         <v>0</v>
       </c>
@@ -5877,7 +5897,7 @@
         <v>0</v>
       </c>
       <c r="Z70" s="7" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="71" spans="3:26" x14ac:dyDescent="0.3">
@@ -5885,7 +5905,7 @@
         <v>20006</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E71" s="3">
         <v>1</v>
@@ -5909,32 +5929,32 @@
         <v>400006</v>
       </c>
       <c r="L71" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="M71" s="5">
+        <v>0</v>
+      </c>
+      <c r="N71" s="1">
+        <v>0</v>
+      </c>
+      <c r="P71" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q71" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="M71" s="5">
-        <v>0</v>
-      </c>
-      <c r="N71" s="1">
-        <v>0</v>
-      </c>
-      <c r="P71" s="1" t="s">
+      <c r="S71" s="5">
+        <v>2</v>
+      </c>
+      <c r="T71" s="5">
+        <v>0</v>
+      </c>
+      <c r="U71" s="5">
+        <v>0</v>
+      </c>
+      <c r="V71" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="Q71" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="S71" s="5">
-        <v>2</v>
-      </c>
-      <c r="T71" s="5">
-        <v>0</v>
-      </c>
-      <c r="U71" s="5">
-        <v>0</v>
-      </c>
-      <c r="V71" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="W71" s="1">
         <v>0</v>
       </c>
@@ -5942,7 +5962,7 @@
         <v>0</v>
       </c>
       <c r="Z71" s="7" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="72" spans="3:26" x14ac:dyDescent="0.3">
@@ -5950,7 +5970,7 @@
         <v>20007</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E72" s="3">
         <v>1</v>
@@ -5974,7 +5994,7 @@
         <v>400007</v>
       </c>
       <c r="L72" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="M72" s="5">
         <v>0</v>
@@ -5983,23 +6003,23 @@
         <v>0</v>
       </c>
       <c r="P72" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q72" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="S72" s="5">
+        <v>2</v>
+      </c>
+      <c r="T72" s="5">
+        <v>0</v>
+      </c>
+      <c r="U72" s="5">
+        <v>0</v>
+      </c>
+      <c r="V72" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="S72" s="5">
-        <v>2</v>
-      </c>
-      <c r="T72" s="5">
-        <v>0</v>
-      </c>
-      <c r="U72" s="5">
-        <v>0</v>
-      </c>
-      <c r="V72" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="W72" s="1">
         <v>0</v>
       </c>
@@ -6007,7 +6027,7 @@
         <v>0</v>
       </c>
       <c r="Z72" s="7" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="73" spans="3:26" x14ac:dyDescent="0.3">
@@ -6015,7 +6035,7 @@
         <v>20008</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E73" s="3">
         <v>1</v>
@@ -6039,32 +6059,32 @@
         <v>400008</v>
       </c>
       <c r="L73" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="M73" s="5">
+        <v>0</v>
+      </c>
+      <c r="N73" s="1">
+        <v>0</v>
+      </c>
+      <c r="P73" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="Q73" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="M73" s="5">
-        <v>0</v>
-      </c>
-      <c r="N73" s="1">
-        <v>0</v>
-      </c>
-      <c r="P73" s="1" t="s">
+      <c r="S73" s="5">
+        <v>2</v>
+      </c>
+      <c r="T73" s="5">
+        <v>0</v>
+      </c>
+      <c r="U73" s="5">
+        <v>0</v>
+      </c>
+      <c r="V73" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="Q73" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="S73" s="5">
-        <v>2</v>
-      </c>
-      <c r="T73" s="5">
-        <v>0</v>
-      </c>
-      <c r="U73" s="5">
-        <v>0</v>
-      </c>
-      <c r="V73" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="W73" s="1">
         <v>0</v>
       </c>
@@ -6072,7 +6092,7 @@
         <v>0</v>
       </c>
       <c r="Z73" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="74" spans="3:26" x14ac:dyDescent="0.3">

--- a/Unity/Assets/Config/Excel/JingLingConfig.xlsx
+++ b/Unity/Assets/Config/Excel/JingLingConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitMengJing\Unity\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E63EF601-8EE2-4436-A27D-45159CB87045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CFB9F4B-C06D-474B-BEB7-E79F0A568C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -181,7 +181,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="191">
   <si>
     <t>c</t>
   </si>
@@ -755,6 +755,10 @@
   </si>
   <si>
     <t>冰狼</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,60,400,25,0</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -907,7 +911,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -935,6 +939,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="2" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2103,8 +2110,8 @@
       <c r="Y14" s="5">
         <v>0</v>
       </c>
-      <c r="Z14" s="9" t="s">
-        <v>54</v>
+      <c r="Z14" s="11" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="15" spans="3:26" x14ac:dyDescent="0.3">
